--- a/src/attributions/attributions_saliency_traj_42.xlsx
+++ b/src/attributions/attributions_saliency_traj_42.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2.908976603066549e-05</v>
+        <v>3.217049556638435e-15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0003491916577331722</v>
+        <v>1.202915851746444e-15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001013090804917738</v>
+        <v>6.642396796984439e-15</v>
       </c>
       <c r="D4" t="n">
-        <v>6.69736837153323e-05</v>
+        <v>9.891193360244202e-15</v>
       </c>
       <c r="E4" t="n">
-        <v>3.365323937032372e-05</v>
+        <v>2.563921085735484e-15</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004901305655948818</v>
+        <v>4.302189606354787e-15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001201918348670006</v>
+        <v>1.126577536770743e-14</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000144069388625212</v>
+        <v>6.299990504320466e-15</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001199688922497444</v>
+        <v>7.273475623841821e-16</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001084623072529212</v>
+        <v>5.270834461978176e-15</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001465761160943657</v>
+        <v>4.06598091648577e-15</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001313009997829795</v>
+        <v>1.315264290167005e-14</v>
       </c>
       <c r="M4" t="n">
-        <v>6.479208241216838e-05</v>
+        <v>1.265812135014047e-14</v>
       </c>
       <c r="N4" t="n">
-        <v>3.124131035292521e-05</v>
+        <v>4.494245856815227e-15</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0002119622513419017</v>
+        <v>1.146695077487801e-14</v>
       </c>
       <c r="P4" t="n">
-        <v>1.842345955083147e-05</v>
+        <v>1.289420722023213e-14</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.565962343709543e-05</v>
+        <v>6.425150210189129e-15</v>
       </c>
       <c r="R4" t="n">
-        <v>9.976467481465079e-06</v>
+        <v>3.06443814822397e-16</v>
       </c>
       <c r="S4" t="n">
-        <v>6.627646143897437e-06</v>
+        <v>2.213095285575803e-15</v>
       </c>
       <c r="T4" t="n">
-        <v>4.491060462896712e-05</v>
+        <v>5.646198383103341e-15</v>
       </c>
       <c r="U4" t="n">
-        <v>2.861712346202694e-05</v>
+        <v>1.938948837032213e-15</v>
       </c>
       <c r="V4" t="n">
-        <v>4.553555845632218e-05</v>
+        <v>2.97421833967131e-15</v>
       </c>
       <c r="W4" t="n">
-        <v>7.85911688581109e-05</v>
+        <v>1.278670772779725e-14</v>
       </c>
       <c r="X4" t="n">
-        <v>5.627179780276492e-05</v>
+        <v>3.336519953958629e-15</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.604303335829172e-05</v>
+        <v>1.59000789693841e-16</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.025075016514165e-05</v>
+        <v>6.448688832276853e-15</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.353800174314529e-05</v>
+        <v>5.701917692681386e-16</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0001326860801782459</v>
+        <v>1.583110190011563e-15</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.351837924332358e-05</v>
+        <v>7.790682941160362e-15</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0001156930593424477</v>
+        <v>1.146867787505746e-16</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0001307895145146176</v>
+        <v>1.732713255034736e-15</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.878235141513869e-05</v>
+        <v>1.288973996846831e-14</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.737251194659621e-05</v>
+        <v>5.703243511002076e-15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0001337149587925524</v>
+        <v>1.998294506415691e-15</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.740400567650795e-05</v>
+        <v>7.307239733547917e-15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5.245145439403132e-05</v>
+        <v>2.747148923544929e-15</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.588262163451873e-05</v>
+        <v>3.454160336596279e-15</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.403517671860754e-06</v>
+        <v>5.079812862262808e-15</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.24145910074003e-05</v>
+        <v>1.894949816466207e-16</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.404083276516758e-05</v>
+        <v>5.783587550664462e-15</v>
       </c>
       <c r="AO4" t="n">
-        <v>3.341287083458155e-05</v>
+        <v>3.520577884056383e-15</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.811127655557357e-05</v>
+        <v>1.890234701686197e-15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.52510648756288e-05</v>
+        <v>2.949845178372304e-16</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.486551551963203e-05</v>
+        <v>1.635590551478426e-15</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.9297993023647e-05</v>
+        <v>1.001788196058266e-15</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.67402247118298e-05</v>
+        <v>2.059349647105406e-16</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0001004456207738258</v>
+        <v>8.497492125095554e-15</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0001228136825375259</v>
+        <v>2.311214735152794e-15</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.0001543688558740541</v>
+        <v>2.700537123973999e-15</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.713499846635386e-05</v>
+        <v>7.556692207063729e-16</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.562000195728615e-05</v>
+        <v>4.08646005556801e-15</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0001880231429822743</v>
+        <v>5.391652276959214e-15</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0001926800614455715</v>
+        <v>9.853090430144915e-15</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0001300426083616912</v>
+        <v>4.701868243505596e-16</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0001275745453312993</v>
+        <v>1.56498442609415e-16</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.594800990773365e-05</v>
+        <v>1.112914154177702e-15</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.397426866693422e-05</v>
+        <v>2.330433065693047e-15</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.706467810436152e-05</v>
+        <v>5.038852890032431e-16</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.259464352187933e-05</v>
+        <v>2.555845261858125e-15</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0002441676333546638</v>
+        <v>7.398258505928075e-15</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0001203996507683769</v>
+        <v>2.148694311804875e-15</v>
       </c>
       <c r="BJ4" t="n">
-        <v>7.518228812841699e-05</v>
+        <v>8.740916688642231e-15</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.861381679191254e-05</v>
+        <v>4.311780454537429e-16</v>
       </c>
       <c r="BL4" t="n">
-        <v>2.458743256283924e-05</v>
+        <v>3.775302925910617e-15</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.854865331551991e-05</v>
+        <v>2.709074369049375e-15</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.149806773057207e-05</v>
+        <v>2.20324598646513e-15</v>
       </c>
       <c r="BO4" t="n">
-        <v>8.309126133099198e-05</v>
+        <v>2.350728610383971e-15</v>
       </c>
       <c r="BP4" t="n">
-        <v>7.944252138258889e-05</v>
+        <v>5.578955825552611e-15</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.136049781460315e-05</v>
+        <v>5.982107721303636e-16</v>
       </c>
       <c r="BR4" t="n">
-        <v>3.853228918160312e-05</v>
+        <v>6.917024572000306e-16</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.638452709419653e-05</v>
+        <v>3.848341306402934e-15</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.000151616201037541</v>
+        <v>3.054441041864002e-15</v>
       </c>
       <c r="BU4" t="n">
-        <v>7.909658597782254e-05</v>
+        <v>6.39815759950074e-16</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.614177254959941e-05</v>
+        <v>3.324586742039473e-15</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.613205525558442e-05</v>
+        <v>2.361127210360938e-15</v>
       </c>
       <c r="BX4" t="n">
-        <v>4.817484659724869e-05</v>
+        <v>9.947285576077276e-15</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.249678310472518e-05</v>
+        <v>1.53737564128828e-14</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.869877375313081e-05</v>
+        <v>1.392258420402118e-15</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.549280755687505e-05</v>
+        <v>3.609491144287904e-16</v>
       </c>
       <c r="CB4" t="n">
-        <v>7.502026710426435e-05</v>
+        <v>3.179274640047972e-15</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.053892214666121e-05</v>
+        <v>1.659771753935761e-15</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.011709355225321e-05</v>
+        <v>8.654801601751965e-16</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.251605863217264e-05</v>
+        <v>2.217893091947289e-15</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.301979293406475e-05</v>
+        <v>2.357976247797152e-15</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.32347042078618e-06</v>
+        <v>1.356738305517246e-15</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.430718566552969e-05</v>
+        <v>4.455287423439213e-17</v>
       </c>
       <c r="CI4" t="n">
-        <v>8.512032945873216e-05</v>
+        <v>1.395178778246014e-15</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.068427627615165e-05</v>
+        <v>9.192804107321191e-16</v>
       </c>
       <c r="CK4" t="n">
-        <v>7.973225365276448e-06</v>
+        <v>9.831011669341784e-16</v>
       </c>
       <c r="CL4" t="n">
-        <v>3.453826138866134e-05</v>
+        <v>1.891465440558558e-15</v>
       </c>
       <c r="CM4" t="n">
-        <v>8.669547241879627e-05</v>
+        <v>1.394664099851439e-15</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.000161583608132787</v>
+        <v>9.534032600672007e-15</v>
       </c>
       <c r="CO4" t="n">
-        <v>6.641724030487239e-05</v>
+        <v>2.016394965223805e-15</v>
       </c>
       <c r="CP4" t="n">
-        <v>9.637501352699474e-05</v>
+        <v>1.970178306522768e-15</v>
       </c>
       <c r="CQ4" t="n">
-        <v>9.540319297229871e-05</v>
+        <v>1.294410423708899e-14</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.320374485658249e-05</v>
+        <v>6.685724649818864e-15</v>
       </c>
       <c r="CS4" t="n">
-        <v>5.192966636968777e-05</v>
+        <v>3.62138179280146e-15</v>
       </c>
       <c r="CT4" t="n">
-        <v>7.774781988700852e-05</v>
+        <v>5.385700176438859e-15</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0001044791715685278</v>
+        <v>9.659593376641195e-16</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.082924973161425e-05</v>
+        <v>8.159807194079577e-16</v>
       </c>
       <c r="CW4" t="n">
-        <v>3.754527642740868e-05</v>
+        <v>1.788674392519223e-15</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.534168404759839e-05</v>
+        <v>1.761600678426133e-15</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.216494067397434e-06</v>
+        <v>5.773858318474062e-16</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.542842619528528e-05</v>
+        <v>1.35905208189179e-15</v>
       </c>
       <c r="DA4" t="n">
-        <v>6.846713949926198e-05</v>
+        <v>2.194939769626118e-15</v>
       </c>
       <c r="DB4" t="n">
-        <v>3.144329821225256e-05</v>
+        <v>1.256528696263787e-15</v>
       </c>
       <c r="DC4" t="n">
-        <v>3.232270682929084e-05</v>
+        <v>1.31745768198392e-15</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.663218012661673e-05</v>
+        <v>5.567420507360428e-16</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.000154146968270652</v>
+        <v>1.050369135473326e-15</v>
       </c>
       <c r="DF4" t="n">
-        <v>4.552171958494e-05</v>
+        <v>1.078096420188517e-14</v>
       </c>
       <c r="DG4" t="n">
-        <v>8.559305570088327e-05</v>
+        <v>4.540809799024638e-15</v>
       </c>
       <c r="DH4" t="n">
-        <v>2.306666283402592e-05</v>
+        <v>1.275225783904123e-15</v>
       </c>
       <c r="DI4" t="n">
-        <v>3.408810152905062e-05</v>
+        <v>3.560386526753204e-15</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0001867793325800449</v>
+        <v>1.309522592630747e-14</v>
       </c>
       <c r="DK4" t="n">
-        <v>1.90856426343089e-05</v>
+        <v>2.0379523772479e-15</v>
       </c>
       <c r="DL4" t="n">
-        <v>3.840506906271912e-05</v>
+        <v>9.297151154884632e-16</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0002207632351201028</v>
+        <v>5.377657175088205e-15</v>
       </c>
       <c r="DN4" t="n">
-        <v>8.532232459401712e-05</v>
+        <v>3.868470197361485e-15</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.281688830407802e-05</v>
+        <v>1.100084675521233e-15</v>
       </c>
       <c r="DP4" t="n">
-        <v>3.110471516265534e-05</v>
+        <v>3.357652578959676e-15</v>
       </c>
       <c r="DQ4" t="n">
-        <v>3.284257036284544e-05</v>
+        <v>4.216114118254805e-15</v>
       </c>
       <c r="DR4" t="n">
-        <v>1.779485319275409e-05</v>
+        <v>2.256896841585981e-15</v>
       </c>
       <c r="DS4" t="n">
-        <v>3.053403997910209e-05</v>
+        <v>7.512339973758718e-16</v>
       </c>
       <c r="DT4" t="n">
-        <v>3.800812919507734e-05</v>
+        <v>4.481111763935102e-15</v>
       </c>
       <c r="DU4" t="n">
-        <v>2.344551649002824e-05</v>
+        <v>9.312042205855599e-15</v>
       </c>
       <c r="DV4" t="n">
-        <v>9.717634384287521e-05</v>
+        <v>5.953968757400256e-16</v>
       </c>
       <c r="DW4" t="n">
-        <v>3.226910484954715e-05</v>
+        <v>3.672391810951008e-16</v>
       </c>
       <c r="DX4" t="n">
-        <v>1.282025914406404e-05</v>
+        <v>8.97925058417591e-15</v>
       </c>
       <c r="DY4" t="n">
-        <v>3.973691127612256e-05</v>
+        <v>3.688263937833133e-15</v>
       </c>
       <c r="DZ4" t="n">
-        <v>9.201250213664025e-05</v>
+        <v>8.734686761315176e-15</v>
       </c>
       <c r="EA4" t="n">
-        <v>4.28333441959694e-05</v>
+        <v>7.091216897603153e-16</v>
       </c>
       <c r="EB4" t="n">
-        <v>9.032650268636644e-06</v>
+        <v>3.036106749022886e-16</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.269487024226692e-06</v>
+        <v>1.086538712870505e-15</v>
       </c>
       <c r="ED4" t="n">
-        <v>4.168580198893324e-05</v>
+        <v>3.193526816418473e-15</v>
       </c>
       <c r="EE4" t="n">
-        <v>1.991860699490644e-05</v>
+        <v>5.134420652855819e-15</v>
       </c>
       <c r="EF4" t="n">
-        <v>3.552769339876249e-05</v>
+        <v>4.037488422206029e-17</v>
       </c>
       <c r="EG4" t="n">
-        <v>2.817072891048156e-05</v>
+        <v>1.18725834183733e-15</v>
       </c>
       <c r="EH4" t="n">
-        <v>5.73346005694475e-06</v>
+        <v>1.798563819815772e-16</v>
       </c>
       <c r="EI4" t="n">
-        <v>5.974591476842761e-05</v>
+        <v>1.168130432064197e-16</v>
       </c>
       <c r="EJ4" t="n">
-        <v>3.669492434710264e-05</v>
+        <v>5.091537280560465e-16</v>
       </c>
       <c r="EK4" t="n">
-        <v>1.387204247293994e-05</v>
+        <v>6.175065003061718e-16</v>
       </c>
       <c r="EL4" t="n">
-        <v>5.182203676667996e-05</v>
+        <v>1.995450805053521e-15</v>
       </c>
       <c r="EM4" t="n">
-        <v>5.24457027495373e-06</v>
+        <v>1.31404117459117e-15</v>
       </c>
       <c r="EN4" t="n">
-        <v>2.986173740282538e-06</v>
+        <v>4.921396525302572e-15</v>
       </c>
       <c r="EO4" t="n">
-        <v>6.402103463187814e-05</v>
+        <v>1.27895283475116e-15</v>
       </c>
       <c r="EP4" t="n">
-        <v>1.495502147008665e-05</v>
+        <v>7.930296205482736e-16</v>
       </c>
       <c r="EQ4" t="n">
-        <v>2.257922642456833e-05</v>
+        <v>2.260519177984914e-18</v>
       </c>
       <c r="ER4" t="n">
-        <v>3.349659527884796e-05</v>
+        <v>1.581074028685482e-15</v>
       </c>
       <c r="ES4" t="n">
-        <v>6.189589475980029e-05</v>
+        <v>4.326251694803914e-15</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0001321336749242619</v>
+        <v>1.280703757732253e-15</v>
       </c>
       <c r="EU4" t="n">
-        <v>6.213262531673536e-05</v>
+        <v>6.403154035098356e-16</v>
       </c>
       <c r="EV4" t="n">
-        <v>3.931924220523797e-05</v>
+        <v>6.761581320684933e-16</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0001456339523429051</v>
+        <v>1.495405116400182e-15</v>
       </c>
       <c r="EX4" t="n">
-        <v>1.054083440976683e-05</v>
+        <v>6.393367628184017e-16</v>
       </c>
       <c r="EY4" t="n">
-        <v>4.562833782983944e-05</v>
+        <v>2.827703874411181e-15</v>
       </c>
       <c r="EZ4" t="n">
-        <v>6.242616109375376e-06</v>
+        <v>2.031607041681782e-15</v>
       </c>
       <c r="FA4" t="n">
-        <v>9.494337064097635e-06</v>
+        <v>1.002327014891838e-15</v>
       </c>
       <c r="FB4" t="n">
-        <v>1.660194720898289e-05</v>
+        <v>6.399109982170809e-16</v>
       </c>
       <c r="FC4" t="n">
-        <v>5.615775808109902e-05</v>
+        <v>8.305520683808958e-16</v>
       </c>
       <c r="FD4" t="n">
-        <v>5.855286872247234e-06</v>
+        <v>1.418287636992125e-15</v>
       </c>
       <c r="FE4" t="n">
-        <v>8.7736189016141e-06</v>
+        <v>1.805690013880141e-15</v>
       </c>
       <c r="FF4" t="n">
-        <v>5.189625517232344e-05</v>
+        <v>7.24387870447798e-16</v>
       </c>
       <c r="FG4" t="n">
-        <v>7.054110756143928e-05</v>
+        <v>4.046412761338301e-15</v>
       </c>
       <c r="FH4" t="n">
-        <v>3.062514952034689e-05</v>
+        <v>3.500999352755311e-15</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.0001222975988639519</v>
+        <v>3.90478631145854e-15</v>
       </c>
       <c r="FJ4" t="n">
-        <v>5.558414341066964e-05</v>
+        <v>3.474275039752964e-17</v>
       </c>
       <c r="FK4" t="n">
-        <v>9.38037846935913e-05</v>
+        <v>7.093108957449083e-16</v>
       </c>
       <c r="FL4" t="n">
-        <v>8.661917672725394e-05</v>
+        <v>3.322084394955047e-15</v>
       </c>
       <c r="FM4" t="n">
-        <v>3.755568468477577e-05</v>
+        <v>2.11787882966729e-16</v>
       </c>
       <c r="FN4" t="n">
-        <v>7.871459820307791e-05</v>
+        <v>9.448280679157876e-15</v>
       </c>
       <c r="FO4" t="n">
-        <v>5.573282760451548e-05</v>
+        <v>2.510484106433815e-15</v>
       </c>
       <c r="FP4" t="n">
-        <v>5.448588490253314e-05</v>
+        <v>3.939461299220289e-15</v>
       </c>
       <c r="FQ4" t="n">
-        <v>2.352593583054841e-06</v>
+        <v>2.41488563866609e-15</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.0001228595210704952</v>
+        <v>6.805619198887395e-15</v>
       </c>
       <c r="FS4" t="n">
-        <v>8.613574027549475e-05</v>
+        <v>1.084190144617653e-14</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0002064662403427064</v>
+        <v>3.607516710487854e-15</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0001968209544429556</v>
+        <v>5.417593613880943e-16</v>
       </c>
       <c r="FV4" t="n">
-        <v>2.698075695661828e-05</v>
+        <v>1.073346259420314e-14</v>
       </c>
       <c r="FW4" t="n">
-        <v>4.255631574778818e-05</v>
+        <v>3.999924628577669e-15</v>
       </c>
       <c r="FX4" t="n">
-        <v>8.354317105840892e-05</v>
+        <v>3.774939972292718e-15</v>
       </c>
       <c r="FY4" t="n">
-        <v>7.335076224990189e-05</v>
+        <v>9.618443457272397e-16</v>
       </c>
       <c r="FZ4" t="n">
-        <v>6.760510586900637e-05</v>
+        <v>2.393887480145419e-15</v>
       </c>
       <c r="GA4" t="n">
-        <v>2.100230994983576e-05</v>
+        <v>2.44467070522334e-15</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.000105025312223006</v>
+        <v>2.892206703894017e-16</v>
       </c>
       <c r="GC4" t="n">
-        <v>7.879703480284661e-05</v>
+        <v>3.215097780969725e-15</v>
       </c>
       <c r="GD4" t="n">
-        <v>7.699559500906616e-05</v>
+        <v>4.518299051418408e-15</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.0002069299662252888</v>
+        <v>8.768541715304865e-16</v>
       </c>
       <c r="GF4" t="n">
-        <v>7.453873695340008e-05</v>
+        <v>4.879837277262013e-16</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0001676081883488223</v>
+        <v>7.613255796731951e-15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.01307631377130747</v>
+        <v>0.000782312243245542</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03085260838270187</v>
+        <v>0.00133297371212393</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001150261843577027</v>
+        <v>0.0006557228625752032</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01863517612218857</v>
+        <v>0.0007539120852015913</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004063652362674475</v>
+        <v>0.0001250153873115778</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01584704592823982</v>
+        <v>4.581550456350669e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0005593793466687202</v>
+        <v>0.0005266660591587424</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003683926071971655</v>
+        <v>0.0007205945439636707</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01552286650985479</v>
+        <v>0.001127753406763077</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01165396254509687</v>
+        <v>0.000963105820119381</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02925932221114635</v>
+        <v>0.0009005723404698074</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001145642250776291</v>
+        <v>0.0007451748824678361</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01695723831653595</v>
+        <v>0.001555036520585418</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003633263055235147</v>
+        <v>0.0005156317492946982</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01055048499256372</v>
+        <v>0.0006684251129627228</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002347338479012251</v>
+        <v>4.279098357073963e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.007422920782119036</v>
+        <v>0.0003886221384163946</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01397498324513435</v>
+        <v>0.001169670489616692</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0006872409721836448</v>
+        <v>0.0002821986272465438</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0007832577684894204</v>
+        <v>0.0009928115177899599</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003123981412500143</v>
+        <v>0.0004487643018364906</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003673734609037638</v>
+        <v>0.001055686152540147</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01226140093058348</v>
+        <v>0.001843092381022871</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002871991135179996</v>
+        <v>0.0003210972645319998</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00600759033113718</v>
+        <v>0.0004704933089669794</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00745152123272419</v>
+        <v>0.001103376853279769</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00329485023394227</v>
+        <v>0.001009416184388101</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002914820564910769</v>
+        <v>0.0001009315019473433</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.002379724755883217</v>
+        <v>0.000184752861969173</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0007023217622190714</v>
+        <v>0.0001450596028007567</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0004728944040834904</v>
+        <v>6.540672620758414e-05</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.003622473450377584</v>
+        <v>0.0003782073326874524</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002303958404809237</v>
+        <v>3.596934766392224e-05</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.004720366559922695</v>
+        <v>0.0004348872462287545</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.001108588185161352</v>
+        <v>0.000585007481276989</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.001573588117025793</v>
+        <v>0.0004499624483287334</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.000404873862862587</v>
+        <v>5.013516420149244e-05</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.005031499080359936</v>
+        <v>0.0009365587611682713</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.005139447748661041</v>
+        <v>0.0003562875499483198</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0003281226963736117</v>
+        <v>0.001557936426252127</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.000682845595292747</v>
+        <v>0.0003669323050417006</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.004268341697752476</v>
+        <v>0.0001198389509227127</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.004132888279855251</v>
+        <v>1.031917054206133e-05</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.002785602351650596</v>
+        <v>0.001032426254823804</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.00516365235671401</v>
+        <v>3.440024011069909e-05</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.001701905624940991</v>
+        <v>0.0003723332192748785</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.01159984245896339</v>
+        <v>0.001383936265483499</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.005790079478174448</v>
+        <v>6.118151941336691e-05</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0149304186925292</v>
+        <v>0.0008920985856093466</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.01094580627977848</v>
+        <v>0.0004453488509170711</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.01499676704406738</v>
+        <v>0.0002384342806180939</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.01452191267162561</v>
+        <v>0.0007459142943844199</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.01432428043335676</v>
+        <v>0.0007247678586281836</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.005794031079858541</v>
+        <v>4.414954310050234e-05</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.004565932787954807</v>
+        <v>0.0003995585138909519</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.004760162439197302</v>
+        <v>4.563299444271252e-05</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.003318789880722761</v>
+        <v>1.988984877243638e-05</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.008187221363186836</v>
+        <v>0.001211283961310983</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.004680365324020386</v>
+        <v>0.0004116171330679208</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.002098740777000785</v>
+        <v>0.0004660371050704271</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.01069463603198528</v>
+        <v>8.96220444701612e-05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.001869703875854611</v>
+        <v>0.0005237201694399118</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.01553323678672314</v>
+        <v>0.0006545575452037156</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.004595935344696045</v>
+        <v>4.884123336523771e-05</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.009498954750597477</v>
+        <v>8.832168532535434e-05</v>
       </c>
       <c r="BN5" t="n">
-        <v>8.341344073414803e-05</v>
+        <v>0.0004577343934215605</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.003022716380655766</v>
+        <v>0.000170359606272541</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.005778532475233078</v>
+        <v>0.0008513127104379237</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.001625596196390688</v>
+        <v>0.0001238436088897288</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.003209307324141264</v>
+        <v>0.0002648575755301863</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.004531925078481436</v>
+        <v>7.716917025391012e-06</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0002780569193419069</v>
+        <v>0.0004455061280168593</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0002171439118683338</v>
+        <v>0.0003110450925305486</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.01085755694657564</v>
+        <v>0.0002245760406367481</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.004330605734139681</v>
+        <v>0.000157448259415105</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.01085147820413113</v>
+        <v>0.002198266331106424</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.005497273989021778</v>
+        <v>0.0013707026373595</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.007344161160290241</v>
+        <v>0.0001321198797086254</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.008044124580919743</v>
+        <v>0.0001353515981463715</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.008742514066398144</v>
+        <v>0.0004792683466803282</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.002768231555819511</v>
+        <v>0.0008689878159202635</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.001582159427925944</v>
+        <v>3.11752810375765e-05</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.003536216681823134</v>
+        <v>0.0005762967630289495</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.003887323429808021</v>
+        <v>0.0003354497603140771</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.004183589946478605</v>
+        <v>0.0003431219374760985</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001163058564998209</v>
+        <v>0.0002589869836810976</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.001535018673166633</v>
+        <v>8.028127194847912e-05</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.00306805269792676</v>
+        <v>6.244900578167289e-05</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.001809301087632775</v>
+        <v>1.816093572415411e-06</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.002373781288042665</v>
+        <v>0.000289490883005783</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.005485385190695524</v>
+        <v>0.0003166153910569847</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.005299713928252459</v>
+        <v>0.001010343432426453</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.00114527135156095</v>
+        <v>0.0002471724874339998</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.001376975793391466</v>
+        <v>0.000753236236050725</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.008929220959544182</v>
+        <v>0.0006981914630159736</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.001458434853702784</v>
+        <v>0.0003179262566845864</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.009945210069417953</v>
+        <v>0.0008066721493378282</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.006544825155287981</v>
+        <v>5.966072785668075e-05</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.002695344854146242</v>
+        <v>0.000364933192031458</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.001635433058254421</v>
+        <v>4.668674955610186e-05</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.00546642579138279</v>
+        <v>0.0005083665600977838</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.004166902974247932</v>
+        <v>0.0003928002552129328</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.004190298728644848</v>
+        <v>0.0003890414081979543</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0002987014013342559</v>
+        <v>0.0001161305990535766</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.002102382015436888</v>
+        <v>0.0001287860359298065</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.003565746825188398</v>
+        <v>0.0001101175585063174</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.001240837038494647</v>
+        <v>0.0002186115161748603</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.001841812743805349</v>
+        <v>0.0003771592164412141</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.002579874591901898</v>
+        <v>2.99772946164012e-05</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.005128738936036825</v>
+        <v>0.0004522381641436368</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.002841418376192451</v>
+        <v>0.0003386615426279604</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.009069712832570076</v>
+        <v>6.349661998683587e-05</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.001883870689198375</v>
+        <v>0.0005194611730985343</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.002875894075259566</v>
+        <v>0.001195662305690348</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.00368836522102356</v>
+        <v>0.0002043128479272127</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.007783389650285244</v>
+        <v>0.001086746109649539</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0001030284911394119</v>
+        <v>0.0007684010197408497</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0006616443279199302</v>
+        <v>0.0003203355881851166</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.00834028422832489</v>
+        <v>4.310286021791399e-05</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.004021497443318367</v>
+        <v>0.0002003295230679214</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.003419488668441772</v>
+        <v>0.0002116550604114309</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0002946442691609263</v>
+        <v>0.0001305687765125185</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.003093284787610173</v>
+        <v>0.0006366060115396976</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.004951938055455685</v>
+        <v>0.0002684428764041513</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.00355942826718092</v>
+        <v>6.483413744717836e-05</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.004363450687378645</v>
+        <v>4.997415089746937e-05</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0004844228969886899</v>
+        <v>5.641599273076281e-05</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.001134112826548517</v>
+        <v>0.0004478598129935563</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.004598652943968773</v>
+        <v>0.0001682555885054171</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.003087350632995367</v>
+        <v>0.001100552268326283</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.01046539749950171</v>
+        <v>0.0005557098193094134</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.001520739635452628</v>
+        <v>0.0005887660081498325</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.001002580975182354</v>
+        <v>0.000774515385273844</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.006223687436431646</v>
+        <v>0.001738218939863145</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.00147815584205091</v>
+        <v>0.0008240928291343153</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0006134208524599671</v>
+        <v>0.0001526529085822403</v>
       </c>
       <c r="EG5" t="n">
-        <v>4.302116576582193e-05</v>
+        <v>0.0007297187112271786</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.006378142163157463</v>
+        <v>0.0001146223294199444</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0007034232839941978</v>
+        <v>0.0002680394682101905</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.00360291893593967</v>
+        <v>0.0002054802316706628</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.003436516737565398</v>
+        <v>0.0002592760429251939</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.00197036424651742</v>
+        <v>1.312544918619096e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.001357151661068201</v>
+        <v>0.0001524963154224679</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.001133662648499012</v>
+        <v>5.806762055726722e-05</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.001567813567817211</v>
+        <v>0.0005199553561396897</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.006042769178748131</v>
+        <v>0.0001942377421073616</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.004847347736358643</v>
+        <v>0.0002458387170918286</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.00676847854629159</v>
+        <v>4.881771019427106e-05</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.006825749296694994</v>
+        <v>0.0006496438873000443</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.008795845322310925</v>
+        <v>0.0005080039263702929</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.006691954098641872</v>
+        <v>0.0001325397897744551</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.008095537312328815</v>
+        <v>0.0001814776624087244</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.003494176780804992</v>
+        <v>0.0006022987654432654</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.001305320882238448</v>
+        <v>2.279975160490721e-05</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.004133753944188356</v>
+        <v>0.000601857784204185</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.003279470838606358</v>
+        <v>0.0002962410217151046</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.005440435837954283</v>
+        <v>0.0002727631363086402</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.002128382911905646</v>
+        <v>0.0002369132416788489</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.002442571334540844</v>
+        <v>5.02970433444716e-05</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.004813862964510918</v>
+        <v>0.0001749475341057405</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.001664279378019273</v>
+        <v>0.0002808675926644355</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.003373037558048964</v>
+        <v>0.0003599594929255545</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.001707104267552495</v>
+        <v>0.0007387822261080146</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.000958593504037708</v>
+        <v>1.210101618198678e-05</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.002017602091655135</v>
+        <v>0.0004799589223694056</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.006255419924855232</v>
+        <v>0.0006022959714755416</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0008247612277045846</v>
+        <v>6.721034878864884e-05</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.003742095781490207</v>
+        <v>0.0003911762323696166</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.004023002926260233</v>
+        <v>0.0005370889557525516</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.003383478615432978</v>
+        <v>0.00109134940430522</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0006976157892495394</v>
+        <v>0.0003381487913429737</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.004376059863716364</v>
+        <v>0.0002261791814817116</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.01274529471993446</v>
+        <v>0.001088522491045296</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.003485127817839384</v>
+        <v>2.147148916264996e-05</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.005157620646059513</v>
+        <v>0.0006831659120507538</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.02292894758284092</v>
+        <v>0.001403047353960574</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.00346144032664597</v>
+        <v>0.0006772056221961975</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.008672069758176804</v>
+        <v>0.0006987127126194537</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.002485082950443029</v>
+        <v>0.0007006555679254234</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.00244154897518456</v>
+        <v>0.0001282900630030781</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.002383586717769504</v>
+        <v>2.191205203416757e-05</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.003431391902267933</v>
+        <v>0.0007199698593467474</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.002871476113796234</v>
+        <v>0.0002803259994834661</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.005948647856712341</v>
+        <v>2.517995744710788e-05</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.009710272774100304</v>
+        <v>0.001209099078550935</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0007469740230590105</v>
+        <v>0.0003577845927793533</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.01455497648566961</v>
+        <v>0.0008322990033775568</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.006647234782576561</v>
+        <v>8.430815796600655e-06</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.002658323384821415</v>
+        <v>0.0005862522521056235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.009107819527344e-07</v>
+        <v>1.455037167260377e-18</v>
       </c>
       <c r="B6" t="n">
-        <v>1.278576064578374e-06</v>
+        <v>2.450662192775743e-16</v>
       </c>
       <c r="C6" t="n">
-        <v>3.94049067153901e-07</v>
+        <v>8.615802749022499e-17</v>
       </c>
       <c r="D6" t="n">
-        <v>2.156869243208348e-07</v>
+        <v>1.019423342610762e-16</v>
       </c>
       <c r="E6" t="n">
-        <v>7.200762865977595e-07</v>
+        <v>2.008382218831236e-16</v>
       </c>
       <c r="F6" t="n">
-        <v>1.557307541588671e-06</v>
+        <v>2.654266413983016e-16</v>
       </c>
       <c r="G6" t="n">
-        <v>5.667195068781439e-07</v>
+        <v>5.511521626797565e-16</v>
       </c>
       <c r="H6" t="n">
-        <v>5.822640147812308e-08</v>
+        <v>4.952028307169721e-16</v>
       </c>
       <c r="I6" t="n">
-        <v>9.237700737685373e-07</v>
+        <v>6.616119426210666e-17</v>
       </c>
       <c r="J6" t="n">
-        <v>7.182019601259526e-08</v>
+        <v>9.954182303622278e-17</v>
       </c>
       <c r="K6" t="n">
-        <v>3.364263818639301e-07</v>
+        <v>7.8778312494276e-17</v>
       </c>
       <c r="L6" t="n">
-        <v>1.467342798378013e-07</v>
+        <v>1.983759500450146e-16</v>
       </c>
       <c r="M6" t="n">
-        <v>5.017838020648924e-07</v>
+        <v>2.185327004465966e-16</v>
       </c>
       <c r="N6" t="n">
-        <v>7.516248956562777e-07</v>
+        <v>3.248384058214451e-16</v>
       </c>
       <c r="O6" t="n">
-        <v>1.346584440398146e-06</v>
+        <v>5.322940858398827e-16</v>
       </c>
       <c r="P6" t="n">
-        <v>7.513676791859325e-09</v>
+        <v>7.249599353245499e-16</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.380238476959676e-08</v>
+        <v>4.775845983536419e-16</v>
       </c>
       <c r="R6" t="n">
-        <v>2.77301381856887e-07</v>
+        <v>8.471751561452105e-17</v>
       </c>
       <c r="S6" t="n">
-        <v>2.892044790314685e-07</v>
+        <v>7.140553919802756e-19</v>
       </c>
       <c r="T6" t="n">
-        <v>2.185410465926907e-07</v>
+        <v>3.560339410545513e-16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.323088127946903e-07</v>
+        <v>9.408577280304751e-17</v>
       </c>
       <c r="V6" t="n">
-        <v>2.10505106679193e-08</v>
+        <v>1.328081222147943e-16</v>
       </c>
       <c r="W6" t="n">
-        <v>7.292451869034267e-07</v>
+        <v>5.331835763136181e-16</v>
       </c>
       <c r="X6" t="n">
-        <v>3.064679106046242e-07</v>
+        <v>1.599436300083636e-16</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.253258119504608e-08</v>
+        <v>1.138608686874424e-16</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.04005094828608e-07</v>
+        <v>3.316252573113201e-16</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.674334767671098e-08</v>
+        <v>3.269437657688497e-17</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.600483170084772e-08</v>
+        <v>1.606630835810214e-18</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.345416636577283e-07</v>
+        <v>2.22589300049675e-16</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.902481123281177e-07</v>
+        <v>2.729646390588238e-17</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.265610135054885e-07</v>
+        <v>1.408844622528558e-16</v>
       </c>
       <c r="AF6" t="n">
-        <v>5.191131435822172e-07</v>
+        <v>4.289651718790411e-16</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.36512249784937e-07</v>
+        <v>2.955320716980711e-16</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.510883849841775e-07</v>
+        <v>1.743349447753408e-16</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.205653342774895e-07</v>
+        <v>3.224731721953558e-16</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.952810405076889e-07</v>
+        <v>8.967333333533855e-17</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.206427893725049e-07</v>
+        <v>4.966176917218808e-18</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.314447217737325e-07</v>
+        <v>6.517371928173066e-17</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.986235472235421e-07</v>
+        <v>3.911098533330377e-18</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.825379159636213e-07</v>
+        <v>2.046738252963075e-16</v>
       </c>
       <c r="AO6" t="n">
-        <v>3.619350650296838e-07</v>
+        <v>2.83555581689267e-16</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.176080778961477e-07</v>
+        <v>3.303456204842292e-18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.035659688066517e-07</v>
+        <v>3.95591253194054e-17</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.338556323091325e-07</v>
+        <v>1.003594414408947e-17</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.054218981584199e-07</v>
+        <v>6.741193767040115e-17</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.154560891336587e-07</v>
+        <v>1.663390728672684e-17</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.314340445598646e-07</v>
+        <v>4.039503831224903e-16</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.905530547854141e-07</v>
+        <v>7.620376246854146e-17</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.913126071594888e-07</v>
+        <v>8.517565455986722e-17</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.342407524087321e-07</v>
+        <v>1.638038370816873e-16</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.097289653756889e-07</v>
+        <v>4.288041826795035e-16</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.209755737363594e-06</v>
+        <v>1.556239869704933e-16</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.523938059719512e-07</v>
+        <v>4.167952407209077e-16</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.446435456084146e-07</v>
+        <v>3.486596060413064e-17</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.548941384044156e-07</v>
+        <v>1.736346073466391e-17</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.308732345885801e-07</v>
+        <v>1.807999369801491e-16</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.887711272909655e-07</v>
+        <v>9.213319642350384e-17</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.512601670583535e-07</v>
+        <v>2.620811524242227e-16</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.117130409511446e-06</v>
+        <v>4.977533197130487e-17</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.78919343247253e-07</v>
+        <v>2.35464624364414e-16</v>
       </c>
       <c r="BI6" t="n">
-        <v>5.430385954241501e-07</v>
+        <v>7.107047811038438e-17</v>
       </c>
       <c r="BJ6" t="n">
-        <v>3.026654553650587e-07</v>
+        <v>4.042926109029606e-16</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.227713705200586e-07</v>
+        <v>4.305731183456155e-17</v>
       </c>
       <c r="BL6" t="n">
-        <v>2.014590307908293e-07</v>
+        <v>1.16172646593626e-16</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.32299512958889e-07</v>
+        <v>9.998476171063268e-17</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.155493288886646e-07</v>
+        <v>7.072778710877101e-17</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.798370246637205e-07</v>
+        <v>2.259412410325318e-18</v>
       </c>
       <c r="BP6" t="n">
-        <v>9.412184454049566e-08</v>
+        <v>1.566096421535217e-16</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.902207978967454e-08</v>
+        <v>5.639160889270417e-17</v>
       </c>
       <c r="BR6" t="n">
-        <v>5.716616442441591e-07</v>
+        <v>1.896139500710405e-17</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.623503322889519e-07</v>
+        <v>1.363849305928124e-16</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.218508931648103e-07</v>
+        <v>2.015450047031583e-16</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.47431322261582e-07</v>
+        <v>1.736458570029698e-17</v>
       </c>
       <c r="BV6" t="n">
-        <v>1.664733417783282e-07</v>
+        <v>1.908802775620755e-16</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.114623723377008e-07</v>
+        <v>1.11408192144439e-16</v>
       </c>
       <c r="BX6" t="n">
-        <v>1.259329422964584e-07</v>
+        <v>3.332662777675069e-16</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.399089104685117e-07</v>
+        <v>6.114492618212379e-16</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.193716627767571e-07</v>
+        <v>6.90023214382099e-17</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.679380711218982e-07</v>
+        <v>3.523459860719857e-17</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.784333676368988e-07</v>
+        <v>1.397133994986073e-16</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.06313671924363e-07</v>
+        <v>1.301036651282195e-16</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.424673415494908e-08</v>
+        <v>1.209037623554047e-17</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.802769986625208e-07</v>
+        <v>2.501720081521702e-18</v>
       </c>
       <c r="CF6" t="n">
-        <v>1.201469785883091e-07</v>
+        <v>5.713852651605995e-17</v>
       </c>
       <c r="CG6" t="n">
-        <v>1.114926817535888e-08</v>
+        <v>2.55979775581803e-17</v>
       </c>
       <c r="CH6" t="n">
-        <v>5.605875230685342e-08</v>
+        <v>2.153987579510945e-17</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.684955321934467e-07</v>
+        <v>7.598147587689131e-17</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.518773160569253e-07</v>
+        <v>6.002264723168124e-17</v>
       </c>
       <c r="CK6" t="n">
-        <v>6.989946399471592e-09</v>
+        <v>8.765886068491875e-18</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.184770113127342e-07</v>
+        <v>1.190503483876939e-16</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.473992767841992e-07</v>
+        <v>4.809682699847962e-17</v>
       </c>
       <c r="CN6" t="n">
-        <v>6.978722808526072e-07</v>
+        <v>3.144385617648364e-16</v>
       </c>
       <c r="CO6" t="n">
-        <v>9.248570620457031e-08</v>
+        <v>2.307745897005772e-17</v>
       </c>
       <c r="CP6" t="n">
-        <v>4.87065904053452e-07</v>
+        <v>4.010112052652974e-17</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.124418412880914e-07</v>
+        <v>3.787373621865023e-16</v>
       </c>
       <c r="CR6" t="n">
-        <v>3.223010196506948e-07</v>
+        <v>7.558168294323218e-17</v>
       </c>
       <c r="CS6" t="n">
-        <v>1.807746912163566e-07</v>
+        <v>3.541572072110114e-16</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.369039234257798e-07</v>
+        <v>1.400571889960742e-16</v>
       </c>
       <c r="CU6" t="n">
-        <v>7.175168548201327e-07</v>
+        <v>2.290497857745061e-17</v>
       </c>
       <c r="CV6" t="n">
-        <v>5.497622979078187e-08</v>
+        <v>4.643677807948165e-18</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.121124171277188e-07</v>
+        <v>3.761678281840023e-18</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.109823770661933e-07</v>
+        <v>3.384493517810948e-17</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.01948430142329e-07</v>
+        <v>4.14583882541088e-17</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.113287962401955e-07</v>
+        <v>5.694392069642828e-17</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.405041700763832e-07</v>
+        <v>1.309352132544068e-16</v>
       </c>
       <c r="DB6" t="n">
-        <v>4.717685442301445e-08</v>
+        <v>6.498455300180713e-17</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.608999238873366e-08</v>
+        <v>1.010324355872678e-17</v>
       </c>
       <c r="DD6" t="n">
-        <v>6.887403714017637e-08</v>
+        <v>7.559840522649555e-17</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.071904094374077e-07</v>
+        <v>1.305186583328149e-16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.100334401371583e-07</v>
+        <v>5.059103330218914e-16</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.414504933767603e-07</v>
+        <v>2.050114473351272e-16</v>
       </c>
       <c r="DH6" t="n">
-        <v>2.298186245752731e-07</v>
+        <v>1.536012590575602e-16</v>
       </c>
       <c r="DI6" t="n">
-        <v>3.495119074159447e-07</v>
+        <v>1.517815940588416e-16</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.186614781545359e-06</v>
+        <v>6.053473952878955e-16</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.561445964805898e-07</v>
+        <v>1.195271352927695e-16</v>
       </c>
       <c r="DL6" t="n">
-        <v>2.663747977749154e-07</v>
+        <v>2.521933066970047e-17</v>
       </c>
       <c r="DM6" t="n">
-        <v>9.768169775270508e-07</v>
+        <v>1.752062372756001e-16</v>
       </c>
       <c r="DN6" t="n">
-        <v>2.242050669565288e-07</v>
+        <v>1.681461382508967e-16</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.293798277401947e-07</v>
+        <v>6.9687147576065e-17</v>
       </c>
       <c r="DP6" t="n">
-        <v>3.033843398725367e-08</v>
+        <v>1.003700359701803e-16</v>
       </c>
       <c r="DQ6" t="n">
-        <v>5.922028378790856e-08</v>
+        <v>3.788626965929164e-16</v>
       </c>
       <c r="DR6" t="n">
-        <v>3.917245123830071e-07</v>
+        <v>2.085276994748615e-17</v>
       </c>
       <c r="DS6" t="n">
-        <v>1.619055183255114e-07</v>
+        <v>5.13473887254619e-17</v>
       </c>
       <c r="DT6" t="n">
-        <v>1.477439184327523e-07</v>
+        <v>2.1916380616675e-16</v>
       </c>
       <c r="DU6" t="n">
-        <v>1.012756598584019e-07</v>
+        <v>3.043402349676706e-16</v>
       </c>
       <c r="DV6" t="n">
-        <v>3.92211120470165e-07</v>
+        <v>6.454077391189488e-17</v>
       </c>
       <c r="DW6" t="n">
-        <v>1.530718236608664e-07</v>
+        <v>6.289764249078485e-17</v>
       </c>
       <c r="DX6" t="n">
-        <v>6.32881125284257e-08</v>
+        <v>3.058672500831129e-16</v>
       </c>
       <c r="DY6" t="n">
-        <v>3.029770709872537e-07</v>
+        <v>2.643878018106085e-17</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.157983030632749e-07</v>
+        <v>3.746516722956416e-16</v>
       </c>
       <c r="EA6" t="n">
-        <v>1.532791884528706e-07</v>
+        <v>7.94755661936541e-17</v>
       </c>
       <c r="EB6" t="n">
-        <v>3.503281220673671e-07</v>
+        <v>2.303152463802591e-16</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.696610496537687e-07</v>
+        <v>1.703671777526056e-17</v>
       </c>
       <c r="ED6" t="n">
-        <v>2.245079997464927e-07</v>
+        <v>6.863902371317661e-17</v>
       </c>
       <c r="EE6" t="n">
-        <v>5.993420870709087e-08</v>
+        <v>1.565458102800122e-16</v>
       </c>
       <c r="EF6" t="n">
-        <v>1.041766637399633e-07</v>
+        <v>7.556462317027889e-17</v>
       </c>
       <c r="EG6" t="n">
-        <v>4.170654577251298e-08</v>
+        <v>5.825011829298831e-17</v>
       </c>
       <c r="EH6" t="n">
-        <v>1.205314958951931e-08</v>
+        <v>3.048269414226519e-17</v>
       </c>
       <c r="EI6" t="n">
-        <v>6.90355307142454e-07</v>
+        <v>1.498636732382414e-16</v>
       </c>
       <c r="EJ6" t="n">
-        <v>6.348298597913526e-08</v>
+        <v>1.262896478203008e-16</v>
       </c>
       <c r="EK6" t="n">
-        <v>3.183773742421181e-07</v>
+        <v>9.929375984232425e-18</v>
       </c>
       <c r="EL6" t="n">
-        <v>6.351660317704955e-07</v>
+        <v>4.721300767502386e-17</v>
       </c>
       <c r="EM6" t="n">
-        <v>2.875034681437683e-07</v>
+        <v>1.0236839845099e-18</v>
       </c>
       <c r="EN6" t="n">
-        <v>8.13019198631082e-08</v>
+        <v>2.393790283114722e-16</v>
       </c>
       <c r="EO6" t="n">
-        <v>2.686990967504244e-07</v>
+        <v>8.09402846828038e-17</v>
       </c>
       <c r="EP6" t="n">
-        <v>3.373376955551066e-07</v>
+        <v>1.478979612305704e-16</v>
       </c>
       <c r="EQ6" t="n">
-        <v>1.048271585091243e-07</v>
+        <v>1.258610226792105e-17</v>
       </c>
       <c r="ER6" t="n">
-        <v>3.876363052768284e-07</v>
+        <v>8.801418769756948e-17</v>
       </c>
       <c r="ES6" t="n">
-        <v>1.396141442455701e-07</v>
+        <v>3.82719714057798e-16</v>
       </c>
       <c r="ET6" t="n">
-        <v>8.787206411398074e-07</v>
+        <v>5.289492453754041e-17</v>
       </c>
       <c r="EU6" t="n">
-        <v>3.136617010568443e-07</v>
+        <v>2.003802020517857e-18</v>
       </c>
       <c r="EV6" t="n">
-        <v>1.79036675262978e-07</v>
+        <v>3.563655875406259e-17</v>
       </c>
       <c r="EW6" t="n">
-        <v>4.317108448503859e-09</v>
+        <v>1.393501547131333e-18</v>
       </c>
       <c r="EX6" t="n">
-        <v>3.760415268061479e-08</v>
+        <v>1.025652591649715e-17</v>
       </c>
       <c r="EY6" t="n">
-        <v>1.395289643824071e-07</v>
+        <v>1.358116745759784e-17</v>
       </c>
       <c r="EZ6" t="n">
-        <v>5.379661160986871e-08</v>
+        <v>2.481495019236413e-17</v>
       </c>
       <c r="FA6" t="n">
-        <v>2.479983152170462e-08</v>
+        <v>1.106659795244074e-17</v>
       </c>
       <c r="FB6" t="n">
-        <v>2.775890663997416e-07</v>
+        <v>2.89058430492778e-17</v>
       </c>
       <c r="FC6" t="n">
-        <v>7.991904737991717e-08</v>
+        <v>8.607769832657874e-17</v>
       </c>
       <c r="FD6" t="n">
-        <v>1.597597076852253e-07</v>
+        <v>7.843209439453071e-17</v>
       </c>
       <c r="FE6" t="n">
-        <v>5.694981197734705e-08</v>
+        <v>2.068439071635608e-17</v>
       </c>
       <c r="FF6" t="n">
-        <v>2.292707961260021e-07</v>
+        <v>6.240120839179992e-17</v>
       </c>
       <c r="FG6" t="n">
-        <v>7.210717001271405e-08</v>
+        <v>2.664526629952226e-16</v>
       </c>
       <c r="FH6" t="n">
-        <v>2.307081459207438e-08</v>
+        <v>1.583990654290454e-16</v>
       </c>
       <c r="FI6" t="n">
-        <v>8.745341517624183e-08</v>
+        <v>8.413326140426259e-17</v>
       </c>
       <c r="FJ6" t="n">
-        <v>5.296637937135529e-07</v>
+        <v>8.382846850959395e-17</v>
       </c>
       <c r="FK6" t="n">
-        <v>3.624030284754554e-07</v>
+        <v>2.393183595766251e-16</v>
       </c>
       <c r="FL6" t="n">
-        <v>3.913103512331872e-07</v>
+        <v>3.945341825456602e-17</v>
       </c>
       <c r="FM6" t="n">
-        <v>4.137564246775582e-08</v>
+        <v>2.282665780833164e-17</v>
       </c>
       <c r="FN6" t="n">
-        <v>1.951144952272443e-07</v>
+        <v>3.005275543836218e-16</v>
       </c>
       <c r="FO6" t="n">
-        <v>7.234012855406036e-07</v>
+        <v>1.495126707258331e-16</v>
       </c>
       <c r="FP6" t="n">
-        <v>5.726196832256392e-07</v>
+        <v>1.708611038399733e-17</v>
       </c>
       <c r="FQ6" t="n">
-        <v>3.19253786074114e-07</v>
+        <v>1.403925875734073e-16</v>
       </c>
       <c r="FR6" t="n">
-        <v>3.082923569763807e-07</v>
+        <v>2.820542687298179e-16</v>
       </c>
       <c r="FS6" t="n">
-        <v>1.200880035412411e-07</v>
+        <v>2.953896113442548e-16</v>
       </c>
       <c r="FT6" t="n">
-        <v>7.871648222135263e-07</v>
+        <v>8.140133530390616e-17</v>
       </c>
       <c r="FU6" t="n">
-        <v>1.046596366904851e-06</v>
+        <v>7.923929694092936e-17</v>
       </c>
       <c r="FV6" t="n">
-        <v>4.079847713001072e-07</v>
+        <v>5.152379657161741e-16</v>
       </c>
       <c r="FW6" t="n">
-        <v>3.332657740884315e-07</v>
+        <v>1.308640095472782e-16</v>
       </c>
       <c r="FX6" t="n">
-        <v>4.560525042052177e-07</v>
+        <v>7.112675947926249e-17</v>
       </c>
       <c r="FY6" t="n">
-        <v>3.15342333578883e-07</v>
+        <v>5.892935930734746e-17</v>
       </c>
       <c r="FZ6" t="n">
-        <v>3.645234016858012e-07</v>
+        <v>2.512370859088934e-18</v>
       </c>
       <c r="GA6" t="n">
-        <v>3.299061290817917e-07</v>
+        <v>6.866316415217336e-17</v>
       </c>
       <c r="GB6" t="n">
-        <v>2.566396801739756e-07</v>
+        <v>2.1259060550293e-16</v>
       </c>
       <c r="GC6" t="n">
-        <v>2.806575878366857e-07</v>
+        <v>8.839691424083042e-17</v>
       </c>
       <c r="GD6" t="n">
-        <v>3.523401232996548e-07</v>
+        <v>2.15263881189134e-16</v>
       </c>
       <c r="GE6" t="n">
-        <v>3.00195040381368e-07</v>
+        <v>3.330098120729461e-17</v>
       </c>
       <c r="GF6" t="n">
-        <v>3.587207970667805e-07</v>
+        <v>2.379862414483901e-16</v>
       </c>
       <c r="GG6" t="n">
-        <v>9.752750429470325e-07</v>
+        <v>2.553644458502921e-16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3.887209629738209e-07</v>
+        <v>9.832574367561568e-28</v>
       </c>
       <c r="B7" t="n">
-        <v>2.315330448254826e-06</v>
+        <v>6.814158736290728e-28</v>
       </c>
       <c r="C7" t="n">
-        <v>3.523122984461224e-07</v>
+        <v>7.572006391617273e-28</v>
       </c>
       <c r="D7" t="n">
-        <v>6.033442900843511e-07</v>
+        <v>2.135575507739553e-27</v>
       </c>
       <c r="E7" t="n">
-        <v>5.739791220094048e-08</v>
+        <v>7.831859118986318e-28</v>
       </c>
       <c r="F7" t="n">
-        <v>6.643278993578861e-07</v>
+        <v>1.776440032475876e-27</v>
       </c>
       <c r="G7" t="n">
-        <v>2.712313573738356e-08</v>
+        <v>1.20910700428857e-28</v>
       </c>
       <c r="H7" t="n">
-        <v>3.086364017690357e-07</v>
+        <v>1.018634169829125e-27</v>
       </c>
       <c r="I7" t="n">
-        <v>1.124434220400872e-06</v>
+        <v>2.779070494839122e-27</v>
       </c>
       <c r="J7" t="n">
-        <v>4.193219353965105e-07</v>
+        <v>7.134971479742004e-28</v>
       </c>
       <c r="K7" t="n">
-        <v>1.27971543406602e-06</v>
+        <v>3.171399180101318e-27</v>
       </c>
       <c r="L7" t="n">
-        <v>2.07260086426686e-07</v>
+        <v>2.278297605529838e-28</v>
       </c>
       <c r="M7" t="n">
-        <v>1.080761649063788e-06</v>
+        <v>3.25079949391857e-27</v>
       </c>
       <c r="N7" t="n">
-        <v>4.02811508593004e-07</v>
+        <v>5.859824819142882e-28</v>
       </c>
       <c r="O7" t="n">
-        <v>2.588626557553653e-07</v>
+        <v>3.313367180021878e-27</v>
       </c>
       <c r="P7" t="n">
-        <v>2.804385417221056e-07</v>
+        <v>3.981669974438602e-28</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.352834798102776e-07</v>
+        <v>2.318709297256419e-27</v>
       </c>
       <c r="R7" t="n">
-        <v>8.181694397535466e-07</v>
+        <v>2.466570065027821e-27</v>
       </c>
       <c r="S7" t="n">
-        <v>1.091095782612683e-07</v>
+        <v>1.355100871868381e-27</v>
       </c>
       <c r="T7" t="n">
-        <v>2.614515324239619e-07</v>
+        <v>1.955160746118173e-27</v>
       </c>
       <c r="U7" t="n">
-        <v>3.957993754966083e-08</v>
+        <v>3.318214071616421e-28</v>
       </c>
       <c r="V7" t="n">
-        <v>4.359752665550332e-07</v>
+        <v>2.946018383917368e-27</v>
       </c>
       <c r="W7" t="n">
-        <v>8.543476042177645e-07</v>
+        <v>3.430628195057873e-27</v>
       </c>
       <c r="X7" t="n">
-        <v>8.302225751322112e-08</v>
+        <v>1.438936409754563e-27</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.796031008590944e-08</v>
+        <v>3.224083041878279e-28</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.071925267609913e-09</v>
+        <v>1.07930972605857e-27</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.873060722663467e-08</v>
+        <v>2.022115700634795e-28</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.308478279175688e-08</v>
+        <v>4.135824777564759e-28</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.668719218945625e-07</v>
+        <v>3.329706577077065e-29</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.535758992256888e-07</v>
+        <v>1.47402540889384e-27</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.805727206123265e-07</v>
+        <v>9.593810091601077e-28</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.964832705425579e-07</v>
+        <v>1.516877109415213e-28</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.789563258280396e-07</v>
+        <v>5.512933058314658e-28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.088395151782606e-09</v>
+        <v>3.899412062066365e-28</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.703859879853553e-07</v>
+        <v>1.517536692272917e-27</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.195430622326967e-07</v>
+        <v>4.253693134608716e-28</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.413016548212909e-07</v>
+        <v>2.451477900204619e-27</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.37285882778815e-07</v>
+        <v>1.704695097594569e-27</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.492849754924919e-08</v>
+        <v>5.2227647491735e-28</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.335985271884056e-08</v>
+        <v>2.003654699152872e-27</v>
       </c>
       <c r="AO7" t="n">
-        <v>3.17654155423952e-07</v>
+        <v>1.985164616128787e-27</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.749560045842372e-07</v>
+        <v>1.25174288028555e-28</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.334786917250312e-08</v>
+        <v>9.443340073941019e-29</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.278195717688504e-07</v>
+        <v>1.177985420834731e-27</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.805365457130392e-07</v>
+        <v>2.932549489147793e-28</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.026680192557251e-07</v>
+        <v>1.807500275060987e-27</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.698077085166005e-06</v>
+        <v>3.25482815417624e-27</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.757650522904441e-07</v>
+        <v>1.012779150205194e-27</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.025791718234359e-07</v>
+        <v>9.462982633443824e-28</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.247120379361149e-07</v>
+        <v>1.036696696405556e-27</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.333449841302354e-07</v>
+        <v>2.062747766895262e-28</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.216871047901805e-07</v>
+        <v>5.23870856021811e-28</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.733729497274908e-07</v>
+        <v>6.631117872893679e-28</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.454408125160626e-08</v>
+        <v>4.637106786454841e-28</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.010071811919261e-08</v>
+        <v>9.744127960795529e-28</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.979609341011383e-08</v>
+        <v>2.390607921347288e-27</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.10505240513703e-08</v>
+        <v>2.318374522483835e-28</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.482222036334861e-07</v>
+        <v>1.406112207933388e-27</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.198797907723929e-07</v>
+        <v>1.264446193828107e-28</v>
       </c>
       <c r="BH7" t="n">
-        <v>1.497601971323093e-07</v>
+        <v>8.847061570544037e-28</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.958801204044903e-09</v>
+        <v>1.129587764297252e-27</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.4686781923956e-07</v>
+        <v>8.63380431076701e-28</v>
       </c>
       <c r="BK7" t="n">
-        <v>8.406818210460187e-07</v>
+        <v>2.655586077929083e-28</v>
       </c>
       <c r="BL7" t="n">
-        <v>2.283073570197303e-07</v>
+        <v>2.705455289388819e-27</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.365384581068611e-08</v>
+        <v>1.988113407466639e-27</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.337173441446794e-07</v>
+        <v>2.275160747132918e-28</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.296489919397573e-08</v>
+        <v>2.269593846628666e-28</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.591369927060441e-07</v>
+        <v>1.624144040635545e-27</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.476652329301942e-07</v>
+        <v>1.257853543035475e-27</v>
       </c>
       <c r="BR7" t="n">
-        <v>8.427532804944349e-08</v>
+        <v>2.155640616272157e-27</v>
       </c>
       <c r="BS7" t="n">
-        <v>3.255162539517187e-07</v>
+        <v>1.68506857145855e-28</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.535952851687398e-08</v>
+        <v>1.430530688512285e-28</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.888815942014844e-08</v>
+        <v>1.610357945204129e-27</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.036779147209018e-07</v>
+        <v>4.476685007289648e-28</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.282191928770771e-07</v>
+        <v>1.206693139992773e-27</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.245359726453898e-07</v>
+        <v>2.035114379608448e-27</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.801197413442424e-09</v>
+        <v>1.848607516386983e-27</v>
       </c>
       <c r="BZ7" t="n">
-        <v>9.047252547134121e-08</v>
+        <v>1.567458626064881e-27</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.260694256823626e-07</v>
+        <v>4.880963221188292e-28</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.058101694681682e-07</v>
+        <v>6.606871859341302e-28</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.433658951555117e-07</v>
+        <v>1.468869020357235e-27</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.843814321337959e-08</v>
+        <v>2.052586993842912e-27</v>
       </c>
       <c r="CE7" t="n">
-        <v>3.802961145993322e-07</v>
+        <v>1.247338278502737e-28</v>
       </c>
       <c r="CF7" t="n">
-        <v>5.637375011247059e-08</v>
+        <v>6.220958350427363e-29</v>
       </c>
       <c r="CG7" t="n">
-        <v>7.694780634892595e-08</v>
+        <v>1.112508424957431e-27</v>
       </c>
       <c r="CH7" t="n">
-        <v>3.8248362699278e-08</v>
+        <v>1.957206143904423e-29</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.333637283413736e-09</v>
+        <v>5.203725487225774e-28</v>
       </c>
       <c r="CJ7" t="n">
-        <v>5.178289441687411e-08</v>
+        <v>4.793445112655447e-28</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.806581622076919e-07</v>
+        <v>1.841876583824344e-28</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.013152169411114e-07</v>
+        <v>9.675306780162795e-28</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.715771418275835e-07</v>
+        <v>1.839637305078005e-27</v>
       </c>
       <c r="CN7" t="n">
-        <v>3.431535944287134e-08</v>
+        <v>7.850311453783492e-28</v>
       </c>
       <c r="CO7" t="n">
-        <v>9.071649031966444e-08</v>
+        <v>4.180336870439437e-28</v>
       </c>
       <c r="CP7" t="n">
-        <v>3.769062217884311e-08</v>
+        <v>3.05775202816122e-28</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.707300836846116e-07</v>
+        <v>8.90246287132428e-28</v>
       </c>
       <c r="CR7" t="n">
-        <v>5.697131655324483e-09</v>
+        <v>2.753613263944719e-28</v>
       </c>
       <c r="CS7" t="n">
-        <v>4.633448611457425e-07</v>
+        <v>7.397483434881762e-28</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.653558226484165e-07</v>
+        <v>2.415110950250744e-27</v>
       </c>
       <c r="CU7" t="n">
-        <v>4.795608532504048e-08</v>
+        <v>4.54326007212474e-28</v>
       </c>
       <c r="CV7" t="n">
-        <v>5.718214168837221e-08</v>
+        <v>2.084200170915057e-27</v>
       </c>
       <c r="CW7" t="n">
-        <v>3.999917339569947e-07</v>
+        <v>9.074995138721023e-29</v>
       </c>
       <c r="CX7" t="n">
-        <v>4.76402348681404e-08</v>
+        <v>3.107458594837153e-28</v>
       </c>
       <c r="CY7" t="n">
-        <v>9.447197157896881e-08</v>
+        <v>1.041278483743253e-27</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.257912458640931e-07</v>
+        <v>7.39962025415506e-29</v>
       </c>
       <c r="DA7" t="n">
-        <v>4.215691262743348e-08</v>
+        <v>3.949603722347041e-28</v>
       </c>
       <c r="DB7" t="n">
-        <v>8.886399172070014e-09</v>
+        <v>2.911584056514437e-28</v>
       </c>
       <c r="DC7" t="n">
-        <v>9.167392533981911e-08</v>
+        <v>6.830565733486963e-29</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.038690200516612e-07</v>
+        <v>8.595539934631925e-28</v>
       </c>
       <c r="DE7" t="n">
-        <v>5.077560558675032e-07</v>
+        <v>1.559121660521618e-27</v>
       </c>
       <c r="DF7" t="n">
-        <v>4.213873978642368e-07</v>
+        <v>1.318317921046518e-27</v>
       </c>
       <c r="DG7" t="n">
-        <v>4.837211236008443e-07</v>
+        <v>3.80121683866308e-28</v>
       </c>
       <c r="DH7" t="n">
-        <v>7.585470029880526e-07</v>
+        <v>1.831483302879458e-28</v>
       </c>
       <c r="DI7" t="n">
-        <v>8.822326549307036e-07</v>
+        <v>1.078992621693227e-28</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.704242945128499e-07</v>
+        <v>1.359335221444111e-27</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.838362599457469e-08</v>
+        <v>7.814525749486833e-28</v>
       </c>
       <c r="DL7" t="n">
-        <v>8.340524004779581e-08</v>
+        <v>5.316713537790654e-28</v>
       </c>
       <c r="DM7" t="n">
-        <v>5.106883804728568e-09</v>
+        <v>6.714436491182788e-28</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.825279980494088e-07</v>
+        <v>6.650998766227103e-28</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.63829554367112e-08</v>
+        <v>2.260688828048306e-28</v>
       </c>
       <c r="DP7" t="n">
-        <v>5.36924247285242e-08</v>
+        <v>9.698585495400604e-28</v>
       </c>
       <c r="DQ7" t="n">
-        <v>2.560997813816357e-08</v>
+        <v>1.650242702497925e-27</v>
       </c>
       <c r="DR7" t="n">
-        <v>1.40087379918441e-07</v>
+        <v>2.592050852769963e-28</v>
       </c>
       <c r="DS7" t="n">
-        <v>3.255753426856245e-07</v>
+        <v>9.423554032657357e-28</v>
       </c>
       <c r="DT7" t="n">
-        <v>2.241693835003389e-07</v>
+        <v>7.310087622900386e-28</v>
       </c>
       <c r="DU7" t="n">
-        <v>1.13386725786313e-07</v>
+        <v>1.143913553447333e-28</v>
       </c>
       <c r="DV7" t="n">
-        <v>8.780494908933179e-08</v>
+        <v>1.052762033629656e-27</v>
       </c>
       <c r="DW7" t="n">
-        <v>2.436649637616028e-08</v>
+        <v>1.367920920839692e-27</v>
       </c>
       <c r="DX7" t="n">
-        <v>2.84047246168484e-07</v>
+        <v>4.267548274628638e-28</v>
       </c>
       <c r="DY7" t="n">
-        <v>1.886638401060736e-08</v>
+        <v>1.135611013901826e-27</v>
       </c>
       <c r="DZ7" t="n">
-        <v>9.842377579616368e-08</v>
+        <v>5.327409911960537e-29</v>
       </c>
       <c r="EA7" t="n">
-        <v>1.548925467886875e-07</v>
+        <v>2.794296367348712e-28</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.106251090732258e-08</v>
+        <v>1.554666503077764e-27</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.651598490250763e-08</v>
+        <v>1.87446351107637e-27</v>
       </c>
       <c r="ED7" t="n">
-        <v>2.216637682295186e-07</v>
+        <v>9.401140059964578e-28</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.868152850192928e-07</v>
+        <v>1.32319909419407e-27</v>
       </c>
       <c r="EF7" t="n">
-        <v>7.788653988427541e-08</v>
+        <v>2.714471337830474e-27</v>
       </c>
       <c r="EG7" t="n">
-        <v>3.272616595495492e-07</v>
+        <v>6.947931422815435e-28</v>
       </c>
       <c r="EH7" t="n">
-        <v>3.713034146812788e-08</v>
+        <v>6.214662966921647e-29</v>
       </c>
       <c r="EI7" t="n">
-        <v>1.338130317662944e-07</v>
+        <v>1.618866222215946e-27</v>
       </c>
       <c r="EJ7" t="n">
-        <v>1.446065880372771e-07</v>
+        <v>8.258287453175359e-28</v>
       </c>
       <c r="EK7" t="n">
-        <v>3.245343904723086e-08</v>
+        <v>4.234810354468971e-28</v>
       </c>
       <c r="EL7" t="n">
-        <v>9.828691815982893e-08</v>
+        <v>1.015038506771203e-28</v>
       </c>
       <c r="EM7" t="n">
-        <v>2.607028193324368e-07</v>
+        <v>5.393386855177275e-29</v>
       </c>
       <c r="EN7" t="n">
-        <v>1.101495570310362e-07</v>
+        <v>1.234692887303258e-27</v>
       </c>
       <c r="EO7" t="n">
-        <v>1.886337344103595e-07</v>
+        <v>1.962370464864987e-27</v>
       </c>
       <c r="EP7" t="n">
-        <v>6.589188501493481e-07</v>
+        <v>4.858169840296469e-28</v>
       </c>
       <c r="EQ7" t="n">
-        <v>2.112941217546904e-07</v>
+        <v>6.140921035281004e-28</v>
       </c>
       <c r="ER7" t="n">
-        <v>7.95246322127241e-08</v>
+        <v>8.489147712644085e-29</v>
       </c>
       <c r="ES7" t="n">
-        <v>1.151464203985597e-07</v>
+        <v>8.055525548630271e-28</v>
       </c>
       <c r="ET7" t="n">
-        <v>5.851014179825142e-07</v>
+        <v>1.634519603024942e-27</v>
       </c>
       <c r="EU7" t="n">
-        <v>2.925496858097176e-07</v>
+        <v>1.462412821701163e-27</v>
       </c>
       <c r="EV7" t="n">
-        <v>2.67475712689702e-07</v>
+        <v>1.026264030193307e-27</v>
       </c>
       <c r="EW7" t="n">
-        <v>2.125102867012174e-07</v>
+        <v>4.373144606066959e-28</v>
       </c>
       <c r="EX7" t="n">
-        <v>6.659741202952318e-09</v>
+        <v>2.316050165782203e-27</v>
       </c>
       <c r="EY7" t="n">
-        <v>4.922389962302987e-07</v>
+        <v>2.458566574254428e-28</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1.957774600214179e-07</v>
+        <v>1.019811322285259e-28</v>
       </c>
       <c r="FA7" t="n">
-        <v>6.239852723410877e-08</v>
+        <v>9.274540981000228e-28</v>
       </c>
       <c r="FB7" t="n">
-        <v>7.937092050269712e-08</v>
+        <v>1.304662259220586e-28</v>
       </c>
       <c r="FC7" t="n">
-        <v>8.371129922579712e-08</v>
+        <v>6.609345234872382e-28</v>
       </c>
       <c r="FD7" t="n">
-        <v>6.734875768188431e-09</v>
+        <v>5.846854643932406e-28</v>
       </c>
       <c r="FE7" t="n">
-        <v>1.443797970068772e-07</v>
+        <v>3.090192873626965e-28</v>
       </c>
       <c r="FF7" t="n">
-        <v>4.581356449762097e-08</v>
+        <v>8.934020196428037e-28</v>
       </c>
       <c r="FG7" t="n">
-        <v>1.474778343890648e-07</v>
+        <v>2.56263082842199e-27</v>
       </c>
       <c r="FH7" t="n">
-        <v>4.301562910313805e-07</v>
+        <v>5.623349029438809e-28</v>
       </c>
       <c r="FI7" t="n">
-        <v>1.280567687445e-07</v>
+        <v>1.057098168602947e-27</v>
       </c>
       <c r="FJ7" t="n">
-        <v>3.772630918774666e-08</v>
+        <v>4.10333385792046e-28</v>
       </c>
       <c r="FK7" t="n">
-        <v>1.654223922287201e-07</v>
+        <v>5.148144954590081e-29</v>
       </c>
       <c r="FL7" t="n">
-        <v>2.364076294725237e-07</v>
+        <v>1.604001124533187e-27</v>
       </c>
       <c r="FM7" t="n">
-        <v>9.80527232741224e-08</v>
+        <v>1.620712033474647e-27</v>
       </c>
       <c r="FN7" t="n">
-        <v>4.461921321308182e-08</v>
+        <v>4.715940876868444e-28</v>
       </c>
       <c r="FO7" t="n">
-        <v>3.534549080086435e-07</v>
+        <v>1.227231256919718e-27</v>
       </c>
       <c r="FP7" t="n">
-        <v>1.087030057078664e-07</v>
+        <v>4.306546911555021e-28</v>
       </c>
       <c r="FQ7" t="n">
-        <v>1.102474470826564e-06</v>
+        <v>5.454657307092417e-28</v>
       </c>
       <c r="FR7" t="n">
-        <v>5.305274797251514e-08</v>
+        <v>8.613595527860555e-28</v>
       </c>
       <c r="FS7" t="n">
-        <v>1.407374128348238e-08</v>
+        <v>6.371051367300807e-28</v>
       </c>
       <c r="FT7" t="n">
-        <v>8.69114444412844e-07</v>
+        <v>1.660552398083224e-27</v>
       </c>
       <c r="FU7" t="n">
-        <v>1.875681761021042e-07</v>
+        <v>1.495583690912327e-27</v>
       </c>
       <c r="FV7" t="n">
-        <v>3.142299362934864e-07</v>
+        <v>2.007115113780449e-28</v>
       </c>
       <c r="FW7" t="n">
-        <v>1.362311934371974e-07</v>
+        <v>1.157259044255722e-27</v>
       </c>
       <c r="FX7" t="n">
-        <v>3.600960951644083e-07</v>
+        <v>6.192947625316195e-28</v>
       </c>
       <c r="FY7" t="n">
-        <v>2.926927891166997e-07</v>
+        <v>6.864637360133118e-28</v>
       </c>
       <c r="FZ7" t="n">
-        <v>3.717861147833901e-07</v>
+        <v>1.353310527392079e-27</v>
       </c>
       <c r="GA7" t="n">
-        <v>3.718093566362768e-08</v>
+        <v>6.182211528841208e-28</v>
       </c>
       <c r="GB7" t="n">
-        <v>1.720542144312276e-07</v>
+        <v>1.39052190133007e-28</v>
       </c>
       <c r="GC7" t="n">
-        <v>7.753134241283988e-07</v>
+        <v>2.274921931819814e-28</v>
       </c>
       <c r="GD7" t="n">
-        <v>2.634722022776259e-07</v>
+        <v>9.038235154613747e-28</v>
       </c>
       <c r="GE7" t="n">
-        <v>1.852267530466634e-07</v>
+        <v>1.867388992611653e-27</v>
       </c>
       <c r="GF7" t="n">
-        <v>8.399109674428473e-08</v>
+        <v>2.912309169138499e-28</v>
       </c>
       <c r="GG7" t="n">
-        <v>2.413865161088324e-07</v>
+        <v>1.98616051450303e-27</v>
       </c>
     </row>
     <row r="8">
@@ -4982,5123 +4982,5123 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0006512075779028237</v>
+        <v>3.628965350799263e-05</v>
       </c>
       <c r="B9" t="n">
-        <v>0.005317140836268663</v>
+        <v>0.001155665842816234</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0003693675971589983</v>
+        <v>0.00028539530467242</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004718473646789789</v>
+        <v>0.0007582824910059571</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002968274988234043</v>
+        <v>0.000104950086097233</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001759112812578678</v>
+        <v>0.0005675902357324958</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0005268803797662258</v>
+        <v>0.0003520765458233654</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002277616295032203</v>
+        <v>0.0003038501599803567</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001683470327407122</v>
+        <v>3.852152531180764e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001066432800143957</v>
+        <v>0.0001115251652663574</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00417618453502655</v>
+        <v>0.001187075977213681</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001735893019940704</v>
+        <v>0.0004604747809935361</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00353641202673316</v>
+        <v>0.001157726161181927</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003348757745698094</v>
+        <v>0.0003036376729141921</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002333198674023151</v>
+        <v>0.000455571775091812</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001037425361573696</v>
+        <v>0.0004173425550106913</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0005592547822743654</v>
+        <v>8.779994095675647e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001544812577776611</v>
+        <v>1.942462404258549e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0002453179622534662</v>
+        <v>8.103032087092288e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0004799829912371933</v>
+        <v>7.991363236214966e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0004502465890254825</v>
+        <v>0.000123931240523234</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001518726348876953</v>
+        <v>9.188931289827451e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002501139417290688</v>
+        <v>0.000245279778027907</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0004529670695774257</v>
+        <v>0.0001791961403796449</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001185848843306303</v>
+        <v>0.0001303864701185375</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001148523995652795</v>
+        <v>0.0001724127650959417</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001042815507389605</v>
+        <v>0.0002052916534012184</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0007121103117242455</v>
+        <v>2.541823414503597e-05</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0003130733966827393</v>
+        <v>0.0001704410824459046</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0005574298556894064</v>
+        <v>0.0001806460204534233</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0007845967775210738</v>
+        <v>0.0001950807200046256</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001378012006171048</v>
+        <v>1.091961348720361e-05</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.00153528549708426</v>
+        <v>0.0003255139745306224</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0003908709622919559</v>
+        <v>5.941529161646031e-05</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0003556936571840197</v>
+        <v>0.0002442912082187831</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.000457148824352771</v>
+        <v>1.64469238370657e-05</v>
       </c>
       <c r="AK9" t="n">
-        <v>6.512441905215383e-05</v>
+        <v>5.721099296351895e-05</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0006140697514638305</v>
+        <v>0.0003131082048639655</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0003461820015218109</v>
+        <v>0.0002718151081353426</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.889574534492567e-05</v>
+        <v>0.0002910559123847634</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001301411539316177</v>
+        <v>7.030109554762021e-05</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0006529064849019051</v>
+        <v>0.0001525167172076181</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0001817268057493493</v>
+        <v>3.342359559610486e-05</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0004656121891457587</v>
+        <v>2.641084756760392e-05</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.001191844115965068</v>
+        <v>6.405798558262177e-08</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0005614012479782104</v>
+        <v>2.019858402491082e-05</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.002150889253243804</v>
+        <v>0.0008163814200088382</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.000490246107801795</v>
+        <v>0.0001603497512405738</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001964777708053589</v>
+        <v>0.0004146920400671661</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.002089235233142972</v>
+        <v>0.0007064539822749794</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.002329185605049133</v>
+        <v>0.0002723432262428105</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.001105255680158734</v>
+        <v>4.768232611240819e-05</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.001760349958203733</v>
+        <v>4.193971835775301e-05</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.001283469144254923</v>
+        <v>8.233675907831639e-05</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001096403691917658</v>
+        <v>6.884311005705968e-05</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0009568204404786229</v>
+        <v>8.04034061729908e-05</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001154001103714108</v>
+        <v>0.0001784980704542249</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0007535754702985287</v>
+        <v>0.000169922539498657</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001445222413167357</v>
+        <v>0.0004536212945822626</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.0004899103660136461</v>
+        <v>0.0002097382093779743</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001432474004104733</v>
+        <v>5.331500142347068e-05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.00030024244915694</v>
+        <v>0.0002872280892916024</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0009584336075931787</v>
+        <v>0.0001024348166538402</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0006218990311026573</v>
+        <v>6.296625360846519e-05</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0002315830352017656</v>
+        <v>2.791822589642834e-05</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0004743939207401127</v>
+        <v>6.704737461404875e-05</v>
       </c>
       <c r="BO9" t="n">
-        <v>9.914743714034557e-05</v>
+        <v>8.082884596660733e-05</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0001314244436798617</v>
+        <v>7.1647074946668e-05</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0005168041680008173</v>
+        <v>7.314809772651643e-05</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0002589107607491314</v>
+        <v>0.0001514435280114412</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0006083599291741848</v>
+        <v>4.477421316551045e-05</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0002467186423018575</v>
+        <v>9.181076165987179e-05</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0004378681187517941</v>
+        <v>8.840662303555291e-06</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.001512240269221365</v>
+        <v>0.0005040513351559639</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0004206711892038584</v>
+        <v>0.0002635501441545784</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.002173557179048657</v>
+        <v>0.000614400370977819</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.001998206367716193</v>
+        <v>0.0001453926088288426</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0004330850497353822</v>
+        <v>0.0001839067263063043</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0004853187710978091</v>
+        <v>0.0001121834793593735</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.001211583032272756</v>
+        <v>5.759779378422536e-05</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.00140829652082175</v>
+        <v>0.0001244293234776706</v>
       </c>
       <c r="CD9" t="n">
-        <v>9.823198342928663e-05</v>
+        <v>7.191306940512732e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0008282314520329237</v>
+        <v>0.0003583938523661345</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0006525097996927798</v>
+        <v>6.683175888611004e-05</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0007600377430208027</v>
+        <v>0.0002757241600193083</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0004986735293641686</v>
+        <v>1.776308272383176e-05</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0002970092464238405</v>
+        <v>7.453573925886303e-05</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.00017558217223268</v>
+        <v>3.46968590747565e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>6.584226503036916e-05</v>
+        <v>1.789837551768869e-05</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0003004223690368235</v>
+        <v>1.606340083526447e-05</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0006440261495299637</v>
+        <v>0.0002241308684460819</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.001045005046762526</v>
+        <v>0.0004153867776039988</v>
       </c>
       <c r="CO9" t="n">
-        <v>8.581403380958363e-05</v>
+        <v>0.0004043807275593281</v>
       </c>
       <c r="CP9" t="n">
-        <v>4.600382089847699e-05</v>
+        <v>0.0004559483495540917</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.000690838904120028</v>
+        <v>0.0001130347227444872</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0009057614952325821</v>
+        <v>2.88714418275049e-05</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.001083614537492394</v>
+        <v>0.0001376555737806484</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.001682557049207389</v>
+        <v>0.0002188061189372092</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0004714973038062453</v>
+        <v>5.140705252415501e-05</v>
       </c>
       <c r="CV9" t="n">
-        <v>4.74790831503924e-05</v>
+        <v>8.358829654753208e-05</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0008532745414413512</v>
+        <v>0.0003426629700697958</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0005855370545759797</v>
+        <v>9.153487917501479e-05</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0008117466350086033</v>
+        <v>0.0002893750206567347</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0005019387463107705</v>
+        <v>4.827708835364319e-05</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0003340294933877885</v>
+        <v>9.331255569122732e-05</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0002918751270044595</v>
+        <v>4.146759965806268e-05</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0001565915299579501</v>
+        <v>4.034325320390053e-05</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0002806236443575472</v>
+        <v>1.363773662887979e-05</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0002298519393661991</v>
+        <v>0.00020278335432522</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.001032380270771682</v>
+        <v>0.000171208186657168</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0003260562370996922</v>
+        <v>0.0002112424408551306</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.002979034557938576</v>
+        <v>0.000236268388107419</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0007504353416152298</v>
+        <v>1.158743816631613e-05</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.00112054031342268</v>
+        <v>0.0005701732588931918</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0001225023588631302</v>
+        <v>9.079481060325634e-06</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0003889749059453607</v>
+        <v>0.0005262130289338529</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0004538687062449753</v>
+        <v>7.256288517965004e-05</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0001676344982115552</v>
+        <v>8.179479482350871e-05</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0005945259472355247</v>
+        <v>0.0001996469945879653</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0002262795460410416</v>
+        <v>4.570612509269267e-05</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.000800914189312607</v>
+        <v>0.0002100249985232949</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0001348202058579773</v>
+        <v>1.383880407956894e-05</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0005945572629570961</v>
+        <v>9.827866597333923e-05</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0003654505708254874</v>
+        <v>0.0001061061921063811</v>
       </c>
       <c r="DU9" t="n">
-        <v>3.770742296183016e-06</v>
+        <v>0.0002751619322225451</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.001196440425701439</v>
+        <v>0.0003249672299716622</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0004709769273176789</v>
+        <v>3.144583752145991e-05</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0002744577650446445</v>
+        <v>1.609931678103749e-05</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0004440620832610875</v>
+        <v>0.0001670059864409268</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0008987128967419267</v>
+        <v>0.0002983261074405164</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001027771388180554</v>
+        <v>8.802133379504085e-05</v>
       </c>
       <c r="EB9" t="n">
-        <v>6.384820881066844e-05</v>
+        <v>0.0002919930848293006</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0004895346355624497</v>
+        <v>8.982986400951631e-06</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0001156118596554734</v>
+        <v>0.0005669305101037025</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0002945471205748618</v>
+        <v>0.0003389857884030789</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0004067406116519123</v>
+        <v>0.0001992743200389668</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0002048835303867236</v>
+        <v>0.0001799294259399176</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0006816113600507379</v>
+        <v>0.0001362229231745005</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0001961294037755579</v>
+        <v>0.000183167343493551</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0009884771425276995</v>
+        <v>6.502035830635577e-06</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.000362158811185509</v>
+        <v>4.842019188799895e-05</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0003282413817942142</v>
+        <v>2.400220000708941e-05</v>
       </c>
       <c r="EM9" t="n">
-        <v>8.975847595138475e-05</v>
+        <v>3.179927807650529e-05</v>
       </c>
       <c r="EN9" t="n">
-        <v>3.315089270472527e-05</v>
+        <v>1.876131318567786e-05</v>
       </c>
       <c r="EO9" t="n">
-        <v>3.088396624661982e-06</v>
+        <v>8.152030204655603e-05</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0007543032406829298</v>
+        <v>0.0003174972953274846</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0003911229141522199</v>
+        <v>0.0001020123745547608</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0001485457760281861</v>
+        <v>5.629350198432803e-05</v>
       </c>
       <c r="ES9" t="n">
-        <v>1.761190651450306e-05</v>
+        <v>2.17561155295698e-05</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0018222585786134</v>
+        <v>2.119230885000434e-05</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001244345679879189</v>
+        <v>0.0001428039977326989</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0006717739161103964</v>
+        <v>0.0001044820019160397</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0001177300291601568</v>
+        <v>0.0002622361353132874</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0002003542322199792</v>
+        <v>7.841606566216797e-05</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0006659762584604323</v>
+        <v>0.0003857913543470204</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0004330913652665913</v>
+        <v>6.041115921107121e-05</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0009912218665704131</v>
+        <v>0.000330247130477801</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0003946488432120532</v>
+        <v>2.511377942937543e-06</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0003738651284947991</v>
+        <v>7.812793046468869e-05</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0004029172705486417</v>
+        <v>8.320466440636665e-05</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0002305373200215399</v>
+        <v>9.262258390663192e-05</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0006178484763950109</v>
+        <v>5.370232611312531e-05</v>
       </c>
       <c r="FG9" t="n">
-        <v>5.379799767979421e-05</v>
+        <v>3.754180943360552e-05</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0002395112678641453</v>
+        <v>0.0002257326705148444</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0001520969090051949</v>
+        <v>2.708307692955714e-05</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0003741365508176386</v>
+        <v>0.0001111951132770628</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.001161472173407674</v>
+        <v>8.543290277884807e-06</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0003318012459203601</v>
+        <v>2.491210034349933e-05</v>
       </c>
       <c r="FM9" t="n">
-        <v>6.382644642144442e-05</v>
+        <v>0.0001184012071462348</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0004004788352176547</v>
+        <v>8.029428863665089e-05</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.000105117738712579</v>
+        <v>8.768516272539273e-05</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0006595187587663531</v>
+        <v>0.0002461526019033045</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0007639754330739379</v>
+        <v>0.0006003605667501688</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0009276457712985575</v>
+        <v>0.0002287860843352973</v>
       </c>
       <c r="FS9" t="n">
-        <v>2.076791133731604e-05</v>
+        <v>0.0004240762791596353</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.000351494294591248</v>
+        <v>0.0001469044800614938</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0005283195059746504</v>
+        <v>8.157432603184134e-05</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0004888145485892892</v>
+        <v>8.308160613523796e-05</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0002304695663042367</v>
+        <v>0.0002468210877850652</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0002035351644735783</v>
+        <v>0.0003228044952265918</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.000962808495387435</v>
+        <v>3.193570591975003e-06</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0002567066985648125</v>
+        <v>2.786247205222026e-05</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0007662284187972546</v>
+        <v>2.210329330409877e-05</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0001176474906969815</v>
+        <v>0.0002833711623679847</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.001317539252340794</v>
+        <v>0.000253560981946066</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0005642649484798312</v>
+        <v>0.0001151570759247988</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.002702484140172601</v>
+        <v>0.0003259808872826397</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0006377914687618613</v>
+        <v>6.847733311587945e-05</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0002861536631826311</v>
+        <v>0.0001365584030281752</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.01261211186647415</v>
+        <v>0.001368208089843392</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02086189948022366</v>
+        <v>0.004947705660015345</v>
       </c>
       <c r="C10" t="n">
-        <v>0.005579558201134205</v>
+        <v>0.004066979512572289</v>
       </c>
       <c r="D10" t="n">
-        <v>0.009372102096676826</v>
+        <v>0.01926781609654427</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01700983755290508</v>
+        <v>0.004109750501811504</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0169663168489933</v>
+        <v>0.002454438246786594</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001231450471095741</v>
+        <v>0.002133007161319256</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00921245664358139</v>
+        <v>0.009952994994819164</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001458343933336437</v>
+        <v>0.001151618780568242</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01375800743699074</v>
+        <v>0.003929692320525646</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02015603147447109</v>
+        <v>0.0002111038193106651</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003394978120923042</v>
+        <v>0.005022736731916666</v>
       </c>
       <c r="M10" t="n">
-        <v>0.003421136178076267</v>
+        <v>0.03118011727929115</v>
       </c>
       <c r="N10" t="n">
-        <v>0.005181808024644852</v>
+        <v>0.01322106551378965</v>
       </c>
       <c r="O10" t="n">
-        <v>0.007416102103888988</v>
+        <v>0.0033987732604146</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005298207979649305</v>
+        <v>0.006006492301821709</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01064077951014042</v>
+        <v>0.01355094090104103</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001538942684419453</v>
+        <v>0.0007132592727430165</v>
       </c>
       <c r="S10" t="n">
-        <v>0.003538226243108511</v>
+        <v>0.0008243580814450979</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0006516468711197376</v>
+        <v>0.005430577322840691</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0005258283345028758</v>
+        <v>0.0008326339302584529</v>
       </c>
       <c r="V10" t="n">
-        <v>0.005418590735644102</v>
+        <v>0.01264704670757055</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01064282841980457</v>
+        <v>0.01462698262184858</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0004799099115189165</v>
+        <v>0.003693113103508949</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.005394387990236282</v>
+        <v>0.00401195976883173</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0007034171721898019</v>
+        <v>0.01475364435464144</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0004427664680406451</v>
+        <v>0.003160366322845221</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.004401856567710638</v>
+        <v>0.00327783590182662</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.001626859069801867</v>
+        <v>0.004433430265635252</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0007457607425749302</v>
+        <v>0.0006838227855041623</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0009809683542698622</v>
+        <v>0.0005001339595764875</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.001694524195045233</v>
+        <v>0.0006117394659668207</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.006105479784309864</v>
+        <v>0.001728331670165062</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.001004792982712388</v>
+        <v>0.0001729303039610386</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.006167308893054724</v>
+        <v>0.0001185656292364001</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.001560391159728169</v>
+        <v>0.004524230491369963</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.001913659740239382</v>
+        <v>0.002672013361006975</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0008657005382701755</v>
+        <v>0.007897681556642056</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.001638478832319379</v>
+        <v>0.0007904445519670844</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.001251121866516769</v>
+        <v>0.009019193239510059</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.003300145268440247</v>
+        <v>0.001238235970959067</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.006428420078009367</v>
+        <v>0.003727051895111799</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.001901969430036843</v>
+        <v>0.002556456252932549</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.001787934568710625</v>
+        <v>0.004890595562756062</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.003231678623706102</v>
+        <v>0.001828657696023583</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.897425580769777e-05</v>
+        <v>0.001013888278976083</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.001714420970529318</v>
+        <v>0.0143448943272233</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.005820406135171652</v>
+        <v>0.001474923104979098</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0004207227320875973</v>
+        <v>0.008789068087935448</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0175697673112154</v>
+        <v>0.01921920105814934</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.02003978192806244</v>
+        <v>0.001053788466379046</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.002028929768130183</v>
+        <v>0.005567308049649</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.004406161606311798</v>
+        <v>0.01126906368881464</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.01011479645967484</v>
+        <v>0.003496447810903192</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.01412829849869013</v>
+        <v>0.0006697350181639194</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.004727558232843876</v>
+        <v>0.009446753188967705</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.002696714131161571</v>
+        <v>0.000330367882270366</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.001293038716539741</v>
+        <v>0.002686151536181569</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.003922367002815008</v>
+        <v>0.001191698596812785</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.394337207078934e-05</v>
+        <v>0.001268939697183669</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.00160495878662914</v>
+        <v>0.006283210590481758</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.008673660457134247</v>
+        <v>0.01239819452166557</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.002625187393277884</v>
+        <v>0.004538022913038731</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.00599181279540062</v>
+        <v>0.0001581805991008878</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0032549649477005</v>
+        <v>0.0004471498832572252</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.00453563965857029</v>
+        <v>0.001139493426308036</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.003920399118214846</v>
+        <v>0.006909373216331005</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.005489237606525421</v>
+        <v>0.0008173599489964545</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.00352163752540946</v>
+        <v>0.003411964047700167</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.001701253466308117</v>
+        <v>0.001845010207034647</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0002339586499147117</v>
+        <v>0.0008415653137490153</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.005430013407021761</v>
+        <v>0.000216007509152405</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.846032243221998e-05</v>
+        <v>0.002153609646484256</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.004069952294230461</v>
+        <v>0.005562611855566502</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.002218362409621477</v>
+        <v>0.0027599495369941</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.006636807229369879</v>
+        <v>0.02150631695985794</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01480857655405998</v>
+        <v>0.01535133738070726</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.00466585299000144</v>
+        <v>0.004301820881664753</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0007924600504338741</v>
+        <v>0.0007086115656420588</v>
       </c>
       <c r="CB10" t="n">
-        <v>2.462649717926979e-06</v>
+        <v>0.006598495878279209</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.003464786801487207</v>
+        <v>0.002770814346149564</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0001494198804721236</v>
+        <v>0.0003472071839496493</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.003645357210189104</v>
+        <v>0.002692948561161757</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.001059207250364125</v>
+        <v>0.00162229803390801</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.001608257880434394</v>
+        <v>0.006783644203096628</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0002339251950616017</v>
+        <v>0.00186970504000783</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.002362794242799282</v>
+        <v>0.001539326971396804</v>
       </c>
       <c r="CJ10" t="n">
-        <v>3.782883868552744e-05</v>
+        <v>0.001543149002827704</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0005565386964008212</v>
+        <v>0.003038011258468032</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.004565517418086529</v>
+        <v>0.0002824158582370728</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0005923693533986807</v>
+        <v>0.001232828944921494</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.007437196094542742</v>
+        <v>0.00246848096139729</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.00030486736795865</v>
+        <v>0.002724797930568457</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.001548717613331974</v>
+        <v>0.01445300225168467</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.002085122046992183</v>
+        <v>0.01818536408245564</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.005000034347176552</v>
+        <v>0.003658177796751261</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.002689558081328869</v>
+        <v>0.006417810451239347</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.002334419172257185</v>
+        <v>0.005271581001579762</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0036944430321455</v>
+        <v>0.002763723023235798</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0001355161366518587</v>
+        <v>0.0007112493040040135</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.003523144405335188</v>
+        <v>0.002762236632406712</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.001523561892099679</v>
+        <v>0.001768871443346143</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.002825658302754164</v>
+        <v>0.008248517289757729</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.000233349681366235</v>
+        <v>0.002411380643025041</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.003284589853137732</v>
+        <v>0.001944930641911924</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0007672603824175894</v>
+        <v>0.001851048204116523</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0001646059681661427</v>
+        <v>0.003196978475898504</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.003703937865793705</v>
+        <v>0.0005790674476884305</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0002849160227924585</v>
+        <v>0.001858631148934364</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.00831426028162241</v>
+        <v>0.007249872200191021</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.005683512892574072</v>
+        <v>0.003593833418563008</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01491609122604132</v>
+        <v>0.002647531917318702</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.006365072913467884</v>
+        <v>0.00585108483210206</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.004716724157333374</v>
+        <v>0.002694107592105865</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.003928417339920998</v>
+        <v>0.004436030052602291</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0009726742282509804</v>
+        <v>0.014624266885221</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.003486963920295238</v>
+        <v>0.001116853440180421</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.003399946261197329</v>
+        <v>0.003775195451453328</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.003138530999422073</v>
+        <v>0.0008797923801466823</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.001235708827152848</v>
+        <v>0.0005637353751808405</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.001945373602211475</v>
+        <v>0.0005873548798263073</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.001661101821810007</v>
+        <v>0.009633530862629414</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.006354961544275284</v>
+        <v>0.002541779773309827</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.002573724370449781</v>
+        <v>0.001783238141797483</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.003139378037303686</v>
+        <v>0.005775175988674164</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.004127972759306431</v>
+        <v>0.00571767333894968</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.003218674566596746</v>
+        <v>0.002547685289755464</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.003918435424566269</v>
+        <v>0.004764561541378498</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.002574522281065583</v>
+        <v>0.003621173091232777</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.004576947074383497</v>
+        <v>0.005953777115792036</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.009656960144639015</v>
+        <v>0.006725775077939034</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.001132793491706252</v>
+        <v>0.0009447427000850439</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0009605757659301162</v>
+        <v>0.007643243763595819</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.002778152469545603</v>
+        <v>0.0172914881259203</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.002013708697631955</v>
+        <v>0.004615325015038252</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.00186068587936461</v>
+        <v>0.003988967277109623</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.001167395617812872</v>
+        <v>0.00239269551821053</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.002600627485662699</v>
+        <v>0.0008270117687061429</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0008866009884513915</v>
+        <v>0.00779547356069088</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.002997845411300659</v>
+        <v>0.0002828004071488976</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.00500181270763278</v>
+        <v>0.00119693239685148</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.001188177731819451</v>
+        <v>0.001714370911940932</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.001657054526731372</v>
+        <v>0.001075330656021833</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.003036731388419867</v>
+        <v>0.001068071695044637</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.002570291748270392</v>
+        <v>0.003518761368468404</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.003329304279759526</v>
+        <v>0.0007214904180727899</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.003089454025030136</v>
+        <v>0.0009890049695968628</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0005008401349186897</v>
+        <v>0.008781572803854942</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.001976937055587769</v>
+        <v>0.007408503443002701</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.009437747299671173</v>
+        <v>0.000406322069466114</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.003581826807931066</v>
+        <v>0.005623946897685528</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0004518232308328152</v>
+        <v>0.002254507038742304</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.001075286651030183</v>
+        <v>0.00170963688287884</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0004372001276351511</v>
+        <v>0.0007834306452423334</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.003530543996021152</v>
+        <v>0.003433807287365198</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0003347480378579348</v>
+        <v>0.001536526484414935</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.003379771020263433</v>
+        <v>0.008658488281071186</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0004486741963773966</v>
+        <v>0.002148657338693738</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.00157585518900305</v>
+        <v>0.0009090550593100488</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0008715866133570671</v>
+        <v>0.001878996612504125</v>
       </c>
       <c r="FE10" t="n">
-        <v>5.993252852931619e-05</v>
+        <v>0.003056017681956291</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.005088153760880232</v>
+        <v>6.62035308778286e-05</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0001392281847074628</v>
+        <v>0.006308875046670437</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.001150951022282243</v>
+        <v>0.001365387579426169</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0003057583817280829</v>
+        <v>0.001304964418523014</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.005065246019512415</v>
+        <v>0.0004615774960257113</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.002614571247249842</v>
+        <v>0.002171424683183432</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.002393143717199564</v>
+        <v>0.003299034899100661</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.001375501626171172</v>
+        <v>0.001213844050653279</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.001202861778438091</v>
+        <v>0.005574957467615604</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.004021634813398123</v>
+        <v>0.003123879432678223</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.003812053008005023</v>
+        <v>0.003880228148773313</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.001782719162292778</v>
+        <v>0.01824473589658737</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.007809720933437347</v>
+        <v>0.001798156416043639</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.00466391583904624</v>
+        <v>0.005983781069517136</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.002407592022791505</v>
+        <v>0.002387045882642269</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.001686635310761631</v>
+        <v>0.001104247756302357</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.008450483903288841</v>
+        <v>0.01069655921310186</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.007658449932932854</v>
+        <v>0.001046383869834244</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.004342363215982914</v>
+        <v>0.004980419296771288</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.006209857761859894</v>
+        <v>0.002152475994080305</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0001583025732543319</v>
+        <v>0.002568048425018787</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.00288439285941422</v>
+        <v>0.003230288391932845</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.001512664719484746</v>
+        <v>0.004926324356347322</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.01269388198852539</v>
+        <v>0.007646280806511641</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.005838713608682156</v>
+        <v>0.0009629257256165147</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.009164412505924702</v>
+        <v>0.006944411899894476</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.002617175690829754</v>
+        <v>0.002806074917316437</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.001351840444840491</v>
+        <v>0.004371663555502892</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3.394663872313686e-05</v>
+        <v>1.142227119999006e-05</v>
       </c>
       <c r="B11" t="n">
-        <v>8.934246125136269e-07</v>
+        <v>1.180675371870166e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>2.628714537422638e-05</v>
+        <v>1.110479388444219e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>3.847391053568572e-05</v>
+        <v>3.186649792041862e-06</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001052429433912039</v>
+        <v>1.851406523201149e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>4.267694021109492e-05</v>
+        <v>2.121533179888502e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>2.047951966233086e-05</v>
+        <v>6.115948508522706e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>3.753424243768677e-05</v>
+        <v>1.304106172028696e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>5.997864718665369e-05</v>
+        <v>1.831765644055849e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>6.3622064772062e-06</v>
+        <v>8.98052348929923e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>7.074377936078236e-05</v>
+        <v>1.219509249494877e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>5.741970016970299e-05</v>
+        <v>3.105644282186404e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>4.348366928752512e-06</v>
+        <v>2.026352376560681e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0001069838035618886</v>
+        <v>1.404382874170551e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.729201125679538e-05</v>
+        <v>2.592505370557774e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>7.624682621099055e-05</v>
+        <v>3.167137492710026e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.907939728582278e-05</v>
+        <v>1.334204171143938e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.510043668735307e-05</v>
+        <v>7.53387075747014e-06</v>
       </c>
       <c r="S11" t="n">
-        <v>1.799858728190884e-05</v>
+        <v>4.914566488878336e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>2.539607521612197e-05</v>
+        <v>1.542924565001158e-06</v>
       </c>
       <c r="U11" t="n">
-        <v>4.041067768412177e-06</v>
+        <v>6.271339316299418e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.355945096292999e-05</v>
+        <v>8.139122655848041e-07</v>
       </c>
       <c r="W11" t="n">
-        <v>5.980589776299894e-05</v>
+        <v>2.143497567885788e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>2.791785391309531e-06</v>
+        <v>5.285092356643872e-06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.511640948592685e-05</v>
+        <v>5.565213541558478e-06</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.192582532094093e-06</v>
+        <v>3.963814378948882e-06</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.351859049871564e-05</v>
+        <v>1.395522872371657e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.646417669893708e-05</v>
+        <v>1.993675141420681e-06</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.084245640318841e-05</v>
+        <v>2.118940756190568e-08</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.468148836167529e-05</v>
+        <v>2.184307504649041e-06</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.043116571963765e-05</v>
+        <v>2.356345476073329e-06</v>
       </c>
       <c r="AF11" t="n">
-        <v>6.476786802522838e-05</v>
+        <v>2.880897227441892e-06</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.07456544355955e-05</v>
+        <v>1.64304055942921e-05</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.927625170443207e-05</v>
+        <v>3.73307011614088e-06</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.2584644688759e-05</v>
+        <v>1.303524277318502e-05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5.783157394034788e-05</v>
+        <v>2.649653879416292e-06</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.531527959741652e-05</v>
+        <v>5.708706339646596e-06</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.649201451276895e-05</v>
+        <v>5.288514785206644e-06</v>
       </c>
       <c r="AM11" t="n">
-        <v>4.568410986394156e-06</v>
+        <v>2.779053374979412e-06</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.833995677065104e-05</v>
+        <v>2.537979071348673e-08</v>
       </c>
       <c r="AO11" t="n">
-        <v>6.129793473519385e-05</v>
+        <v>6.312760888249613e-06</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.854903348430526e-05</v>
+        <v>3.668237241072347e-06</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.6794391386793e-06</v>
+        <v>1.686784571575117e-06</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.863950456026942e-05</v>
+        <v>2.349580427107867e-06</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.654118568694685e-05</v>
+        <v>8.147762287080695e-07</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.453497290844098e-05</v>
+        <v>1.955414518306497e-06</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.422330842615338e-05</v>
+        <v>1.117794454330578e-05</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.438600859022699e-06</v>
+        <v>7.572396953037241e-06</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.114030889468268e-05</v>
+        <v>5.455695372802438e-06</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0001119834269047715</v>
+        <v>1.580352181917988e-05</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.055914228549227e-05</v>
+        <v>2.244057759526186e-05</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.870488788175862e-05</v>
+        <v>4.295971393730724e-06</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.210484131472185e-05</v>
+        <v>2.660948439370259e-07</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.738299397402443e-05</v>
+        <v>1.571679490552924e-06</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.655150819919072e-05</v>
+        <v>9.81431185209658e-06</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.659205271513201e-06</v>
+        <v>3.110839770670282e-06</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.832031714206096e-05</v>
+        <v>5.270935616863426e-07</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.169910607743077e-05</v>
+        <v>3.361325980222318e-06</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.561667158966884e-05</v>
+        <v>8.323473593918607e-06</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.635296863853e-05</v>
+        <v>4.690169816967682e-07</v>
       </c>
       <c r="BI11" t="n">
-        <v>4.05768514610827e-05</v>
+        <v>6.678310455754399e-06</v>
       </c>
       <c r="BJ11" t="n">
-        <v>3.887168713845313e-05</v>
+        <v>1.804839121177793e-05</v>
       </c>
       <c r="BK11" t="n">
-        <v>2.218172994616907e-05</v>
+        <v>2.947585244328366e-06</v>
       </c>
       <c r="BL11" t="n">
-        <v>9.172859790851362e-06</v>
+        <v>2.937177214334952e-06</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.391361158515792e-05</v>
+        <v>3.90216700907331e-06</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.28031528624706e-05</v>
+        <v>2.097414608215331e-06</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.243498551659286e-05</v>
+        <v>5.595565198746044e-06</v>
       </c>
       <c r="BP11" t="n">
-        <v>2.255083745694719e-05</v>
+        <v>5.189130206417758e-06</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.919646405847743e-05</v>
+        <v>8.654212251713034e-06</v>
       </c>
       <c r="BR11" t="n">
-        <v>7.873190952523146e-06</v>
+        <v>5.212315500102704e-06</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.913138268922921e-05</v>
+        <v>5.028643499827012e-06</v>
       </c>
       <c r="BT11" t="n">
-        <v>4.715512477559969e-05</v>
+        <v>7.918261871964205e-06</v>
       </c>
       <c r="BU11" t="n">
-        <v>2.223974661319517e-05</v>
+        <v>2.495338776498102e-06</v>
       </c>
       <c r="BV11" t="n">
-        <v>1.550221895740833e-05</v>
+        <v>4.629187515092781e-06</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.869762283808086e-05</v>
+        <v>1.664756723585015e-06</v>
       </c>
       <c r="BX11" t="n">
-        <v>2.391201451246161e-05</v>
+        <v>1.205810440296773e-05</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.699408964370377e-05</v>
+        <v>3.973917500843527e-06</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5.574686383624794e-06</v>
+        <v>7.771410309942439e-06</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.407265699526761e-05</v>
+        <v>9.270640930481022e-07</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.770473995245993e-05</v>
+        <v>7.043615823931759e-08</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.904107845504768e-05</v>
+        <v>1.033550688589457e-06</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.961486178624909e-07</v>
+        <v>1.993152636714512e-06</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.661585883994121e-05</v>
+        <v>4.405089839565335e-06</v>
       </c>
       <c r="CF11" t="n">
-        <v>1.970313405763591e-06</v>
+        <v>2.3712714209978e-06</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.431042594253086e-05</v>
+        <v>8.163650022652291e-07</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.976340354303829e-05</v>
+        <v>1.927183802763466e-06</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.198042991745751e-05</v>
+        <v>5.088060788693838e-06</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.413933205185458e-05</v>
+        <v>1.39681560540339e-06</v>
       </c>
       <c r="CK11" t="n">
-        <v>8.045927643252071e-06</v>
+        <v>9.195476877721376e-07</v>
       </c>
       <c r="CL11" t="n">
-        <v>9.246441550203599e-06</v>
+        <v>1.396608695358736e-06</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.472923733876087e-05</v>
+        <v>4.097801593161421e-06</v>
       </c>
       <c r="CN11" t="n">
-        <v>4.802991679753177e-05</v>
+        <v>3.263106464146404e-06</v>
       </c>
       <c r="CO11" t="n">
-        <v>2.401376150373835e-06</v>
+        <v>7.144442406570306e-06</v>
       </c>
       <c r="CP11" t="n">
-        <v>7.23237099009566e-05</v>
+        <v>9.229710485669784e-06</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.990130790043622e-05</v>
+        <v>2.91000333163538e-07</v>
       </c>
       <c r="CR11" t="n">
-        <v>3.061388269998133e-05</v>
+        <v>2.775381062747329e-06</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.371576010773424e-05</v>
+        <v>5.575661361945095e-06</v>
       </c>
       <c r="CT11" t="n">
-        <v>1.810944377211854e-05</v>
+        <v>4.387652552395593e-06</v>
       </c>
       <c r="CU11" t="n">
-        <v>3.560016193659976e-05</v>
+        <v>3.432062385400059e-07</v>
       </c>
       <c r="CV11" t="n">
-        <v>3.586985258152708e-06</v>
+        <v>1.84486134457984e-06</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.133924317604396e-05</v>
+        <v>2.762993062788155e-06</v>
       </c>
       <c r="CX11" t="n">
-        <v>3.330333584017353e-06</v>
+        <v>6.410044761651079e-07</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.513373328838497e-05</v>
+        <v>1.378892875436577e-06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.769204391166568e-05</v>
+        <v>2.615822268126067e-06</v>
       </c>
       <c r="DA11" t="n">
-        <v>5.890295597055228e-06</v>
+        <v>5.885889549972489e-06</v>
       </c>
       <c r="DB11" t="n">
-        <v>2.546289397287183e-05</v>
+        <v>2.302101165696513e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>8.827732017380185e-06</v>
+        <v>1.372887652451027e-07</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.903056833427399e-06</v>
+        <v>1.777096031219116e-06</v>
       </c>
       <c r="DE11" t="n">
-        <v>7.087492849677801e-05</v>
+        <v>1.060663407770335e-06</v>
       </c>
       <c r="DF11" t="n">
-        <v>5.689215322490782e-05</v>
+        <v>2.447597580612637e-06</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.50126570588327e-05</v>
+        <v>2.045942210315843e-06</v>
       </c>
       <c r="DH11" t="n">
-        <v>1.204873115057126e-06</v>
+        <v>3.537098109518411e-06</v>
       </c>
       <c r="DI11" t="n">
-        <v>2.417314317426644e-05</v>
+        <v>3.403767095733201e-06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>4.830282705370337e-05</v>
+        <v>8.277646884380374e-06</v>
       </c>
       <c r="DK11" t="n">
-        <v>2.403200596745592e-05</v>
+        <v>2.587939889053814e-07</v>
       </c>
       <c r="DL11" t="n">
-        <v>2.649529415066354e-05</v>
+        <v>1.428889754606644e-05</v>
       </c>
       <c r="DM11" t="n">
-        <v>4.521122536971234e-05</v>
+        <v>4.322184395277873e-06</v>
       </c>
       <c r="DN11" t="n">
-        <v>9.480527296545915e-06</v>
+        <v>2.784609932859894e-06</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.570514334365726e-05</v>
+        <v>5.41691406397149e-07</v>
       </c>
       <c r="DP11" t="n">
-        <v>1.136409809987526e-05</v>
+        <v>3.506002030917443e-06</v>
       </c>
       <c r="DQ11" t="n">
-        <v>2.77626677416265e-05</v>
+        <v>2.807597411447205e-06</v>
       </c>
       <c r="DR11" t="n">
-        <v>1.61421558004804e-05</v>
+        <v>3.479762654023943e-06</v>
       </c>
       <c r="DS11" t="n">
-        <v>1.629157850402407e-05</v>
+        <v>3.038488557649544e-06</v>
       </c>
       <c r="DT11" t="n">
-        <v>9.871095244307071e-06</v>
+        <v>6.114748885011068e-07</v>
       </c>
       <c r="DU11" t="n">
-        <v>2.26643678615801e-05</v>
+        <v>2.433575900795404e-06</v>
       </c>
       <c r="DV11" t="n">
-        <v>5.606054764939472e-05</v>
+        <v>9.44175781114609e-07</v>
       </c>
       <c r="DW11" t="n">
-        <v>9.917131137626711e-06</v>
+        <v>8.192223504011054e-07</v>
       </c>
       <c r="DX11" t="n">
-        <v>1.434512705600355e-05</v>
+        <v>5.18847741659556e-07</v>
       </c>
       <c r="DY11" t="n">
-        <v>1.000732663669623e-05</v>
+        <v>7.519070095440838e-06</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.394162533571944e-05</v>
+        <v>6.339079391182167e-06</v>
       </c>
       <c r="EA11" t="n">
-        <v>2.079941623378545e-05</v>
+        <v>1.026308927976061e-05</v>
       </c>
       <c r="EB11" t="n">
-        <v>5.823885658173822e-06</v>
+        <v>5.245599368208786e-07</v>
       </c>
       <c r="EC11" t="n">
-        <v>4.600327429216122e-06</v>
+        <v>9.642067766435503e-08</v>
       </c>
       <c r="ED11" t="n">
-        <v>2.928662070189603e-05</v>
+        <v>1.34490128402831e-05</v>
       </c>
       <c r="EE11" t="n">
-        <v>1.444991721655242e-05</v>
+        <v>9.23966035770718e-06</v>
       </c>
       <c r="EF11" t="n">
-        <v>1.437996979802847e-05</v>
+        <v>1.298967504226312e-06</v>
       </c>
       <c r="EG11" t="n">
-        <v>1.728508323139977e-06</v>
+        <v>7.901533649601333e-08</v>
       </c>
       <c r="EH11" t="n">
-        <v>5.482450887939194e-06</v>
+        <v>6.027583367540501e-06</v>
       </c>
       <c r="EI11" t="n">
-        <v>4.415614603203721e-05</v>
+        <v>7.72571365814656e-06</v>
       </c>
       <c r="EJ11" t="n">
-        <v>1.901468567666598e-05</v>
+        <v>2.045713472398347e-06</v>
       </c>
       <c r="EK11" t="n">
-        <v>3.356541583343642e-06</v>
+        <v>4.014586920675356e-06</v>
       </c>
       <c r="EL11" t="n">
-        <v>1.982048161153216e-06</v>
+        <v>8.27039343676006e-08</v>
       </c>
       <c r="EM11" t="n">
-        <v>2.135691465809941e-05</v>
+        <v>2.859007508959621e-06</v>
       </c>
       <c r="EN11" t="n">
-        <v>1.074013198376633e-07</v>
+        <v>2.267614036099985e-06</v>
       </c>
       <c r="EO11" t="n">
-        <v>1.1077353519795e-05</v>
+        <v>3.708558551807073e-06</v>
       </c>
       <c r="EP11" t="n">
-        <v>3.924188149539987e-06</v>
+        <v>5.520220838661771e-06</v>
       </c>
       <c r="EQ11" t="n">
-        <v>4.735143647849327e-06</v>
+        <v>4.697900521932752e-07</v>
       </c>
       <c r="ER11" t="n">
-        <v>1.265456376131624e-06</v>
+        <v>2.338420472369762e-06</v>
       </c>
       <c r="ES11" t="n">
-        <v>3.430547803873196e-05</v>
+        <v>4.944805823470233e-06</v>
       </c>
       <c r="ET11" t="n">
-        <v>4.362115760159213e-06</v>
+        <v>4.658319085137919e-06</v>
       </c>
       <c r="EU11" t="n">
-        <v>1.785821586963721e-05</v>
+        <v>1.497557832408347e-06</v>
       </c>
       <c r="EV11" t="n">
-        <v>1.597562004462816e-05</v>
+        <v>4.217995410726871e-06</v>
       </c>
       <c r="EW11" t="n">
-        <v>3.331063635414466e-05</v>
+        <v>2.653104729688494e-06</v>
       </c>
       <c r="EX11" t="n">
-        <v>6.173266228870489e-06</v>
+        <v>2.423684009045246e-06</v>
       </c>
       <c r="EY11" t="n">
-        <v>1.333331510977587e-05</v>
+        <v>3.470639057923108e-06</v>
       </c>
       <c r="EZ11" t="n">
-        <v>3.048046664844151e-06</v>
+        <v>1.558591520733899e-06</v>
       </c>
       <c r="FA11" t="n">
-        <v>2.004480666073505e-05</v>
+        <v>1.846487862167123e-06</v>
       </c>
       <c r="FB11" t="n">
-        <v>2.092534668918233e-05</v>
+        <v>5.82650841352006e-07</v>
       </c>
       <c r="FC11" t="n">
-        <v>5.660611350322142e-06</v>
+        <v>3.697545253089629e-06</v>
       </c>
       <c r="FD11" t="n">
-        <v>1.926804179674946e-05</v>
+        <v>1.303298290622479e-06</v>
       </c>
       <c r="FE11" t="n">
-        <v>7.656381058041006e-06</v>
+        <v>9.557572866469854e-07</v>
       </c>
       <c r="FF11" t="n">
-        <v>1.932462055265205e-06</v>
+        <v>2.328346226931899e-07</v>
       </c>
       <c r="FG11" t="n">
-        <v>3.461966480244882e-05</v>
+        <v>1.015121142700082e-06</v>
       </c>
       <c r="FH11" t="n">
-        <v>2.153561217710376e-05</v>
+        <v>2.739354385994375e-06</v>
       </c>
       <c r="FI11" t="n">
-        <v>2.084316838590894e-05</v>
+        <v>2.348646830796497e-06</v>
       </c>
       <c r="FJ11" t="n">
-        <v>3.903812103089876e-05</v>
+        <v>5.182053428143263e-06</v>
       </c>
       <c r="FK11" t="n">
-        <v>1.842411074903794e-05</v>
+        <v>3.01299132843269e-06</v>
       </c>
       <c r="FL11" t="n">
-        <v>1.937085107783787e-05</v>
+        <v>5.083050382381771e-06</v>
       </c>
       <c r="FM11" t="n">
-        <v>2.385420339123812e-05</v>
+        <v>5.373320277612947e-07</v>
       </c>
       <c r="FN11" t="n">
-        <v>1.400350902258651e-05</v>
+        <v>1.131644239649177e-06</v>
       </c>
       <c r="FO11" t="n">
-        <v>2.206393764936365e-05</v>
+        <v>1.333326054009376e-05</v>
       </c>
       <c r="FP11" t="n">
-        <v>2.703888094401918e-05</v>
+        <v>6.143208338471595e-06</v>
       </c>
       <c r="FQ11" t="n">
-        <v>1.446265969207161e-06</v>
+        <v>7.478446150344098e-06</v>
       </c>
       <c r="FR11" t="n">
-        <v>1.928293568198569e-05</v>
+        <v>4.862436071562115e-06</v>
       </c>
       <c r="FS11" t="n">
-        <v>2.272572601214051e-05</v>
+        <v>6.372095413098577e-06</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0001319566072197631</v>
+        <v>1.504895863035927e-05</v>
       </c>
       <c r="FU11" t="n">
-        <v>4.319816798670217e-05</v>
+        <v>6.727367690473329e-06</v>
       </c>
       <c r="FV11" t="n">
-        <v>2.008868250413798e-06</v>
+        <v>8.779185918683652e-06</v>
       </c>
       <c r="FW11" t="n">
-        <v>4.426655868883245e-05</v>
+        <v>1.710182550596073e-05</v>
       </c>
       <c r="FX11" t="n">
-        <v>1.794638956198469e-05</v>
+        <v>1.884549419628456e-06</v>
       </c>
       <c r="FY11" t="n">
-        <v>1.85261778824497e-05</v>
+        <v>6.663542535534361e-06</v>
       </c>
       <c r="FZ11" t="n">
-        <v>2.66994447883917e-07</v>
+        <v>3.065113787670271e-06</v>
       </c>
       <c r="GA11" t="n">
-        <v>1.633980718906969e-05</v>
+        <v>7.017303232714767e-06</v>
       </c>
       <c r="GB11" t="n">
-        <v>2.044149732682854e-05</v>
+        <v>1.869025027190219e-06</v>
       </c>
       <c r="GC11" t="n">
-        <v>1.983334368560463e-05</v>
+        <v>7.682956493226811e-06</v>
       </c>
       <c r="GD11" t="n">
-        <v>1.767966568877455e-05</v>
+        <v>1.065053038473707e-05</v>
       </c>
       <c r="GE11" t="n">
-        <v>7.823632040526718e-05</v>
+        <v>5.70730253457441e-06</v>
       </c>
       <c r="GF11" t="n">
-        <v>6.171852874103934e-05</v>
+        <v>2.879622797991033e-06</v>
       </c>
       <c r="GG11" t="n">
-        <v>7.67214223742485e-05</v>
+        <v>3.766746203837101e-06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.001058163121342659</v>
+        <v>2.882842090912163e-05</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0325981006026268</v>
+        <v>0.01164825819432735</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001274352427572012</v>
+        <v>0.002631091978400946</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02953633666038513</v>
+        <v>0.007726551033556461</v>
       </c>
       <c r="E12" t="n">
-        <v>0.009747804142534733</v>
+        <v>0.001381531008519232</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01253620069473982</v>
+        <v>0.006057596299797297</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005245243199169636</v>
+        <v>0.00253945798613131</v>
       </c>
       <c r="H12" t="n">
-        <v>0.004158651456236839</v>
+        <v>0.002531210891902447</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01124388910830021</v>
+        <v>0.0009998551104217768</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0006517297588288784</v>
+        <v>0.001048358855769038</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02794810011982918</v>
+        <v>0.01119978912174702</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001365106203593314</v>
+        <v>0.00467374874278903</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02386867254972458</v>
+        <v>0.01022309809923172</v>
       </c>
       <c r="N12" t="n">
-        <v>0.00698493979871273</v>
+        <v>2.855074126273394e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01269766502082348</v>
+        <v>0.005976412910968065</v>
       </c>
       <c r="P12" t="n">
-        <v>0.00732224527746439</v>
+        <v>0.003026711754500866</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.006064710207283497</v>
+        <v>0.001929489895701408</v>
       </c>
       <c r="R12" t="n">
-        <v>0.01172416284680367</v>
+        <v>0.0006541424663737416</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0003954110434278846</v>
+        <v>0.0002351482107769698</v>
       </c>
       <c r="T12" t="n">
-        <v>0.002582596614956856</v>
+        <v>6.898990250192583e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0004595146747305989</v>
+        <v>0.0005365298711694777</v>
       </c>
       <c r="V12" t="n">
-        <v>0.007192709483206272</v>
+        <v>0.0002028323069680482</v>
       </c>
       <c r="W12" t="n">
-        <v>0.01743965037167072</v>
+        <v>0.0009035957045853138</v>
       </c>
       <c r="X12" t="n">
-        <v>0.001786401262506843</v>
+        <v>0.001695546787232161</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.004949433729052544</v>
+        <v>6.348031456582248e-05</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.004639888182282448</v>
+        <v>0.001671858946792781</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.003584787482395768</v>
+        <v>0.001407049130648375</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.003108196426182985</v>
+        <v>0.0004643200081773102</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.862869925796986e-05</v>
+        <v>0.0003301976248621941</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.004109714180231094</v>
+        <v>0.001828589010983706</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.004811378661543131</v>
+        <v>0.0007239652913995087</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.006231477484107018</v>
+        <v>0.001448273425921798</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.006925559137016535</v>
+        <v>0.003540383419021964</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.002813074504956603</v>
+        <v>0.0008111521019600332</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.001415531383827329</v>
+        <v>0.0009929672814905643</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.005087140947580338</v>
+        <v>0.0007763581234030426</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.001036156085319817</v>
+        <v>0.0002881516702473164</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.002978038508445024</v>
+        <v>0.002969713415950537</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.001620020950213075</v>
+        <v>0.002842995803803205</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0007800678722560406</v>
+        <v>0.002284020651131868</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.004811256658285856</v>
+        <v>0.001108692842535675</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.005403168965131044</v>
+        <v>0.002045823726803064</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.003289316780865192</v>
+        <v>0.00121969380415976</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.0008500887779518962</v>
+        <v>0.0004785049532074481</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.001510899979621172</v>
+        <v>0.0003827912732958794</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0003465055488049984</v>
+        <v>0.0002090999623760581</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.01153315789997578</v>
+        <v>0.004300031810998917</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.002896623453125358</v>
+        <v>0.002478371374309063</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.01571409590542316</v>
+        <v>0.003611137624830008</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.01374744344502687</v>
+        <v>0.004882649518549442</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.002713065361604095</v>
+        <v>0.003893071785569191</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.01455347798764706</v>
+        <v>0.0002962090657092631</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.01614325121045113</v>
+        <v>0.0003299219533801079</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.001953891711309552</v>
+        <v>0.001563478377647698</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.0001672033686190844</v>
+        <v>0.000493616855237633</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.007865395396947861</v>
+        <v>0.001402397523634136</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.003144192975014448</v>
+        <v>0.001716223079711199</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0008877333020791411</v>
+        <v>0.0001965847914107144</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.001988973934203386</v>
+        <v>0.002049590460956097</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.002017925959080458</v>
+        <v>0.001202610088512301</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.007621346041560173</v>
+        <v>0.00139291537925601</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.002967298496514559</v>
+        <v>0.001342050614766777</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.01061340235173702</v>
+        <v>0.00101308710873127</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0003919436712749302</v>
+        <v>0.000206572818569839</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.004286863841116428</v>
+        <v>0.001030682702548802</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.001716644153930247</v>
+        <v>0.0001111219462472945</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.007750103250145912</v>
+        <v>0.001089830766431987</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.004551974590867758</v>
+        <v>0.0001459734776290134</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.001613222644664347</v>
+        <v>0.0009579767938703299</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0009990604594349861</v>
+        <v>3.141570778097957e-05</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.008320778608322144</v>
+        <v>0.001139125321060419</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.004150996915996075</v>
+        <v>0.0008517394890077412</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.003460538573563099</v>
+        <v>1.628672907827422e-05</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.01310601364821196</v>
+        <v>0.003980034030973911</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.001919639762490988</v>
+        <v>0.001859300537034869</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.01732892729341984</v>
+        <v>0.004065870307385921</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.01215100754052401</v>
+        <v>0.0009727355791255832</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.000803910952527076</v>
+        <v>0.002314051380380988</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.006964574567973614</v>
+        <v>0.000353874551365152</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.006459770724177361</v>
+        <v>0.000584798282943666</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.00583819393068552</v>
+        <v>0.0002051932970061898</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0005723554641008377</v>
+        <v>0.0003313501947559416</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.003817454446107149</v>
+        <v>0.003515331540256739</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.001372020808048546</v>
+        <v>0.0006229428108781576</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.004315732512623072</v>
+        <v>0.002892816672101617</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.000338454294251278</v>
+        <v>0.0005863995174877346</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.001135424943640828</v>
+        <v>0.001012092106975615</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.002336329780519009</v>
+        <v>4.959249054081738e-05</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.001064903568476439</v>
+        <v>0.0001360186579404399</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.002037159400060773</v>
+        <v>0.0006769333849661052</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0008506831363774836</v>
+        <v>0.0005054321372881532</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.006551722530275583</v>
+        <v>0.0005686916410923004</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.001029538689181209</v>
+        <v>0.004433882888406515</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0017406438710168</v>
+        <v>0.004473646637052298</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.001169190974906087</v>
+        <v>0.000955563155002892</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.007489420473575592</v>
+        <v>0.0005451217875815928</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.008626947179436684</v>
+        <v>0.0005391145823523402</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.01326098944991827</v>
+        <v>0.001555373077280819</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0007586420979350805</v>
+        <v>4.753380198962986e-05</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.0004020250344183296</v>
+        <v>0.0003115284780506045</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.004800880327820778</v>
+        <v>0.003402709029614925</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.001653520856052637</v>
+        <v>0.000938026059884578</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.004567191004753113</v>
+        <v>0.002782187890261412</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.002270280616357923</v>
+        <v>0.0003487613867036998</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.00171766197308898</v>
+        <v>0.001180483843199909</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.001787907443940639</v>
+        <v>9.21454920899123e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.002055058954283595</v>
+        <v>0.0005119381821714342</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.001529325963929296</v>
+        <v>0.0001837225572671741</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.001001411932520568</v>
+        <v>0.001330467872321606</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.01155098434537649</v>
+        <v>0.002142123179510236</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.0009872135706245899</v>
+        <v>0.001468367176130414</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01649469137191772</v>
+        <v>0.002751683816313744</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.01137128937989473</v>
+        <v>0.0007299172575585544</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.006233073770999908</v>
+        <v>0.00796821154654026</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.005630412138998508</v>
+        <v>1.861806958913803e-05</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.002747527090832591</v>
+        <v>0.004443117883056402</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.003120802342891693</v>
+        <v>0.003326221136376262</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.005000813864171505</v>
+        <v>0.0006210882565937936</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.00790452491492033</v>
+        <v>0.002234562765806913</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.001208784291520715</v>
+        <v>0.0002430057502351701</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01040263473987579</v>
+        <v>0.001349349040538073</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.001958871958777308</v>
+        <v>0.0004569345328491181</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.00467623071745038</v>
+        <v>0.0002521153364796191</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.001763315289281309</v>
+        <v>0.0001743964676279575</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.001217386568896472</v>
+        <v>0.001489336369559169</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.002708720741793513</v>
+        <v>0.00345713971182704</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.002411442808806896</v>
+        <v>9.024020982906222e-05</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.001326095778495073</v>
+        <v>0.0003803182626143098</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.001696811057627201</v>
+        <v>0.00200443621724844</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.003467323491349816</v>
+        <v>0.002590996446087956</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.007677836343646049</v>
+        <v>0.0001104018447222188</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.001505661755800247</v>
+        <v>0.00256479368545115</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.002382309408858418</v>
+        <v>0.0005064667784608901</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.003890274092555046</v>
+        <v>0.004340483341366053</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.001978117972612381</v>
+        <v>0.004333027638494968</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.002316638361662626</v>
+        <v>0.00183348183054477</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0006408252520486712</v>
+        <v>0.002450405620038509</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.002543563256040215</v>
+        <v>0.001464880420826375</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0006872301455587149</v>
+        <v>0.002820841502398252</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.00336262839846313</v>
+        <v>0.0007754316902719438</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.001609214465133846</v>
+        <v>0.0004220372356940061</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.001176030375063419</v>
+        <v>0.0002164107863791287</v>
       </c>
       <c r="EM12" t="n">
-        <v>8.862093091011047e-05</v>
+        <v>0.0004192656488157809</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0005689177778549492</v>
+        <v>0.0002757463371381164</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.0006549315294250846</v>
+        <v>0.0009494525147601962</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0002442157128825784</v>
+        <v>0.00364655489102006</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.001385969575494528</v>
+        <v>0.0007576524512842298</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.007275568321347237</v>
+        <v>0.001177414786070585</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.001418279018253088</v>
+        <v>0.0002265836083097383</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.01725956983864307</v>
+        <v>0.0001155620266217738</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.008172120898962021</v>
+        <v>0.001138060702942312</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.004076036624610424</v>
+        <v>0.001594485598616302</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.006632940843701363</v>
+        <v>0.001796271302737296</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0009177425527013838</v>
+        <v>0.0002087736211251467</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.003289230167865753</v>
+        <v>0.003509557340294123</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.001063589006662369</v>
+        <v>0.0007666698656976223</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.005504495464265347</v>
+        <v>0.003316879272460938</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0002648752997629344</v>
+        <v>0.0004913680022582412</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.001803194405511022</v>
+        <v>0.001032447325997055</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.004331076983362436</v>
+        <v>0.0001987849245779216</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.002110350877046585</v>
+        <v>0.0005607169005088508</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.002077612094581127</v>
+        <v>0.0001266186300199479</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.001071743201464415</v>
+        <v>0.0004568200674839318</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.00119915627874434</v>
+        <v>0.001225188258104026</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.003208521986380219</v>
+        <v>2.392739406786859e-05</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.001827192259952426</v>
+        <v>0.0007630751933902502</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.008373686112463474</v>
+        <v>0.001813437789678574</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.009836652316153049</v>
+        <v>0.0002089686458930373</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0001994573976844549</v>
+        <v>5.789578426629305e-05</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.002591200405731797</v>
+        <v>0.001292963745072484</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.004514273721724749</v>
+        <v>0.001773272175341845</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.002092852257192135</v>
+        <v>0.001489581656642258</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.006577638909220695</v>
+        <v>0.00477828411385417</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.005429370794445276</v>
+        <v>0.001755742472596467</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.005199276376515627</v>
+        <v>0.002314707264304161</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01485535129904747</v>
+        <v>0.006841276772320271</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.006101537030190229</v>
+        <v>0.002171743428334594</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.006036578211933374</v>
+        <v>0.0006192370783537626</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.002561157336458564</v>
+        <v>0.00197611004114151</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.002029638970270753</v>
+        <v>0.002985072555020452</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.002521112561225891</v>
+        <v>0.001123652793467045</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.0005882009281776845</v>
+        <v>0.0003987496020272374</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0004745844344142824</v>
+        <v>0.001477855606935918</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.002769857412204146</v>
+        <v>0.002300831722095609</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.01191836781799793</v>
+        <v>0.0001572700712131336</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.003397874301299453</v>
+        <v>0.001839772099629045</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.008050678297877312</v>
+        <v>0.002398770768195391</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.006050070282071829</v>
+        <v>0.0003053424879908562</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.002868095645681024</v>
+        <v>0.001058332854881883</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0002036989462794736</v>
+        <v>0.000129514082800597</v>
       </c>
       <c r="B13" t="n">
-        <v>0.002836824860423803</v>
+        <v>0.006080381572246552</v>
       </c>
       <c r="C13" t="n">
-        <v>4.675790842156857e-05</v>
+        <v>0.0007690958445891738</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002617910737171769</v>
+        <v>0.001978999236598611</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0003143416251987219</v>
+        <v>0.001233328832313418</v>
       </c>
       <c r="F13" t="n">
-        <v>0.002282236469909549</v>
+        <v>0.01015070546418428</v>
       </c>
       <c r="G13" t="n">
-        <v>1.107229036279023e-05</v>
+        <v>0.002615021076053381</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0005424183327704668</v>
+        <v>0.007057601120322943</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001683037960901856</v>
+        <v>0.001356325228698552</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0007689876947551966</v>
+        <v>0.0004768420476466417</v>
       </c>
       <c r="K13" t="n">
-        <v>0.002041820203885436</v>
+        <v>0.006154222879558802</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0003677647036965936</v>
+        <v>0.0009297200012952089</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001142104738391936</v>
+        <v>0.004323008004575968</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0007533474126830697</v>
+        <v>0.006147273816168308</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001297987764701247</v>
+        <v>0.01161914877593517</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001556470524519682</v>
+        <v>0.003610267769545317</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001116166589781642</v>
+        <v>0.00674162246286869</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0001746552006807178</v>
+        <v>0.002844528993591666</v>
       </c>
       <c r="S13" t="n">
-        <v>3.256615673308261e-05</v>
+        <v>0.0001721800945233554</v>
       </c>
       <c r="T13" t="n">
-        <v>0.000747480196878314</v>
+        <v>0.001097159925848246</v>
       </c>
       <c r="U13" t="n">
-        <v>0.000154127279529348</v>
+        <v>0.001483478583395481</v>
       </c>
       <c r="V13" t="n">
-        <v>0.001720797969028354</v>
+        <v>0.001961905974894762</v>
       </c>
       <c r="W13" t="n">
-        <v>0.003002300625666976</v>
+        <v>0.003369501559063792</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0004930007271468639</v>
+        <v>0.001900098519399762</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0001083170936908573</v>
+        <v>0.0003531535621732473</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.001374969491735101</v>
+        <v>0.0003446131013333797</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.159949068911374e-06</v>
+        <v>0.0008647397626191378</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0007853375282138586</v>
+        <v>0.0003985260846093297</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0002407857391517609</v>
+        <v>0.0007566579151898623</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.001014329725876451</v>
+        <v>0.000946356391068548</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0004379929159767926</v>
+        <v>0.00342689105309546</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0004104194522369653</v>
+        <v>0.002885104157030582</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0005345538957044482</v>
+        <v>0.0006508455844596028</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0007414416177198291</v>
+        <v>0.000705069862306118</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0006302330293692648</v>
+        <v>0.003928291611373425</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0004837824963033199</v>
+        <v>0.0008091850904747844</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0001662802242208272</v>
+        <v>0.0003067113284487277</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.086063174530864e-05</v>
+        <v>0.003154595149680972</v>
       </c>
       <c r="AM13" t="n">
-        <v>4.70881350338459e-05</v>
+        <v>0.001293343026190996</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.001129152486100793</v>
+        <v>0.001989078707993031</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0007759774453006685</v>
+        <v>0.0005022104596719146</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0005711475387215614</v>
+        <v>0.003261436708271503</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.000189884245628491</v>
+        <v>0.0002318553742952645</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0001464839151594788</v>
+        <v>0.0001772595860529691</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0002753512235358357</v>
+        <v>0.001589655643329024</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0009263899410143495</v>
+        <v>0.001001824857667089</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0006866721087135375</v>
+        <v>0.007136000320315361</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0003041000454686582</v>
+        <v>0.002267185831442475</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.001948188059031963</v>
+        <v>0.001391042489558458</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.002824167255312204</v>
+        <v>0.0062283119186759</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.002002684399485588</v>
+        <v>0.006290367338806391</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.001433094032108784</v>
+        <v>0.004149906802922487</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.001199739519506693</v>
+        <v>0.002537338994443417</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0012489726068452</v>
+        <v>0.0002824071561917663</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0003305291756987572</v>
+        <v>0.001011112821288407</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0002038558304775506</v>
+        <v>0.0005610153311863542</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0002445272402837873</v>
+        <v>0.0002222915645688772</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0009758443338796496</v>
+        <v>0.00244895601645112</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0005560668068937957</v>
+        <v>0.001138251041993499</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0007021003984846175</v>
+        <v>0.003362826770171523</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.00148223782889545</v>
+        <v>0.0002333045267732814</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.00041834736475721</v>
+        <v>0.003355236724019051</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0003073911066167057</v>
+        <v>0.001468760194256902</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0002269024262204766</v>
+        <v>0.0004243903676979244</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0001774208212736994</v>
+        <v>0.0002456758520565927</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.180164589546621e-05</v>
+        <v>0.0002055143413599581</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.001308560604229569</v>
+        <v>0.0001407742383889854</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0008513026405125856</v>
+        <v>0.0001931559672812</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0003995338047388941</v>
+        <v>0.001784151885658503</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0002929447218775749</v>
+        <v>0.001757659716531634</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.001817741547711194</v>
+        <v>0.001396240899339318</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0008869478479027748</v>
+        <v>0.001143016386777163</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0002341838699067011</v>
+        <v>0.0001239576959051192</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.0008433657349087298</v>
+        <v>0.003954501822590828</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0001910444116219878</v>
+        <v>0.0009976407745853066</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0009979414753615856</v>
+        <v>0.003307988401502371</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.001294031389988959</v>
+        <v>0.004933417309075594</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.001282751793041825</v>
+        <v>0.006282716058194637</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.001038751215673983</v>
+        <v>0.0006796098896302283</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0008923953282646835</v>
+        <v>0.001499953796155751</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0002790738362818956</v>
+        <v>0.002112718531861901</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.729693268425763e-05</v>
+        <v>0.000157761707669124</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0003411378711462021</v>
+        <v>0.002128872089087963</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0004603677080012858</v>
+        <v>3.724508860614151e-05</v>
       </c>
       <c r="CG13" t="n">
-        <v>4.601214823196642e-05</v>
+        <v>0.001210370101034641</v>
       </c>
       <c r="CH13" t="n">
-        <v>6.563228089362383e-05</v>
+        <v>0.0007625199505127966</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0002216965949628502</v>
+        <v>0.003425797447562218</v>
       </c>
       <c r="CJ13" t="n">
-        <v>9.566963854013011e-05</v>
+        <v>0.0002078447287203744</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0003076515858992934</v>
+        <v>0.001835826900787652</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0003183141816407442</v>
+        <v>0.0005207224749028683</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0002051119954558089</v>
+        <v>0.002368741203099489</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.001186458510346711</v>
+        <v>0.003126410767436028</v>
       </c>
       <c r="CO13" t="n">
-        <v>4.34265130024869e-05</v>
+        <v>0.002201574621722102</v>
       </c>
       <c r="CP13" t="n">
-        <v>6.122225022409111e-05</v>
+        <v>0.0029963543638587</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.001557539915665984</v>
+        <v>0.008767098188400269</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0001904097298393026</v>
+        <v>0.00634534377604723</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0009773541241884232</v>
+        <v>0.002100579207763076</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.0002561773872002959</v>
+        <v>0.002797432709485292</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.001248310669325292</v>
+        <v>0.0009572499548085034</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0001282050361623988</v>
+        <v>0.0003631111176218837</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0004582046531140804</v>
+        <v>0.001769079943187535</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0003147659881506115</v>
+        <v>0.0003529113018885255</v>
       </c>
       <c r="CY13" t="n">
-        <v>9.138559107668698e-06</v>
+        <v>0.0009174864389933646</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0001567331200931221</v>
+        <v>0.001143637113273144</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0002751434221863747</v>
+        <v>0.003179682185873389</v>
       </c>
       <c r="DB13" t="n">
-        <v>7.598141382914037e-05</v>
+        <v>0.0003039634902961552</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0003637423506006598</v>
+        <v>0.00155720766633749</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0001726190675981343</v>
+        <v>0.0004775944980792701</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.001245217630639672</v>
+        <v>0.001034035813063383</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.001819925848394632</v>
+        <v>0.0005194373661652207</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.0009408819023519754</v>
+        <v>3.047275822609663e-05</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.002466754056513309</v>
+        <v>0.0008644475601613522</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001079137204214931</v>
+        <v>0.001228061970323324</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0007610914763063192</v>
+        <v>0.001159543870016932</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.001768299727700651</v>
+        <v>0.0009740758105181158</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0001300549483858049</v>
+        <v>0.0006341271800920367</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0005764790112152696</v>
+        <v>0.0005944984732195735</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0004499624774325639</v>
+        <v>5.758849147241563e-05</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0008279965841211379</v>
+        <v>0.0001923197414726019</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0009031229419633746</v>
+        <v>0.0003643488453235477</v>
       </c>
       <c r="DQ13" t="n">
-        <v>4.100671503692865e-06</v>
+        <v>0.002068609464913607</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0003681268426589668</v>
+        <v>0.001596227171830833</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0003557784948498011</v>
+        <v>0.001668180339038372</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0001601125113666058</v>
+        <v>0.001283639459870756</v>
       </c>
       <c r="DU13" t="n">
-        <v>9.083722397917882e-05</v>
+        <v>0.002997647505253553</v>
       </c>
       <c r="DV13" t="n">
-        <v>5.534085357794538e-05</v>
+        <v>0.001304064877331257</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0001018962939269841</v>
+        <v>5.76431630179286e-05</v>
       </c>
       <c r="DX13" t="n">
-        <v>2.632474934216589e-05</v>
+        <v>0.0002047262387350202</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0002870211319532245</v>
+        <v>0.003045306308194995</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0003963134076911956</v>
+        <v>0.0002075035154120997</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0007106580305844545</v>
+        <v>9.529251838102937e-05</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.002481643809005618</v>
+        <v>0.002503297291696072</v>
       </c>
       <c r="EC13" t="n">
-        <v>6.349787872750312e-05</v>
+        <v>0.002091301372274756</v>
       </c>
       <c r="ED13" t="n">
-        <v>8.64646426634863e-06</v>
+        <v>0.0003669431898742914</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0007517964113503695</v>
+        <v>0.001736007165163755</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0005056164227426052</v>
+        <v>0.0009121354669332504</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0007827987428754568</v>
+        <v>0.001220194157212973</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0004023891233373433</v>
+        <v>0.001054661115631461</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.001181201077997684</v>
+        <v>0.002600303618237376</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0003102882474195212</v>
+        <v>0.0001359695452265441</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0001999845553655177</v>
+        <v>0.001990088727325201</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0001837984455050901</v>
+        <v>0.001199492253363132</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0007337210117839277</v>
+        <v>0.0012235043104738</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0001028417173074558</v>
+        <v>0.0002128362830262631</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0002826598938554525</v>
+        <v>0.002034037839621305</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0008074374636635184</v>
+        <v>0.001975922845304012</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0003617999609559774</v>
+        <v>0.0001957948261406273</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0003198306949343532</v>
+        <v>0.0002778852358460426</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0005001506651751697</v>
+        <v>0.0005665285279974341</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.001282902318052948</v>
+        <v>0.002355296397581697</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.001304773148149252</v>
+        <v>0.002472417894750834</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.001445011235773563</v>
+        <v>0.0002888252784032375</v>
       </c>
       <c r="EW13" t="n">
-        <v>8.563014853280038e-05</v>
+        <v>0.0006252133753150702</v>
       </c>
       <c r="EX13" t="n">
-        <v>1.416166196577251e-05</v>
+        <v>0.0002573954989202321</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.000403566547902301</v>
+        <v>0.002115904120728374</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0001639347901800647</v>
+        <v>0.0004671123460866511</v>
       </c>
       <c r="FA13" t="n">
-        <v>2.806058910209686e-05</v>
+        <v>0.00101939553860575</v>
       </c>
       <c r="FB13" t="n">
-        <v>5.646271165460348e-05</v>
+        <v>0.0008687439258210361</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0002145877078874037</v>
+        <v>0.002962657948955894</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0002668289816938341</v>
+        <v>0.0004762870958074927</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0006240117945708334</v>
+        <v>0.001365589560009539</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0004989903536625206</v>
+        <v>7.530031143687665e-05</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0007736979750916362</v>
+        <v>0.001462719053961337</v>
       </c>
       <c r="FH13" t="n">
-        <v>7.96648018877022e-05</v>
+        <v>0.002448801882565022</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0002772996376734227</v>
+        <v>0.0011445990530774</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0008943493594415486</v>
+        <v>0.0007136432686820626</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0004643779247999191</v>
+        <v>6.764469435438514e-05</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.002155102323740721</v>
+        <v>0.0007347492501139641</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0004186834557913244</v>
+        <v>0.0006619988125748932</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0006912390817888081</v>
+        <v>0.0009561637998558581</v>
       </c>
       <c r="FO13" t="n">
-        <v>3.979222674388438e-05</v>
+        <v>0.001417436986230314</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.00060321728233248</v>
+        <v>0.0006785846780985594</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0002164709294447675</v>
+        <v>0.007750763092190027</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0009997736196964979</v>
+        <v>0.001099516055546701</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0009632985456846654</v>
+        <v>0.0006558711174875498</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.002718340372666717</v>
+        <v>0.008374074473977089</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0002993354864884168</v>
+        <v>0.001100716064684093</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0004714171518571675</v>
+        <v>0.003783851861953735</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.001389350509271026</v>
+        <v>0.0004343006294220686</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.001174184959381819</v>
+        <v>9.895215043798089e-05</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.001441359869204462</v>
+        <v>0.0008437271462753415</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0008471067412756383</v>
+        <v>0.0001084090399672277</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.001570777501910925</v>
+        <v>0.002507830504328012</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.001670281053520739</v>
+        <v>0.001031435094773769</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0003239767393097281</v>
+        <v>0.002176424721255898</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0005411850870586932</v>
+        <v>0.002987022511661053</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0009549543028697371</v>
+        <v>0.001432897290214896</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.002041673520579934</v>
+        <v>0.001128326402977109</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0008403090760111809</v>
+        <v>0.0007815439021214843</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0009269759175367653</v>
+        <v>1.225655796588399e-05</v>
       </c>
       <c r="B14" t="n">
-        <v>0.00990923959761858</v>
+        <v>0.0006331809563562274</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0003934924025088549</v>
+        <v>0.0001031131032505073</v>
       </c>
       <c r="D14" t="n">
-        <v>0.005040929187089205</v>
+        <v>0.0004513142339419574</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002022992819547653</v>
+        <v>1.954018989636097e-05</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0002747102989815176</v>
+        <v>0.0003750907781068236</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0009104807395488024</v>
+        <v>0.0001831349218264222</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0001436244638171047</v>
+        <v>0.0001123492038459517</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0002498714602552354</v>
+        <v>1.433052784705069e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>4.788977093994617e-05</v>
+        <v>3.971441765315831e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.007348729763180017</v>
+        <v>0.0006006339099258184</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0005135669489391148</v>
+        <v>0.000221582711674273</v>
       </c>
       <c r="M14" t="n">
-        <v>0.004517299588769674</v>
+        <v>0.0006080238381400704</v>
       </c>
       <c r="N14" t="n">
-        <v>0.002742791548371315</v>
+        <v>7.289471250260249e-05</v>
       </c>
       <c r="O14" t="n">
-        <v>0.001212108181789517</v>
+        <v>0.0003605369420256466</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0006294770864769816</v>
+        <v>0.0001915019820444286</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.00112551636993885</v>
+        <v>9.009216591948643e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0002828117285389453</v>
+        <v>3.482840838842094e-06</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0002502978895790875</v>
+        <v>6.347519047267269e-06</v>
       </c>
       <c r="T14" t="n">
-        <v>0.001105646835640073</v>
+        <v>3.919681694242172e-05</v>
       </c>
       <c r="U14" t="n">
-        <v>5.645332203130238e-05</v>
+        <v>7.523073145421222e-05</v>
       </c>
       <c r="V14" t="n">
-        <v>0.001409866148605943</v>
+        <v>1.292045908485306e-05</v>
       </c>
       <c r="W14" t="n">
-        <v>0.002086482010781765</v>
+        <v>4.556220301310532e-05</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0005731991259381175</v>
+        <v>0.0001802609622245654</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0002628180955071002</v>
+        <v>3.156562161166221e-05</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.001228803768754005</v>
+        <v>6.08493537583854e-05</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0001627751043997705</v>
+        <v>8.336619066540152e-05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0005280784098431468</v>
+        <v>8.872802027326543e-06</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0009795252699404955</v>
+        <v>8.637984137749299e-05</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0005429150187410414</v>
+        <v>8.423982944805175e-05</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0004966643755324185</v>
+        <v>0.0001063453237293288</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0004067823465447873</v>
+        <v>2.76947484962875e-05</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.001426329137757421</v>
+        <v>0.0002394947514403611</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0005229896050877869</v>
+        <v>6.554323772434145e-05</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0008280479232780635</v>
+        <v>0.0001155903373728506</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.369662979617715e-05</v>
+        <v>3.844160528387874e-05</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.00147369469050318</v>
+        <v>4.152158726355992e-05</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0001840022159740329</v>
+        <v>0.0001670844794716686</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0002481694391462952</v>
+        <v>0.0001545977283967659</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.001013796078041196</v>
+        <v>0.0001370249956380576</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.001619716174900532</v>
+        <v>8.698531019035727e-05</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.001511877868324518</v>
+        <v>0.0001017153626889922</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0002257935120724142</v>
+        <v>5.531450733542442e-05</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0009253454627469182</v>
+        <v>5.225637869443744e-05</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0002899147220887244</v>
+        <v>4.235755477566272e-05</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.369332161033526e-05</v>
+        <v>3.100001049460843e-05</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.005777122918516397</v>
+        <v>0.0002796557382680476</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.344588761450723e-05</v>
+        <v>0.0001518139324616641</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.002288136398419738</v>
+        <v>0.000197135770577006</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0004365906061138958</v>
+        <v>0.0002581011212896556</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0004101636004634202</v>
+        <v>0.0002701971097849309</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0004529230063781142</v>
+        <v>2.25445292016957e-05</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0001351641549263149</v>
+        <v>1.585025711392518e-05</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0003242043894715607</v>
+        <v>7.083016680553555e-05</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0008708255481906235</v>
+        <v>7.584428385598585e-05</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.001756243989802897</v>
+        <v>0.0001465775130782276</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.001663970411755145</v>
+        <v>0.0001118464351748116</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0009383475407958031</v>
+        <v>2.353987656533718e-05</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.002919422462582588</v>
+        <v>0.000256980856647715</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.00131233548745513</v>
+        <v>0.0001186178997159004</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.001478377729654312</v>
+        <v>6.74756447551772e-05</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.000399839598685503</v>
+        <v>0.0001071553851943463</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.607136361300945e-07</v>
+        <v>9.706618584459648e-05</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0001298302668146789</v>
+        <v>1.742111635394394e-05</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.001451467047445476</v>
+        <v>1.19388696475653e-05</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0007968264981172979</v>
+        <v>4.220296614221297e-05</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.079819205391686e-05</v>
+        <v>6.329915049718693e-05</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.001326716504991055</v>
+        <v>0.0001040091592585668</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.001075900392606854</v>
+        <v>2.751929241640028e-05</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0004369622329249978</v>
+        <v>5.018904630560428e-06</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0003008726926054806</v>
+        <v>8.457472722511739e-05</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0007872577989473939</v>
+        <v>4.691879075835459e-05</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.001251990091986954</v>
+        <v>1.463403987145284e-05</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.003229472786188126</v>
+        <v>0.0001825780491344631</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0005826179403811693</v>
+        <v>0.0001218456527567469</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.001084884745068848</v>
+        <v>0.0002143035235349089</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0002724955265875906</v>
+        <v>4.249445191817358e-05</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0009476900449953973</v>
+        <v>0.0001946653064806014</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0004630947660189122</v>
+        <v>4.176245420239866e-05</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.0006566349184140563</v>
+        <v>4.374637683213223e-06</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0001884716184576973</v>
+        <v>4.786880890605971e-05</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.000506566371768713</v>
+        <v>7.871647540014237e-06</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.001668739947490394</v>
+        <v>0.0001893987209768966</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0006324187270365655</v>
+        <v>6.674363248748705e-06</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0008160257712006569</v>
+        <v>0.0001594866043888032</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0002153908717446029</v>
+        <v>1.349684043816524e-05</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.432300632586703e-05</v>
+        <v>6.068441871320829e-05</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0005288496613502502</v>
+        <v>3.596280521378503e-06</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0003700572706293315</v>
+        <v>1.36275812110398e-05</v>
       </c>
       <c r="CL14" t="n">
-        <v>4.851521225646138e-06</v>
+        <v>2.143839992641006e-05</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.003509005298838019</v>
+        <v>9.123913332587108e-05</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0004230664053466171</v>
+        <v>0.0001509194262325764</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0002392250607954338</v>
+        <v>0.0002851547615136951</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0002298566250829026</v>
+        <v>0.0002075458614854142</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0005660320748575032</v>
+        <v>0.0001309928338741884</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.003279546508565545</v>
+        <v>9.98809264274314e-05</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0005371016450226307</v>
+        <v>6.732359179295599e-05</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0006366465240716934</v>
+        <v>0.0001275109825655818</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.001879324438050389</v>
+        <v>2.508488978492096e-05</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0004044591332785785</v>
+        <v>7.818017365934793e-06</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.001715963589958847</v>
+        <v>0.000183324416866526</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.001062344177626073</v>
+        <v>2.72296729235677e-05</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0009984193602576852</v>
+        <v>0.0001524361287010834</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0001712945086183026</v>
+        <v>3.413366721360944e-05</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0002512782521080226</v>
+        <v>6.826242315582931e-05</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0002959732955787331</v>
+        <v>2.668940851435764e-06</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0006426887703128159</v>
+        <v>3.359222318977118e-05</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.459537401795387e-05</v>
+        <v>1.245230123458896e-06</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.001529542380012572</v>
+        <v>4.876080492977053e-05</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.002684004604816437</v>
+        <v>9.772474004421383e-05</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.002796387765556574</v>
+        <v>4.710859866463579e-05</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.001353677827864885</v>
+        <v>0.0001326297206105664</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0005594959948211908</v>
+        <v>4.855957013205625e-05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0006031273514963686</v>
+        <v>0.0003133008722215891</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.00193965039215982</v>
+        <v>1.227930260938592e-05</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.001785098691470921</v>
+        <v>0.0002535942767281085</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.000425539561547339</v>
+        <v>0.0001148318260675296</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0009103637421503663</v>
+        <v>1.613991662452463e-05</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.976717612706125e-05</v>
+        <v>0.0001568397856317461</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.000103181075246539</v>
+        <v>1.708495983621106e-05</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.002077730838209391</v>
+        <v>6.478740397142246e-05</v>
       </c>
       <c r="DR14" t="n">
-        <v>3.192744770785794e-05</v>
+        <v>1.881956450233702e-05</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.000205895077669993</v>
+        <v>1.506684475316433e-05</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0005351377185434103</v>
+        <v>8.234356209868565e-05</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0006559262983500957</v>
+        <v>0.0001145124551840127</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0008687451481819153</v>
+        <v>0.0001644829462748021</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.001098933047614992</v>
+        <v>1.165061348729068e-05</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0008458941010758281</v>
+        <v>2.631179631862324e-05</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0002020143438130617</v>
+        <v>0.0001202326166094281</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.000673678470775485</v>
+        <v>0.0001255376264452934</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.00112084427382797</v>
+        <v>5.881674223928712e-05</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.001368378172628582</v>
+        <v>0.0001401158515363932</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.001868485589511693</v>
+        <v>1.352838535240153e-05</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0003822674043476582</v>
+        <v>0.0003348162572365254</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0003745817230083048</v>
+        <v>0.0001992646721191704</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.00168993475381285</v>
+        <v>7.238949910970405e-05</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.001568076550029218</v>
+        <v>0.000102654128568247</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.002162669785320759</v>
+        <v>0.0001071805454557762</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.001061694929376245</v>
+        <v>0.0001380553876515478</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0002700230979826301</v>
+        <v>7.204116991488263e-05</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0001137922881753184</v>
+        <v>6.084280175855383e-05</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0001748102658893913</v>
+        <v>1.514390532975085e-05</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0001359287707600743</v>
+        <v>1.209515448863385e-05</v>
       </c>
       <c r="EN14" t="n">
-        <v>8.775663445703685e-05</v>
+        <v>8.935974619816989e-06</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.0004200650146231055</v>
+        <v>4.261731010046788e-05</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.001986056799069047</v>
+        <v>0.0001991155440919101</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0002528196782805026</v>
+        <v>4.18136187363416e-05</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.001686095376498997</v>
+        <v>8.382688974961638e-05</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0007854608120396733</v>
+        <v>1.485898064856883e-05</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0002907766320277005</v>
+        <v>4.719100979855284e-05</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.001108126947656274</v>
+        <v>8.860269736032933e-05</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0004775901325047016</v>
+        <v>6.124699575593695e-05</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.0005066010635346174</v>
+        <v>0.0001300561125390232</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.0008425245760008693</v>
+        <v>7.190934411482885e-06</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.001741907093673944</v>
+        <v>0.0002005029527936131</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.000805510557256639</v>
+        <v>1.704598798824009e-05</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.001054974156431854</v>
+        <v>0.0001835772854974493</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.0001735525293042883</v>
+        <v>1.125340531871188e-05</v>
       </c>
       <c r="FC14" t="n">
-        <v>5.016204522689804e-05</v>
+        <v>6.518392910948023e-05</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0004741926677525043</v>
+        <v>2.00276990653947e-05</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0006360029219649732</v>
+        <v>5.081118433736265e-05</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0002110146451741457</v>
+        <v>2.468871025484987e-05</v>
       </c>
       <c r="FG14" t="n">
-        <v>3.598097828216851e-05</v>
+        <v>2.511427737772465e-05</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.0001881558855529875</v>
+        <v>7.979515066836029e-05</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0006256980705074966</v>
+        <v>6.465689693868626e-06</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.001481340616010129</v>
+        <v>5.674119529430754e-05</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0008406962151639163</v>
+        <v>0.00011386965343263</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0005473954952321947</v>
+        <v>2.472207779646851e-05</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.0003659081703517586</v>
+        <v>5.907544618821703e-06</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0002485981094650924</v>
+        <v>9.380339179188013e-05</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0003075600252486765</v>
+        <v>7.565126725239679e-05</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.002734736539423466</v>
+        <v>0.0001331560633843765</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0005036522634327412</v>
+        <v>0.0002621551684569567</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.003370293183252215</v>
+        <v>0.0002122427977155894</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.0004270226927474141</v>
+        <v>0.0001368101802654564</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0004379418096505105</v>
+        <v>0.0001735330879455432</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0008394602336920798</v>
+        <v>2.25179610424675e-06</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.001665729796513915</v>
+        <v>4.334126788307913e-05</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0008176167029887438</v>
+        <v>7.934344466775656e-05</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.001244687358848751</v>
+        <v>0.0001305987971136346</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0005766130634583533</v>
+        <v>1.84764157893369e-05</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0005887315492145717</v>
+        <v>1.283766141568776e-05</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0005112133221700788</v>
+        <v>2.854275953723118e-05</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0002489428443368524</v>
+        <v>0.0001392480044160038</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0005637072026729584</v>
+        <v>0.0001134716294473037</v>
       </c>
       <c r="GD14" t="n">
-        <v>5.121189315104857e-05</v>
+        <v>0.0001381593610858545</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.00154905254021287</v>
+        <v>0.0001834161957958713</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.000383660604711622</v>
+        <v>3.134214421152137e-05</v>
       </c>
       <c r="GG14" t="n">
-        <v>8.10649071354419e-05</v>
+        <v>3.929318700102158e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.01028784364461899</v>
+        <v>0.05309548601508141</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2407517433166504</v>
+        <v>0.971426248550415</v>
       </c>
       <c r="C15" t="n">
-        <v>0.07432901114225388</v>
+        <v>0.1872518062591553</v>
       </c>
       <c r="D15" t="n">
-        <v>0.04409849643707275</v>
+        <v>0.5323891639709473</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04622342437505722</v>
+        <v>0.2694117724895477</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0483844168484211</v>
+        <v>0.2638624906539917</v>
       </c>
       <c r="G15" t="n">
-        <v>0.004563890397548676</v>
+        <v>0.3795044124126434</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05089874193072319</v>
+        <v>0.3694632649421692</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03542245551943779</v>
+        <v>0.09503825008869171</v>
       </c>
       <c r="J15" t="n">
-        <v>0.05111562088131905</v>
+        <v>0.1152950003743172</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2298000156879425</v>
+        <v>1.048564553260803</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05489135533571243</v>
+        <v>0.1798191368579865</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06451290845870972</v>
+        <v>0.7967599034309387</v>
       </c>
       <c r="N15" t="n">
-        <v>0.00620940700173378</v>
+        <v>0.412653386592865</v>
       </c>
       <c r="O15" t="n">
-        <v>0.001380856614559889</v>
+        <v>0.02770231291651726</v>
       </c>
       <c r="P15" t="n">
-        <v>0.01730671152472496</v>
+        <v>0.4108876585960388</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.05987505614757538</v>
+        <v>0.3450199961662292</v>
       </c>
       <c r="R15" t="n">
-        <v>0.08484338223934174</v>
+        <v>0.06991949677467346</v>
       </c>
       <c r="S15" t="n">
-        <v>0.03126472234725952</v>
+        <v>0.03205088153481483</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03788886964321136</v>
+        <v>0.01313734333962202</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03958923742175102</v>
+        <v>0.04280370846390724</v>
       </c>
       <c r="V15" t="n">
-        <v>0.03579510003328323</v>
+        <v>0.003924783319234848</v>
       </c>
       <c r="W15" t="n">
-        <v>0.009378900751471519</v>
+        <v>0.00897948257625103</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0033971699886024</v>
+        <v>0.009138000197708607</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0007848972454667091</v>
+        <v>0.1376371681690216</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.02315444312989712</v>
+        <v>0.1128370240330696</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01174461748450994</v>
+        <v>0.1998868435621262</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.04740123078227043</v>
+        <v>0.1477637737989426</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.03456167504191399</v>
+        <v>0.005959749221801758</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.02159262448549271</v>
+        <v>0.135615810751915</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.04969463497400284</v>
+        <v>0.256767749786377</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02438456378877163</v>
+        <v>0.009964020922780037</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01098793372511864</v>
+        <v>0.1343991160392761</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.01679368130862713</v>
+        <v>0.1727696806192398</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0003366223536431789</v>
+        <v>0.0544232651591301</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.03760354965925217</v>
+        <v>0.1552861034870148</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.005915478803217411</v>
+        <v>0.1061505526304245</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.03053516708314419</v>
+        <v>0.2809678912162781</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.005583522375673056</v>
+        <v>0.08480231463909149</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.01329632475972176</v>
+        <v>0.1101686209440231</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.003269143402576447</v>
+        <v>0.2167661637067795</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.05231895297765732</v>
+        <v>0.05317132547497749</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.01676967367529869</v>
+        <v>0.04866337776184082</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.003590576350688934</v>
+        <v>0.02297093719244003</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.01093422528356314</v>
+        <v>0.004581782966852188</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.0822080671787262</v>
+        <v>0.1494704335927963</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1083494573831558</v>
+        <v>0.4844712018966675</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.03787557035684586</v>
+        <v>0.02332250401377678</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.02156017161905766</v>
+        <v>0.1532618850469589</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.03609611093997955</v>
+        <v>0.2778187096118927</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.05311716720461845</v>
+        <v>0.07420826703310013</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.02162483334541321</v>
+        <v>0.05133447796106339</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.002931075170636177</v>
+        <v>0.1040202528238297</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.02283902652561665</v>
+        <v>0.07479265332221985</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.07779607176780701</v>
+        <v>0.09561388194561005</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.05673006549477577</v>
+        <v>0.08555202186107635</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.02078220061957836</v>
+        <v>0.1114114001393318</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.03376313298940659</v>
+        <v>0.119551919400692</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.113397441804409</v>
+        <v>0.01756482198834419</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.004828204400837421</v>
+        <v>0.0994005873799324</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.03904921188950539</v>
+        <v>0.007801808416843414</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.1001574173569679</v>
+        <v>0.09050711989402771</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.02206504158675671</v>
+        <v>0.04106751084327698</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.03620315343141556</v>
+        <v>0.1156451404094696</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.03093100339174271</v>
+        <v>0.103382520377636</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.05645762011408806</v>
+        <v>0.0998619943857193</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.001527807209640741</v>
+        <v>0.0634453296661377</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.05069062858819962</v>
+        <v>0.03367696702480316</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01130802277475595</v>
+        <v>0.03501088917255402</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.03771670907735825</v>
+        <v>0.07100115716457367</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.01627601683139801</v>
+        <v>0.07995517551898956</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.019489586353302</v>
+        <v>0.1290915608406067</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.06280241161584854</v>
+        <v>0.1066914796829224</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.06749085336923599</v>
+        <v>0.4125486016273499</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.003132734214887023</v>
+        <v>0.0194411613047123</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.02559966035187244</v>
+        <v>0.115889847278595</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.02303499542176723</v>
+        <v>0.007542135193943977</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.01015779562294483</v>
+        <v>0.0534415990114212</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.0153284315019846</v>
+        <v>0.1666474342346191</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.03258286416530609</v>
+        <v>7.325410842895508e-05</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.04085354506969452</v>
+        <v>0.1410974264144897</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.01963960006833076</v>
+        <v>0.007484674453735352</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.03317956626415253</v>
+        <v>0.3014811873435974</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.02316978946328163</v>
+        <v>0.07840366661548615</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.01662617549300194</v>
+        <v>0.1439301669597626</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.01793573796749115</v>
+        <v>0.0848526731133461</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.01743914186954498</v>
+        <v>0.1039390191435814</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.0002034036442637444</v>
+        <v>0.02052228525280952</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.007826090790331364</v>
+        <v>0.04063255712389946</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.01283296104520559</v>
+        <v>0.03412197157740593</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.002967097796499729</v>
+        <v>0.1446065008640289</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.01389603968709707</v>
+        <v>0.2877099215984344</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.0212190393358469</v>
+        <v>0.07115799188613892</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.0208035409450531</v>
+        <v>0.04384750500321388</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.02986715920269489</v>
+        <v>0.2424251735210419</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.01872923225164413</v>
+        <v>0.1158315911889076</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.01580126769840717</v>
+        <v>0.3052737414836884</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.01872895658016205</v>
+        <v>0.2117771655321121</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.03529863059520721</v>
+        <v>0.05930681526660919</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.0151958242058754</v>
+        <v>0.004927635192871094</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.03569201752543449</v>
+        <v>0.296405166387558</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.01370015181601048</v>
+        <v>0.05967588722705841</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.01861237175762653</v>
+        <v>0.1811240017414093</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.007701646536588669</v>
+        <v>0.1288467943668365</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.003463420551270247</v>
+        <v>0.1110630184412003</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.007906089536845684</v>
+        <v>0.007661060895770788</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.005504528991878033</v>
+        <v>0.04952157661318779</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.00887581892311573</v>
+        <v>0.05798862129449844</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.01527511887252331</v>
+        <v>0.1386874169111252</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1466143429279327</v>
+        <v>0.06689633429050446</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.03380373492836952</v>
+        <v>0.159981295466423</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.06096784025430679</v>
+        <v>0.2016977965831757</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.007455742917954922</v>
+        <v>0.01915626972913742</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.1127905547618866</v>
+        <v>0.5085868835449219</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.0288080982863903</v>
+        <v>0.0525633916258812</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.01197973638772964</v>
+        <v>0.06602901220321655</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.02551935240626335</v>
+        <v>0.0309298112988472</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.03785547614097595</v>
+        <v>0.03175760060548782</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.02744903601706028</v>
+        <v>0.21961909532547</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.1019902750849724</v>
+        <v>0.03721635043621063</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.04815464094281197</v>
+        <v>0.157876580953598</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.05578592047095299</v>
+        <v>0.04707217961549759</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.04981553554534912</v>
+        <v>0.004700162447988987</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.02779280953109264</v>
+        <v>0.1363274604082108</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.007997935637831688</v>
+        <v>0.007876142859458923</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.01254038140177727</v>
+        <v>0.2579781413078308</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.003297906834632158</v>
+        <v>0.003292478621006012</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.01917126588523388</v>
+        <v>0.03355048596858978</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.02147985622286797</v>
+        <v>0.1049749851226807</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.04444880783557892</v>
+        <v>0.01486123725771904</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.002678877208381891</v>
+        <v>0.221586287021637</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.08079768717288971</v>
+        <v>0.3119155764579773</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.01799041032791138</v>
+        <v>0.06614142656326294</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.03529368340969086</v>
+        <v>0.2386316359043121</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.03392127901315689</v>
+        <v>0.05499055981636047</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.01896984130144119</v>
+        <v>0.002770133316516876</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.02269413694739342</v>
+        <v>0.3275632262229919</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.008205145597457886</v>
+        <v>0.04161040484905243</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.008811358362436295</v>
+        <v>0.06285451352596283</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.01473458111286163</v>
+        <v>0.04835359752178192</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.03971594944596291</v>
+        <v>0.0973806232213974</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.01058596931397915</v>
+        <v>0.06695310026407242</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.02415870316326618</v>
+        <v>0.08263088762760162</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.01720018684864044</v>
+        <v>0.002129008993506432</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.01499779243022203</v>
+        <v>0.1354964226484299</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.005829587578773499</v>
+        <v>0.3079022169113159</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.00673664128407836</v>
+        <v>0.01254281960427761</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.0140088964253664</v>
+        <v>0.2313735485076904</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.03059963509440422</v>
+        <v>0.08626799285411835</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.03898577392101288</v>
+        <v>0.006129435263574123</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.01211908459663391</v>
+        <v>0.1689570099115372</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.03500732779502869</v>
+        <v>0.1458055973052979</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.002179648727178574</v>
+        <v>0.1378654688596725</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.01300917007029057</v>
+        <v>0.01983505114912987</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.0406843014061451</v>
+        <v>0.3575942516326904</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.02441555261611938</v>
+        <v>0.06230813264846802</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.02086981758475304</v>
+        <v>0.1451794058084488</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.005904517602175474</v>
+        <v>0.08852232992649078</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.008865168318152428</v>
+        <v>0.1171472445130348</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.01141947321593761</v>
+        <v>0.001771620940417051</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.004309151321649551</v>
+        <v>0.06661529839038849</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.01653436198830605</v>
+        <v>0.0671902671456337</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.01147788763046265</v>
+        <v>0.06368721276521683</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.02732993476092815</v>
+        <v>0.0181233286857605</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.03054147399961948</v>
+        <v>0.08803324401378632</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.008271520026028156</v>
+        <v>0.01184148155152798</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.01830568164587021</v>
+        <v>0.1132886707782745</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.0387067086994648</v>
+        <v>0.04147388786077499</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.01871258392930031</v>
+        <v>0.02645723521709442</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.0009703752584755421</v>
+        <v>0.2040657103061676</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.01685154810547829</v>
+        <v>0.222694143652916</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.1044961214065552</v>
+        <v>0.08672653883695602</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.08270071446895599</v>
+        <v>0.07442794740200043</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.07586038112640381</v>
+        <v>0.1433213800191879</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.04868075996637344</v>
+        <v>0.5551274418830872</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.03957310691475868</v>
+        <v>0.1489404290914536</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.02980263531208038</v>
+        <v>0.1107313185930252</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.020555280148983</v>
+        <v>0.3064817488193512</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.005037039984017611</v>
+        <v>0.1102570816874504</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.01933642476797104</v>
+        <v>0.02695906162261963</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.02052573300898075</v>
+        <v>0.04305887967348099</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.02642740309238434</v>
+        <v>0.1708373725414276</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.0323384702205658</v>
+        <v>0.04504933208227158</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.009398858994245529</v>
+        <v>0.07293407618999481</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.1070182844996452</v>
+        <v>0.1433994472026825</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.06685334444046021</v>
+        <v>0.1677420437335968</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.0458427295088768</v>
+        <v>0.1513534486293793</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.008065562695264816</v>
+        <v>0.1786859929561615</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.004427622072398663</v>
+        <v>0.01234281249344349</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.001940644928254187</v>
+        <v>1.099130440707086e-05</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0007836328586563468</v>
+        <v>5.720159970223904e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>0.005424166098237038</v>
+        <v>0.0001324637414654717</v>
       </c>
       <c r="D16" t="n">
-        <v>0.004241309594362974</v>
+        <v>0.0001387688389513642</v>
       </c>
       <c r="E16" t="n">
-        <v>0.003430936019867659</v>
+        <v>2.791815131786279e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001347145065665245</v>
+        <v>6.372737698256969e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001512803602963686</v>
+        <v>2.403101098025218e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0004483723314478993</v>
+        <v>5.346528632799163e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00147357489913702</v>
+        <v>9.417269757250324e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001678086933679879</v>
+        <v>2.133668749593198e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0006897248676978052</v>
+        <v>5.689341196557507e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004336296580731869</v>
+        <v>0.0001695616665529087</v>
       </c>
       <c r="M16" t="n">
-        <v>0.004481583368033171</v>
+        <v>0.0001846233499236405</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0008620326989330351</v>
+        <v>2.882469925680198e-05</v>
       </c>
       <c r="O16" t="n">
-        <v>0.001032154308632016</v>
+        <v>8.177090785466135e-05</v>
       </c>
       <c r="P16" t="n">
-        <v>0.000973094895016402</v>
+        <v>1.540605808258988e-05</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.907615508884192e-05</v>
+        <v>0.0001041938958223909</v>
       </c>
       <c r="R16" t="n">
-        <v>0.00223807105794549</v>
+        <v>4.839649045607075e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0005754177691414952</v>
+        <v>1.519987199571915e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0009735169587656856</v>
+        <v>6.063885393814417e-07</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0009001068538054824</v>
+        <v>2.932640563813038e-05</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0008529489277862012</v>
+        <v>2.448724262649193e-05</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0005921403062529862</v>
+        <v>2.68568310275441e-05</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0003384758601896465</v>
+        <v>4.163610719842836e-05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0006150910048745573</v>
+        <v>1.871596759883687e-05</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.000615636061411351</v>
+        <v>7.964774340507574e-06</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0001165692301583476</v>
+        <v>3.962816117564216e-05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.001733011798933148</v>
+        <v>2.344062886550091e-05</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0004186437872704118</v>
+        <v>2.277366729686037e-05</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0001725502515910193</v>
+        <v>9.794449397304561e-06</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.00169046560768038</v>
+        <v>7.010393164819106e-05</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.001229697256349027</v>
+        <v>6.229547580005601e-06</v>
       </c>
       <c r="AG16" t="n">
-        <v>5.100642738398165e-05</v>
+        <v>1.184870870929444e-05</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0001107537827920169</v>
+        <v>1.40674728754675e-05</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0007400678587146103</v>
+        <v>4.515060936682858e-05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0008735440205782652</v>
+        <v>2.742710603342857e-05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0005085358279757202</v>
+        <v>8.859172339725774e-06</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.867701161652803e-05</v>
+        <v>2.631024472066201e-06</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.867559669539332e-05</v>
+        <v>3.531724723870866e-05</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.0002893874188885093</v>
+        <v>2.712251807679422e-05</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.001079939771443605</v>
+        <v>5.002557372790761e-05</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.000205748830921948</v>
+        <v>1.03146394394571e-05</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.0004582849214784801</v>
+        <v>2.461667281750124e-05</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.0001277374685741961</v>
+        <v>2.438227602397092e-05</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0003384562442079186</v>
+        <v>4.099097714060917e-05</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.001672412035986781</v>
+        <v>3.405331517569721e-05</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.00197251420468092</v>
+        <v>1.099890141631477e-05</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.002881304826587439</v>
+        <v>0.0001666581956669688</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.003587491344660521</v>
+        <v>0.0001172565171145834</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.0007278397097252309</v>
+        <v>4.430571607372258e-06</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0008510386687703431</v>
+        <v>9.110024257097393e-05</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.001072114333510399</v>
+        <v>8.399052603635937e-05</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.001039177644997835</v>
+        <v>3.49062102031894e-05</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0005490191979333758</v>
+        <v>7.620284304721281e-05</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.001466139918193221</v>
+        <v>3.924167685909197e-05</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.002806621138006449</v>
+        <v>1.905474891827907e-05</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0008888319716788828</v>
+        <v>2.491673876647837e-05</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.001535905874334276</v>
+        <v>2.267203672090545e-05</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.001382606336846948</v>
+        <v>1.348567002423806e-05</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.002156517235562205</v>
+        <v>4.339770384831354e-05</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.001204599859192967</v>
+        <v>6.738088268321007e-05</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.0003912892425432801</v>
+        <v>5.854096889379434e-05</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.001732073491439223</v>
+        <v>4.983721373719163e-05</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.0001554047630634159</v>
+        <v>4.525789336184971e-05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0005930118495598435</v>
+        <v>4.597762745106593e-05</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.000785736832767725</v>
+        <v>4.614862064045155e-06</v>
       </c>
       <c r="BO16" t="n">
-        <v>5.825109838042408e-05</v>
+        <v>3.007615305250511e-05</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.0006493370165117085</v>
+        <v>4.542525130091235e-05</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.0002448419691063464</v>
+        <v>9.140408110397402e-06</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.0001440444320905954</v>
+        <v>6.51135815132875e-06</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.0007715169922448695</v>
+        <v>7.487426046282053e-05</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.0003543170751072466</v>
+        <v>1.439306106476579e-05</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.0004338709404692054</v>
+        <v>9.487785064266063e-07</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.001227831817232072</v>
+        <v>2.74575904768426e-05</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.002005850663408637</v>
+        <v>9.847685578279197e-05</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.002415986265987158</v>
+        <v>0.0001122180983657017</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.001138628693297505</v>
+        <v>9.896532901620958e-06</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0003573236172087491</v>
+        <v>3.770732291741297e-05</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.0003665828844532371</v>
+        <v>2.378767021582462e-05</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.0007240429986268282</v>
+        <v>2.357462108193431e-05</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.0008754605078138411</v>
+        <v>4.704228922491893e-05</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.0006133487331680954</v>
+        <v>3.083988303842489e-06</v>
       </c>
       <c r="CE16" t="n">
-        <v>4.437251482158899e-05</v>
+        <v>1.107646494347136e-05</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.001316740992479026</v>
+        <v>4.507420453592204e-05</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.0007441614870913327</v>
+        <v>5.363755190046504e-05</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.000746953533962369</v>
+        <v>1.142978908319492e-05</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.0002855350612662733</v>
+        <v>2.229360507044476e-05</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.0004948971327394247</v>
+        <v>4.327043825469445e-07</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.0004280165303498507</v>
+        <v>7.715739229752216e-06</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.0001784911000868306</v>
+        <v>1.168660583061865e-05</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.001911562983877957</v>
+        <v>5.964472620689776e-06</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.001580640207976103</v>
+        <v>9.476817467657384e-06</v>
       </c>
       <c r="CO16" t="n">
-        <v>2.92710610665381e-05</v>
+        <v>6.332717020995915e-05</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0008086480665951967</v>
+        <v>0.0001034233573591337</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.0003918526053894311</v>
+        <v>5.630079613183625e-06</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0005399271030910313</v>
+        <v>4.877299579675309e-05</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.00044848961988464</v>
+        <v>9.532341209705919e-06</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.001906434074044228</v>
+        <v>1.301439806411508e-05</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.0004118373326491565</v>
+        <v>3.457091224845499e-05</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.0004684184968937188</v>
+        <v>6.332266366371186e-06</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.0004318640858400613</v>
+        <v>2.570451033534482e-05</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.0009292477043345571</v>
+        <v>3.771765841520391e-05</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.0008315108134411275</v>
+        <v>4.768371945829131e-05</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.0004088668792974204</v>
+        <v>1.459755003452301e-05</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.0001586735888849944</v>
+        <v>3.346794619574212e-05</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.0004803854390047491</v>
+        <v>3.494254997349344e-06</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.0003265505947638303</v>
+        <v>7.989102414285298e-06</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.0001124227856053039</v>
+        <v>1.322018670180114e-05</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.0002241733891423792</v>
+        <v>4.721074219560251e-05</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.001710825366899371</v>
+        <v>4.664241714635864e-05</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.002068309113383293</v>
+        <v>1.087081182049587e-05</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0004453820001799613</v>
+        <v>2.236322688986547e-05</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0002310526906512678</v>
+        <v>1.892960790428333e-05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.0001297011040151119</v>
+        <v>1.416260147379944e-05</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.001772144809365273</v>
+        <v>5.241924736765213e-05</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.0005076058441773057</v>
+        <v>4.786717545357533e-05</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0005948789184913039</v>
+        <v>5.743162182625383e-05</v>
       </c>
       <c r="DN16" t="n">
-        <v>7.137792999856174e-05</v>
+        <v>1.433476427337155e-05</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.001346036093309522</v>
+        <v>1.000995234790025e-05</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.0009215110912919044</v>
+        <v>2.273634163429961e-05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0001947935670614243</v>
+        <v>1.602605334483087e-05</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.001768043846823275</v>
+        <v>3.890263542416506e-05</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.0008334890007972717</v>
+        <v>1.236525167769287e-05</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.0007154096383601427</v>
+        <v>2.231250255135819e-05</v>
       </c>
       <c r="DU16" t="n">
-        <v>3.906944766640663e-05</v>
+        <v>1.757072459440678e-05</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.001289713196456432</v>
+        <v>2.992382542288397e-05</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.0003930206003133208</v>
+        <v>6.290668534347787e-05</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.001803657622076571</v>
+        <v>4.141372119192965e-05</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.0004864934307988733</v>
+        <v>1.864131263573654e-05</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.0003506617795210332</v>
+        <v>1.073169414667063e-06</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0009895735420286655</v>
+        <v>3.583068246371113e-05</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.000986642437055707</v>
+        <v>4.357660873210989e-05</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.693246667855419e-05</v>
+        <v>1.933855492097791e-05</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.0004159039235673845</v>
+        <v>3.33259449689649e-05</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.0001954190811375156</v>
+        <v>1.937611159519292e-05</v>
       </c>
       <c r="EF16" t="n">
-        <v>7.124655530788004e-05</v>
+        <v>3.124224531347863e-05</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0005429349257610738</v>
+        <v>2.232270344393328e-05</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.001388640492223203</v>
+        <v>1.78974587470293e-05</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.001580947078764439</v>
+        <v>6.751615728717297e-05</v>
       </c>
       <c r="EJ16" t="n">
-        <v>1.106459967559204e-05</v>
+        <v>1.967227763088886e-05</v>
       </c>
       <c r="EK16" t="n">
-        <v>2.320178646186832e-05</v>
+        <v>6.349993782350793e-06</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.0005255861324258149</v>
+        <v>1.127610971707327e-06</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.0001049562415573746</v>
+        <v>5.117483397043543e-07</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.0006203787634149194</v>
+        <v>8.616607374278829e-07</v>
       </c>
       <c r="EO16" t="n">
-        <v>5.860271630808711e-05</v>
+        <v>9.937805316440063e-07</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.001268016174435616</v>
+        <v>2.699035030673258e-05</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0006558119785040617</v>
+        <v>1.911696017486975e-05</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0009180654305964708</v>
+        <v>3.350668339408003e-05</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.0006899108993820846</v>
+        <v>1.035020977724344e-05</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.000164582539582625</v>
+        <v>5.737128230975941e-05</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.0006550580728799105</v>
+        <v>9.196170140057802e-06</v>
       </c>
       <c r="EV16" t="n">
-        <v>6.432411464629695e-05</v>
+        <v>4.48706814495381e-05</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.000890774535946548</v>
+        <v>1.346644876321079e-05</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.000478508765809238</v>
+        <v>5.372919531509979e-08</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.0005411448073573411</v>
+        <v>1.564812191645615e-05</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.001244725310243666</v>
+        <v>4.407982851262204e-05</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.0007857878226786852</v>
+        <v>6.431840301956981e-05</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.0005293726571835577</v>
+        <v>1.151941614807583e-05</v>
       </c>
       <c r="FC16" t="n">
-        <v>8.86127381818369e-05</v>
+        <v>2.88915507553611e-05</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.0004357514262665063</v>
+        <v>4.42221607954707e-06</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.0003281071549281478</v>
+        <v>2.301033964613453e-05</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.0003445648471824825</v>
+        <v>1.558310577820521e-05</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.0001804527564672753</v>
+        <v>1.231563237524824e-05</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.0009862004080787301</v>
+        <v>2.701280027395114e-05</v>
       </c>
       <c r="FI16" t="n">
-        <v>1.843195059336722e-05</v>
+        <v>1.319254261034075e-05</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.0007936906768009067</v>
+        <v>3.103630660916679e-05</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.0003930855600629002</v>
+        <v>2.504929943825118e-05</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.0006974975694902241</v>
+        <v>3.990684490418062e-05</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.0004099537909496576</v>
+        <v>9.57827978709247e-07</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.0007143021794036031</v>
+        <v>7.907328836154193e-06</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.0004432220885064453</v>
+        <v>2.498629783076467e-06</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0009679358918219805</v>
+        <v>9.551218681735918e-05</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.0006970454705879092</v>
+        <v>5.85437192057725e-06</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.00137997476849705</v>
+        <v>2.610628143884242e-05</v>
       </c>
       <c r="FS16" t="n">
-        <v>6.945949280634522e-05</v>
+        <v>1.573615372763015e-05</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.0002660626778379083</v>
+        <v>6.239503272809088e-05</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0006493350374512374</v>
+        <v>3.825252497335896e-05</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.0001854190195444971</v>
+        <v>4.353907570475712e-05</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.000627756176982075</v>
+        <v>3.767885209526867e-05</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.0003389260964468122</v>
+        <v>2.243151175207458e-05</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0002946047170553356</v>
+        <v>3.237400960642844e-05</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.0009633840527385473</v>
+        <v>2.060984661511611e-05</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.0002214991836808622</v>
+        <v>1.302203781960998e-05</v>
       </c>
       <c r="GB16" t="n">
-        <v>8.677876758156344e-05</v>
+        <v>6.570178811671212e-05</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.001028981292620301</v>
+        <v>1.768547190295067e-05</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.001545144594274461</v>
+        <v>3.656259286799468e-05</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0006669668946415186</v>
+        <v>8.579567293054424e-06</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.0001164838613476604</v>
+        <v>2.608295835671015e-05</v>
       </c>
       <c r="GG16" t="n">
-        <v>4.945537511957809e-06</v>
+        <v>4.520147922448814e-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.144135239883326e-06</v>
+        <v>3.63124163413886e-05</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0004247194156050682</v>
+        <v>0.0002725191006902605</v>
       </c>
       <c r="C17" t="n">
-        <v>7.887799438321963e-05</v>
+        <v>5.17314656462986e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001762864267220721</v>
+        <v>0.0001412053825333714</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0002668102097231895</v>
+        <v>3.825221938313916e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0002014251949731261</v>
+        <v>0.000202748051378876</v>
       </c>
       <c r="G17" t="n">
-        <v>7.921770156826824e-05</v>
+        <v>3.258468495914713e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0001100318477256224</v>
+        <v>0.0001622035197215155</v>
       </c>
       <c r="I17" t="n">
-        <v>3.230910078855231e-05</v>
+        <v>1.504520696471445e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>4.903999069938436e-06</v>
+        <v>8.397846977459267e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0003251529997214675</v>
+        <v>0.0003807085449807346</v>
       </c>
       <c r="L17" t="n">
-        <v>1.79852268047398e-05</v>
+        <v>3.185319656040519e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0001134737831307575</v>
+        <v>0.0002266443334519863</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0002079705009236932</v>
+        <v>0.0001418286265106872</v>
       </c>
       <c r="O17" t="n">
-        <v>0.000195918430108577</v>
+        <v>0.0001983224356081337</v>
       </c>
       <c r="P17" t="n">
-        <v>8.533387881470844e-05</v>
+        <v>7.884683145675808e-05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.492478779458907e-05</v>
+        <v>5.199751831241883e-05</v>
       </c>
       <c r="R17" t="n">
-        <v>3.629837738117203e-05</v>
+        <v>5.210960807744414e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>5.730226348532597e-06</v>
+        <v>4.488425474846736e-05</v>
       </c>
       <c r="T17" t="n">
-        <v>7.144099799916148e-05</v>
+        <v>2.774319182208274e-05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.009912466543028e-05</v>
+        <v>3.68037581210956e-05</v>
       </c>
       <c r="V17" t="n">
-        <v>5.840662197442725e-05</v>
+        <v>1.559987140353769e-05</v>
       </c>
       <c r="W17" t="n">
-        <v>4.903901208308525e-05</v>
+        <v>4.856502073380398e-06</v>
       </c>
       <c r="X17" t="n">
-        <v>7.049219129839912e-05</v>
+        <v>1.862282988440711e-05</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.532710823288653e-05</v>
+        <v>4.26326078013517e-05</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.281628182274289e-05</v>
+        <v>3.37284327542875e-05</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.047526479349472e-05</v>
+        <v>2.66461956925923e-05</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.558073174441233e-05</v>
+        <v>6.343134009512141e-05</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.261312228161842e-05</v>
+        <v>7.611150795128196e-05</v>
       </c>
       <c r="AD17" t="n">
-        <v>6.156281415314879e-06</v>
+        <v>2.001460597966798e-05</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.432932135183364e-05</v>
+        <v>3.043211108888499e-05</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.523613173048943e-05</v>
+        <v>7.434921280946583e-05</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.100556932622567e-05</v>
+        <v>7.722813279542606e-06</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.043735680170357e-05</v>
+        <v>1.580261596245691e-05</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.865081427851692e-05</v>
+        <v>6.489341467386112e-05</v>
       </c>
       <c r="AJ17" t="n">
-        <v>6.238335117814131e-06</v>
+        <v>2.136983857781161e-05</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.912545096478425e-05</v>
+        <v>4.114941475563683e-06</v>
       </c>
       <c r="AL17" t="n">
-        <v>9.378769755130634e-05</v>
+        <v>7.224393357319059e-06</v>
       </c>
       <c r="AM17" t="n">
-        <v>5.720271474274341e-07</v>
+        <v>2.782584851956926e-05</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.580961907166056e-05</v>
+        <v>2.030483301496133e-07</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.023613913275767e-05</v>
+        <v>5.895632784813643e-05</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.488536357413977e-05</v>
+        <v>5.179374420549721e-05</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.346679245121777e-06</v>
+        <v>5.754547601100057e-05</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.950765676563606e-05</v>
+        <v>9.281172970077023e-05</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.432847345015034e-05</v>
+        <v>2.74588746833615e-05</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.860055221593939e-05</v>
+        <v>5.368485653889365e-05</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.0002843094698619097</v>
+        <v>0.0002831870515365154</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.668456651619636e-05</v>
+        <v>2.365178261243273e-05</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.238945282646455e-05</v>
+        <v>5.463738852995448e-05</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0001121462701121345</v>
+        <v>0.0001261731958948076</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0001403058122377843</v>
+        <v>0.0001426147646270692</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.395013259752886e-05</v>
+        <v>5.270866495266091e-06</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.867064803373069e-05</v>
+        <v>4.07315701522748e-06</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.621017145225778e-05</v>
+        <v>4.406046355143189e-05</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03069451142801e-05</v>
+        <v>4.456502210814506e-05</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.203295197337866e-05</v>
+        <v>4.241568967700005e-05</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.039233994670212e-05</v>
+        <v>2.851468343578745e-05</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.840794958407059e-05</v>
+        <v>5.039842653786764e-05</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.0001745302579365671</v>
+        <v>2.584327739896253e-05</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.390792699065059e-05</v>
+        <v>4.141472891205922e-05</v>
       </c>
       <c r="BI17" t="n">
-        <v>7.056917092995718e-05</v>
+        <v>2.240728827018756e-05</v>
       </c>
       <c r="BJ17" t="n">
-        <v>5.555052484851331e-05</v>
+        <v>0.0001293172826990485</v>
       </c>
       <c r="BK17" t="n">
-        <v>2.519765257602558e-05</v>
+        <v>3.086451761191711e-05</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.958340180863161e-05</v>
+        <v>4.935203469358385e-05</v>
       </c>
       <c r="BM17" t="n">
-        <v>7.574875780846924e-05</v>
+        <v>6.439255230361596e-05</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.345184788689949e-05</v>
+        <v>8.631154742033686e-06</v>
       </c>
       <c r="BO17" t="n">
-        <v>7.98931341705611e-06</v>
+        <v>6.380352715495974e-05</v>
       </c>
       <c r="BP17" t="n">
-        <v>1.117483225243632e-05</v>
+        <v>9.486398630542681e-05</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.080290818819776e-05</v>
+        <v>1.679992237768602e-05</v>
       </c>
       <c r="BR17" t="n">
-        <v>2.644135565788019e-05</v>
+        <v>4.68653452116996e-05</v>
       </c>
       <c r="BS17" t="n">
-        <v>2.551536999817472e-05</v>
+        <v>2.878445047826972e-05</v>
       </c>
       <c r="BT17" t="n">
-        <v>2.978403608722147e-05</v>
+        <v>2.308065086253919e-05</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.429173011681996e-05</v>
+        <v>3.964411007473245e-05</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.0001781567989382893</v>
+        <v>0.0001209993206430227</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.935660636983812e-05</v>
+        <v>1.226399217557628e-05</v>
       </c>
       <c r="BX17" t="n">
-        <v>4.173601701040752e-05</v>
+        <v>3.323513737996109e-05</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.465222734026611e-05</v>
+        <v>1.606497244210914e-05</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.337911271548364e-05</v>
+        <v>3.154194564558566e-05</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.794016679923516e-05</v>
+        <v>5.627037899103016e-05</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.296260026923846e-05</v>
+        <v>3.45101288985461e-05</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.960658093797974e-05</v>
+        <v>2.783268610073719e-05</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.632517629943322e-06</v>
+        <v>9.216394573741127e-06</v>
       </c>
       <c r="CE17" t="n">
-        <v>6.798426329623908e-05</v>
+        <v>6.830296479165554e-05</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.290404336235952e-05</v>
+        <v>1.572703513375018e-05</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.283534533693455e-05</v>
+        <v>1.495747710578144e-05</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.318295107921585e-05</v>
+        <v>2.660612517502159e-05</v>
       </c>
       <c r="CI17" t="n">
-        <v>4.231419006828219e-05</v>
+        <v>3.627585829235613e-05</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.810072353691794e-05</v>
+        <v>2.639157173689455e-06</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.234005048900144e-05</v>
+        <v>7.320059921767097e-06</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.548458749311976e-05</v>
+        <v>4.70189843326807e-06</v>
       </c>
       <c r="CM17" t="n">
-        <v>6.054488767404109e-05</v>
+        <v>3.693684266181663e-05</v>
       </c>
       <c r="CN17" t="n">
-        <v>3.751268195628654e-06</v>
+        <v>0.0001503330277046189</v>
       </c>
       <c r="CO17" t="n">
-        <v>7.382400326605421e-06</v>
+        <v>5.447008152259514e-05</v>
       </c>
       <c r="CP17" t="n">
-        <v>5.312388566380832e-06</v>
+        <v>7.125046522560297e-06</v>
       </c>
       <c r="CQ17" t="n">
-        <v>1.156754115072545e-05</v>
+        <v>3.55357497028308e-06</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.97346817003563e-05</v>
+        <v>7.15224723535357e-06</v>
       </c>
       <c r="CS17" t="n">
-        <v>7.367920625256374e-05</v>
+        <v>1.093632090487517e-05</v>
       </c>
       <c r="CT17" t="n">
-        <v>6.404734449461102e-05</v>
+        <v>2.1707692212658e-06</v>
       </c>
       <c r="CU17" t="n">
-        <v>3.776762241614051e-06</v>
+        <v>8.240514944191091e-06</v>
       </c>
       <c r="CV17" t="n">
-        <v>4.697745680459775e-06</v>
+        <v>2.34539074881468e-05</v>
       </c>
       <c r="CW17" t="n">
-        <v>5.333154331310652e-05</v>
+        <v>7.765858754282817e-05</v>
       </c>
       <c r="CX17" t="n">
-        <v>2.93856155622052e-05</v>
+        <v>1.254289145435905e-05</v>
       </c>
       <c r="CY17" t="n">
-        <v>4.764420737046748e-05</v>
+        <v>2.440924072288908e-05</v>
       </c>
       <c r="CZ17" t="n">
-        <v>7.632856068084948e-06</v>
+        <v>6.516406756418291e-07</v>
       </c>
       <c r="DA17" t="n">
-        <v>5.718956163036637e-05</v>
+        <v>4.498089401749894e-05</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.258692827832419e-05</v>
+        <v>1.783746120054275e-05</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.102286089211702e-05</v>
+        <v>1.955941115738824e-07</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.320259798376355e-06</v>
+        <v>9.522091204416938e-06</v>
       </c>
       <c r="DE17" t="n">
-        <v>3.214063326595351e-05</v>
+        <v>1.385536324960412e-05</v>
       </c>
       <c r="DF17" t="n">
-        <v>9.27834480535239e-05</v>
+        <v>6.866813055239618e-05</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.101228735933546e-05</v>
+        <v>0.0001359833695460111</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.0001012304710457101</v>
+        <v>4.202255149721168e-05</v>
       </c>
       <c r="DI17" t="n">
-        <v>2.892127122322563e-05</v>
+        <v>2.778623456833884e-05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>6.17704245087225e-06</v>
+        <v>8.506569429300725e-05</v>
       </c>
       <c r="DK17" t="n">
-        <v>6.045502959750593e-05</v>
+        <v>2.085049709421583e-05</v>
       </c>
       <c r="DL17" t="n">
-        <v>4.192654159851372e-05</v>
+        <v>1.106915442505851e-05</v>
       </c>
       <c r="DM17" t="n">
-        <v>4.302990782889538e-05</v>
+        <v>3.457580532995053e-06</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.302293094340712e-05</v>
+        <v>1.188653550343588e-05</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.453538218105678e-05</v>
+        <v>7.63641728553921e-05</v>
       </c>
       <c r="DP17" t="n">
-        <v>8.925667316361796e-06</v>
+        <v>1.697210450402054e-06</v>
       </c>
       <c r="DQ17" t="n">
-        <v>4.688721674028784e-05</v>
+        <v>5.860400415258482e-05</v>
       </c>
       <c r="DR17" t="n">
-        <v>1.532076930743642e-05</v>
+        <v>2.885762296500616e-05</v>
       </c>
       <c r="DS17" t="n">
-        <v>6.038781066308729e-05</v>
+        <v>3.851549263345078e-05</v>
       </c>
       <c r="DT17" t="n">
-        <v>2.541182402637787e-05</v>
+        <v>3.701923560583964e-06</v>
       </c>
       <c r="DU17" t="n">
-        <v>2.316040263394825e-05</v>
+        <v>1.068520396074746e-05</v>
       </c>
       <c r="DV17" t="n">
-        <v>1.588164559507277e-05</v>
+        <v>4.298023122828454e-05</v>
       </c>
       <c r="DW17" t="n">
-        <v>3.489976734272204e-07</v>
+        <v>4.029432602692395e-05</v>
       </c>
       <c r="DX17" t="n">
-        <v>6.429270797525533e-06</v>
+        <v>3.295393253210932e-05</v>
       </c>
       <c r="DY17" t="n">
-        <v>4.353262920631096e-05</v>
+        <v>5.48143834748771e-05</v>
       </c>
       <c r="DZ17" t="n">
-        <v>1.035277819028124e-06</v>
+        <v>1.723365312500391e-05</v>
       </c>
       <c r="EA17" t="n">
-        <v>2.992536064994056e-05</v>
+        <v>3.853856105706654e-05</v>
       </c>
       <c r="EB17" t="n">
-        <v>2.609467628644779e-05</v>
+        <v>3.91878311347682e-05</v>
       </c>
       <c r="EC17" t="n">
-        <v>4.011549208371434e-07</v>
+        <v>1.982237699849065e-05</v>
       </c>
       <c r="ED17" t="n">
-        <v>4.052298027090728e-05</v>
+        <v>7.827499211998656e-05</v>
       </c>
       <c r="EE17" t="n">
-        <v>1.364006857329514e-05</v>
+        <v>4.791744868271053e-05</v>
       </c>
       <c r="EF17" t="n">
-        <v>3.874164758599363e-05</v>
+        <v>2.951399437733926e-05</v>
       </c>
       <c r="EG17" t="n">
-        <v>4.769870429299772e-05</v>
+        <v>1.129600696003763e-05</v>
       </c>
       <c r="EH17" t="n">
-        <v>3.558797834557481e-05</v>
+        <v>6.735713213856798e-06</v>
       </c>
       <c r="EI17" t="n">
-        <v>2.14052852243185e-05</v>
+        <v>9.659576608100906e-05</v>
       </c>
       <c r="EJ17" t="n">
-        <v>3.240238584112376e-05</v>
+        <v>2.441835385980085e-05</v>
       </c>
       <c r="EK17" t="n">
-        <v>2.380908335908316e-05</v>
+        <v>4.958789577358402e-05</v>
       </c>
       <c r="EL17" t="n">
-        <v>2.731058157223742e-05</v>
+        <v>2.872927780117607e-06</v>
       </c>
       <c r="EM17" t="n">
-        <v>6.386806035152404e-06</v>
+        <v>2.503365431039128e-05</v>
       </c>
       <c r="EN17" t="n">
-        <v>4.326419457356678e-06</v>
+        <v>8.176322808139957e-06</v>
       </c>
       <c r="EO17" t="n">
-        <v>1.584657002240419e-05</v>
+        <v>5.420714660431258e-05</v>
       </c>
       <c r="EP17" t="n">
-        <v>1.795933167159092e-05</v>
+        <v>2.244024653919041e-05</v>
       </c>
       <c r="EQ17" t="n">
-        <v>5.692361446563154e-05</v>
+        <v>1.509353478468256e-05</v>
       </c>
       <c r="ER17" t="n">
-        <v>4.621267362381332e-05</v>
+        <v>1.94826461665798e-05</v>
       </c>
       <c r="ES17" t="n">
-        <v>2.351759030716494e-05</v>
+        <v>3.220081634935923e-05</v>
       </c>
       <c r="ET17" t="n">
-        <v>5.046898877480999e-05</v>
+        <v>7.085434390319278e-06</v>
       </c>
       <c r="EU17" t="n">
-        <v>2.057822894130368e-05</v>
+        <v>2.979701639560517e-05</v>
       </c>
       <c r="EV17" t="n">
-        <v>5.251662514638156e-05</v>
+        <v>1.188883470604196e-05</v>
       </c>
       <c r="EW17" t="n">
-        <v>8.05621766630793e-06</v>
+        <v>2.851954832294723e-06</v>
       </c>
       <c r="EX17" t="n">
-        <v>1.222914397658315e-05</v>
+        <v>9.010096619022079e-06</v>
       </c>
       <c r="EY17" t="n">
-        <v>5.13975573994685e-05</v>
+        <v>8.253561827586964e-05</v>
       </c>
       <c r="EZ17" t="n">
-        <v>1.757462450768799e-05</v>
+        <v>2.183395736210514e-05</v>
       </c>
       <c r="FA17" t="n">
-        <v>4.595228892867453e-05</v>
+        <v>1.105790943256579e-05</v>
       </c>
       <c r="FB17" t="n">
-        <v>5.230128863331629e-07</v>
+        <v>6.494418357760878e-06</v>
       </c>
       <c r="FC17" t="n">
-        <v>4.850561526836827e-05</v>
+        <v>3.3922704460565e-05</v>
       </c>
       <c r="FD17" t="n">
-        <v>2.605691952339839e-05</v>
+        <v>2.059223334072158e-07</v>
       </c>
       <c r="FE17" t="n">
-        <v>2.199413574999198e-05</v>
+        <v>6.729537744831759e-06</v>
       </c>
       <c r="FF17" t="n">
-        <v>2.035747093032114e-05</v>
+        <v>9.640489224693738e-06</v>
       </c>
       <c r="FG17" t="n">
-        <v>4.808925950783305e-06</v>
+        <v>1.736001468088944e-05</v>
       </c>
       <c r="FH17" t="n">
-        <v>3.958619345212355e-05</v>
+        <v>3.039241346414201e-05</v>
       </c>
       <c r="FI17" t="n">
-        <v>3.748705057660118e-05</v>
+        <v>9.561003935232293e-06</v>
       </c>
       <c r="FJ17" t="n">
-        <v>5.647804937325418e-05</v>
+        <v>1.895962122944184e-05</v>
       </c>
       <c r="FK17" t="n">
-        <v>1.697178959148005e-05</v>
+        <v>6.301593384705484e-05</v>
       </c>
       <c r="FL17" t="n">
-        <v>3.938442750950344e-05</v>
+        <v>4.136168172408361e-06</v>
       </c>
       <c r="FM17" t="n">
-        <v>1.942671406141017e-05</v>
+        <v>3.310521424282342e-05</v>
       </c>
       <c r="FN17" t="n">
-        <v>3.218322672182694e-05</v>
+        <v>2.888574726966908e-06</v>
       </c>
       <c r="FO17" t="n">
-        <v>3.869440843118355e-05</v>
+        <v>7.159221422625706e-05</v>
       </c>
       <c r="FP17" t="n">
-        <v>2.173497159674298e-05</v>
+        <v>4.293422898626886e-05</v>
       </c>
       <c r="FQ17" t="n">
-        <v>4.738073403132148e-05</v>
+        <v>1.241150948771974e-05</v>
       </c>
       <c r="FR17" t="n">
-        <v>2.161208794859704e-05</v>
+        <v>3.95922725147102e-05</v>
       </c>
       <c r="FS17" t="n">
-        <v>8.37217885418795e-05</v>
+        <v>0.0001072358354576863</v>
       </c>
       <c r="FT17" t="n">
-        <v>6.472474342444912e-05</v>
+        <v>7.670700142625719e-05</v>
       </c>
       <c r="FU17" t="n">
-        <v>9.408029654878192e-06</v>
+        <v>9.911431698128581e-05</v>
       </c>
       <c r="FV17" t="n">
-        <v>2.89709132630378e-05</v>
+        <v>8.754341979511082e-05</v>
       </c>
       <c r="FW17" t="n">
-        <v>2.791450606309809e-05</v>
+        <v>9.835512901190668e-05</v>
       </c>
       <c r="FX17" t="n">
-        <v>1.119237640523352e-05</v>
+        <v>7.555383945145877e-06</v>
       </c>
       <c r="FY17" t="n">
-        <v>5.820060323458165e-05</v>
+        <v>2.807609598676208e-05</v>
       </c>
       <c r="FZ17" t="n">
-        <v>7.917844868643442e-07</v>
+        <v>7.449894837918691e-06</v>
       </c>
       <c r="GA17" t="n">
-        <v>2.4302191377501e-05</v>
+        <v>2.707145540625788e-06</v>
       </c>
       <c r="GB17" t="n">
-        <v>4.577270374284126e-05</v>
+        <v>2.78480292763561e-05</v>
       </c>
       <c r="GC17" t="n">
-        <v>4.58371068816632e-05</v>
+        <v>1.674211853242014e-05</v>
       </c>
       <c r="GD17" t="n">
-        <v>5.692778358934447e-05</v>
+        <v>3.782503699767403e-05</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.0001493427553214133</v>
+        <v>4.828255987376906e-05</v>
       </c>
       <c r="GF17" t="n">
-        <v>1.021136267809197e-05</v>
+        <v>1.276537568628555e-05</v>
       </c>
       <c r="GG17" t="n">
-        <v>2.052039235422853e-05</v>
+        <v>2.568702620919794e-05</v>
       </c>
     </row>
     <row r="18">
